--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43612,6 +43612,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1881">
+      <c r="A1881" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1881" t="n">
+        <v>4345134</v>
+      </c>
+      <c r="C1881" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="D1881" t="n">
+        <v>4.12200021743774</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="G1881" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43635,6 +43635,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1882">
+      <c r="A1882" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1882" t="n">
+        <v>4836978</v>
+      </c>
+      <c r="C1882" t="n">
+        <v>4.22900009155273</v>
+      </c>
+      <c r="D1882" t="n">
+        <v>4.12599992752075</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>4.1729998588562</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>4.21799993515015</v>
+      </c>
+      <c r="G1882" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43658,6 +43658,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1883">
+      <c r="A1883" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1883" t="n">
+        <v>4564974</v>
+      </c>
+      <c r="C1883" t="n">
+        <v>4.25500011444092</v>
+      </c>
+      <c r="D1883" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>4.22200012207031</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>4.16300010681152</v>
+      </c>
+      <c r="G1883" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43681,6 +43681,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1884">
+      <c r="A1884" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1884" t="n">
+        <v>5385592</v>
+      </c>
+      <c r="C1884" t="n">
+        <v>4.23199987411499</v>
+      </c>
+      <c r="D1884" t="n">
+        <v>4.15799999237061</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="F1884" t="n">
+        <v>4.19500017166138</v>
+      </c>
+      <c r="G1884" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43522,22 +43522,22 @@
     </row>
     <row r="1877">
       <c r="A1877" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1877" t="n">
-        <v>6384922</v>
+        <v>3846991</v>
       </c>
       <c r="C1877" t="n">
-        <v>4.23400020599365</v>
+        <v>4.26300001144409</v>
       </c>
       <c r="D1877" t="n">
-        <v>4.14099979400635</v>
+        <v>4.19399976730347</v>
       </c>
       <c r="E1877" t="n">
-        <v>4.22100019454956</v>
+        <v>4.26000022888184</v>
       </c>
       <c r="F1877" t="n">
-        <v>4.15500020980835</v>
+        <v>4.21400022506714</v>
       </c>
       <c r="G1877" t="s">
         <v>7</v>
@@ -43545,22 +43545,22 @@
     </row>
     <row r="1878">
       <c r="A1878" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1878" t="n">
-        <v>6097770</v>
+        <v>6384922</v>
       </c>
       <c r="C1878" t="n">
-        <v>4.1560001373291</v>
+        <v>4.23400020599365</v>
       </c>
       <c r="D1878" t="n">
-        <v>4.06300020217896</v>
+        <v>4.14099979400635</v>
       </c>
       <c r="E1878" t="n">
-        <v>4.12799978256226</v>
+        <v>4.22100019454956</v>
       </c>
       <c r="F1878" t="n">
-        <v>4.08500003814697</v>
+        <v>4.15500020980835</v>
       </c>
       <c r="G1878" t="s">
         <v>7</v>
@@ -43568,22 +43568,22 @@
     </row>
     <row r="1879">
       <c r="A1879" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1879" t="n">
-        <v>5633768</v>
+        <v>6097770</v>
       </c>
       <c r="C1879" t="n">
-        <v>4.13700008392334</v>
+        <v>4.1560001373291</v>
       </c>
       <c r="D1879" t="n">
-        <v>4.05399990081787</v>
+        <v>4.06300020217896</v>
       </c>
       <c r="E1879" t="n">
+        <v>4.12799978256226</v>
+      </c>
+      <c r="F1879" t="n">
         <v>4.08500003814697</v>
-      </c>
-      <c r="F1879" t="n">
-        <v>4.10599994659424</v>
       </c>
       <c r="G1879" t="s">
         <v>7</v>
@@ -43591,22 +43591,22 @@
     </row>
     <row r="1880">
       <c r="A1880" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1880" t="n">
-        <v>4018638</v>
+        <v>5633768</v>
       </c>
       <c r="C1880" t="n">
-        <v>4.18200016021729</v>
+        <v>4.13700008392334</v>
       </c>
       <c r="D1880" t="n">
+        <v>4.05399990081787</v>
+      </c>
+      <c r="E1880" t="n">
         <v>4.08500003814697</v>
       </c>
-      <c r="E1880" t="n">
-        <v>4.1100001335144</v>
-      </c>
       <c r="F1880" t="n">
-        <v>4.18200016021729</v>
+        <v>4.10599994659424</v>
       </c>
       <c r="G1880" t="s">
         <v>7</v>
@@ -43614,22 +43614,22 @@
     </row>
     <row r="1881">
       <c r="A1881" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1881" t="n">
-        <v>4345134</v>
+        <v>4018638</v>
       </c>
       <c r="C1881" t="n">
-        <v>4.21000003814697</v>
+        <v>4.18200016021729</v>
       </c>
       <c r="D1881" t="n">
-        <v>4.12200021743774</v>
+        <v>4.08500003814697</v>
       </c>
       <c r="E1881" t="n">
-        <v>4.17000007629395</v>
+        <v>4.1100001335144</v>
       </c>
       <c r="F1881" t="n">
-        <v>4.17000007629395</v>
+        <v>4.18200016021729</v>
       </c>
       <c r="G1881" t="s">
         <v>7</v>
@@ -43637,22 +43637,22 @@
     </row>
     <row r="1882">
       <c r="A1882" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1882" t="n">
-        <v>4836978</v>
+        <v>4345134</v>
       </c>
       <c r="C1882" t="n">
-        <v>4.22900009155273</v>
+        <v>4.21000003814697</v>
       </c>
       <c r="D1882" t="n">
-        <v>4.12599992752075</v>
+        <v>4.12200021743774</v>
       </c>
       <c r="E1882" t="n">
-        <v>4.1729998588562</v>
+        <v>4.17000007629395</v>
       </c>
       <c r="F1882" t="n">
-        <v>4.21799993515015</v>
+        <v>4.17000007629395</v>
       </c>
       <c r="G1882" t="s">
         <v>7</v>
@@ -43660,22 +43660,22 @@
     </row>
     <row r="1883">
       <c r="A1883" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1883" t="n">
-        <v>4564974</v>
+        <v>4836978</v>
       </c>
       <c r="C1883" t="n">
-        <v>4.25500011444092</v>
+        <v>4.22900009155273</v>
       </c>
       <c r="D1883" t="n">
-        <v>4.15999984741211</v>
+        <v>4.12599992752075</v>
       </c>
       <c r="E1883" t="n">
-        <v>4.22200012207031</v>
+        <v>4.1729998588562</v>
       </c>
       <c r="F1883" t="n">
-        <v>4.16300010681152</v>
+        <v>4.21799993515015</v>
       </c>
       <c r="G1883" t="s">
         <v>7</v>
@@ -43683,24 +43683,47 @@
     </row>
     <row r="1884">
       <c r="A1884" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1884" t="n">
-        <v>5385592</v>
+        <v>4564974</v>
       </c>
       <c r="C1884" t="n">
-        <v>4.23199987411499</v>
+        <v>4.25500011444092</v>
       </c>
       <c r="D1884" t="n">
-        <v>4.15799999237061</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="E1884" t="n">
-        <v>4.17000007629395</v>
+        <v>4.22200012207031</v>
       </c>
       <c r="F1884" t="n">
-        <v>4.19500017166138</v>
+        <v>4.16300010681152</v>
       </c>
       <c r="G1884" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1885" t="n">
+        <v>14015041</v>
+      </c>
+      <c r="C1885" t="n">
+        <v>4.21400022506714</v>
+      </c>
+      <c r="D1885" t="n">
+        <v>4.13299989700317</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>4.18100023269653</v>
+      </c>
+      <c r="F1885" t="n">
+        <v>4.14599990844727</v>
+      </c>
+      <c r="G1885" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -49437,6 +49437,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1888">
+      <c r="A1888" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1888" t="n">
+        <v>5796018</v>
+      </c>
+      <c r="C1888" t="n">
+        <v>4.25699996948242</v>
+      </c>
+      <c r="D1888" t="n">
+        <v>4.13600015640259</v>
+      </c>
+      <c r="E1888" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F1888" t="n">
+        <v>4.19399976730347</v>
+      </c>
+      <c r="G1888" t="n">
+        <v>4.19399976730347</v>
+      </c>
+      <c r="H1888" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -49460,6 +49460,32 @@
         <v>4.19399976730347</v>
       </c>
       <c r="H1888" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1889" t="n">
+        <v>3951980</v>
+      </c>
+      <c r="C1889" t="n">
+        <v>4.22399997711182</v>
+      </c>
+      <c r="D1889" t="n">
+        <v>4.14099979400635</v>
+      </c>
+      <c r="E1889" t="n">
+        <v>4.20900011062622</v>
+      </c>
+      <c r="F1889" t="n">
+        <v>4.14099979400635</v>
+      </c>
+      <c r="G1889" t="n">
+        <v>4.14099979400635</v>
+      </c>
+      <c r="H1889" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35755968093872</v>
+        <v>7.35756015777588</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.46354389190674</v>
+        <v>7.4635443687439</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0404839515686</v>
+        <v>7.04048442840576</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.19551849365234</v>
+        <v>7.1955189704895</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.36631870269775</v>
+        <v>7.3663182258606</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65098571777344</v>
+        <v>7.6509861946106</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047325134277</v>
+        <v>7.76047372817993</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638624191284</v>
+        <v>7.79638576507568</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813718795776</v>
+        <v>7.79813766479492</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62032985687256</v>
+        <v>7.6203293800354</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675174713135</v>
+        <v>7.78675127029419</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214775085449</v>
+        <v>8.17214679718018</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521339416504</v>
+        <v>8.11521434783936</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287887573242</v>
+        <v>8.03287792205811</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.1160888671875</v>
+        <v>8.11608982086182</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295307159424</v>
+        <v>7.98295259475708</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718954086304</v>
+        <v>7.72718906402588</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.82091093063354</v>
+        <v>7.8209114074707</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010763168335</v>
+        <v>7.89010715484619</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528961181641</v>
+        <v>7.94528913497925</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00484943389893</v>
+        <v>8.00485038757324</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9838285446167</v>
+        <v>7.98382806777954</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907913208008</v>
+        <v>8.34907817840576</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5032377243042</v>
+        <v>8.50323677062988</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411426544189</v>
+        <v>8.38411521911621</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732723236084</v>
+        <v>8.34732627868652</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39375019073486</v>
+        <v>8.39374923706055</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644866943359</v>
+        <v>8.58644771575928</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703330993652</v>
+        <v>8.54703235626221</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535358428955</v>
+        <v>8.61535263061523</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40864086151123</v>
+        <v>8.40863990783691</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206737518311</v>
+        <v>8.70206642150879</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330680847168</v>
+        <v>8.81330585479736</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790580749512</v>
+        <v>8.66790676116943</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.69330787658691</v>
+        <v>8.6933069229126</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.7046947479248</v>
+        <v>8.70469379425049</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856868743896</v>
+        <v>8.33856773376465</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827796936035</v>
+        <v>8.17827892303467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294498443604</v>
+        <v>8.46294593811035</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207557678223</v>
+        <v>8.10207462310791</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944416046143</v>
+        <v>8.33944320678711</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973796844482</v>
+        <v>8.25973701477051</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.47871208190918</v>
+        <v>8.4787130355835</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995555877686</v>
+        <v>8.34995460510254</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470092773438</v>
+        <v>8.22470188140869</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207260131836</v>
+        <v>8.22207355499268</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688087463379</v>
+        <v>8.88688182830811</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184169769287</v>
+        <v>9.09184265136719</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05155086517334</v>
+        <v>9.05154991149902</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.6348991394043</v>
+        <v>9.63490009307861</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429214477539</v>
+        <v>10.1429224014282</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256153106689</v>
+        <v>9.79256248474121</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409881591797</v>
+        <v>9.58409786224365</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235050201416</v>
+        <v>10.2235040664673</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754684448242</v>
+        <v>10.6754693984985</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471460342407</v>
+        <v>10.8471450805664</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141557693481</v>
+        <v>10.6141567230225</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224729537964</v>
+        <v>10.9224739074707</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027616500854</v>
+        <v>11.2027606964111</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652364730835</v>
+        <v>11.6652355194092</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793991088867</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422815322876</v>
+        <v>14.1422805786133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5273990631104</v>
+        <v>13.5274000167847</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789394378662</v>
+        <v>13.0789384841919</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718181610107</v>
+        <v>10.7718191146851</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716648101807</v>
+        <v>9.40716552734375</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651054382324</v>
+        <v>10.5651063919067</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632061004639</v>
+        <v>10.6632070541382</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788940429688</v>
+        <v>9.86788845062256</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743072509766</v>
+        <v>10.2743062973022</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779502868652</v>
+        <v>10.7779493331909</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421770095825</v>
+        <v>11.2421760559082</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.3648023605347</v>
+        <v>11.364803314209</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969161987305</v>
+        <v>11.5969152450562</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064037322998</v>
+        <v>11.7064027786255</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.41588306427</v>
+        <v>12.4158821105957</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.109317779541</v>
+        <v>12.1093168258667</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925359725952</v>
+        <v>11.5925369262695</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961790084839</v>
+        <v>12.0961799621582</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.437780380249</v>
+        <v>12.4377794265747</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633197784424</v>
+        <v>12.9633207321167</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297325134277</v>
+        <v>13.7297334671021</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027433395386</v>
+        <v>12.4027442932129</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421504974365</v>
+        <v>13.0421514511108</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173309326172</v>
+        <v>13.2173318862915</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0844717025757</v>
+        <v>14.08447265625</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676826477051</v>
+        <v>14.1676816940308</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830238342285</v>
+        <v>13.2830228805542</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640478134155</v>
+        <v>13.0640487670898</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3092994689941</v>
+        <v>13.3093004226685</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.347240447998</v>
+        <v>14.3472414016724</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589159011841</v>
+        <v>14.7589149475098</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129251480103</v>
+        <v>15.0129261016846</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326374053955</v>
+        <v>14.7326364517212</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.8070907592773</v>
+        <v>14.807089805603</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.828987121582</v>
+        <v>14.8289880752563</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.271315574646</v>
+        <v>15.2713165283203</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720701217651</v>
+        <v>13.5720710754395</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195251464844</v>
+        <v>12.9195241928101</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268194198608</v>
+        <v>13.3268184661865</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866659164429</v>
+        <v>13.7866649627686</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457853317261</v>
+        <v>14.1457843780518</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647603988647</v>
+        <v>14.3647594451904</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.887393951416</v>
+        <v>13.8873949050903</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348489761353</v>
+        <v>13.2348480224609</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925113677979</v>
+        <v>13.3925104141235</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122226715088</v>
+        <v>13.1122236251831</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027351379395</v>
+        <v>13.0027360916138</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450727462769</v>
+        <v>12.8450736999512</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516380310059</v>
+        <v>13.1516389846802</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.7662420272827</v>
+        <v>12.766242980957</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202531814575</v>
+        <v>13.0202541351318</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049211502075</v>
+        <v>13.3049201965332</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260904312134</v>
+        <v>13.2260894775391</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.4275465011597</v>
+        <v>13.427547454834</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005336761475</v>
+        <v>13.9005327224731</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618381500244</v>
+        <v>14.5618371963501</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465061187744</v>
+        <v>14.8465051651001</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3223972320557</v>
+        <v>16.322395324707</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056053161621</v>
+        <v>16.4056072235107</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968395233154</v>
+        <v>16.9968414306641</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.475679397583</v>
+        <v>16.4756774902344</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588975906372</v>
+        <v>15.9588966369629</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348142623901</v>
+        <v>15.6348161697388</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640068054199</v>
+        <v>16.0640048980713</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793315887451</v>
+        <v>16.3793296813965</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362712860107</v>
+        <v>15.8362722396851</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.8625497817993</v>
+        <v>15.862548828125</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034303665161</v>
+        <v>15.5034313201904</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581787109375</v>
+        <v>15.2581777572632</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756967544556</v>
+        <v>15.2756958007812</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662082672119</v>
+        <v>15.1662092208862</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771518707275</v>
+        <v>15.4771528244019</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552555084229</v>
+        <v>15.4552564620972</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443017959595</v>
+        <v>15.7443027496338</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.884446144104</v>
+        <v>15.8844470977783</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304340362549</v>
+        <v>15.6304349899292</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.6435747146606</v>
+        <v>15.643575668335</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275136947632</v>
+        <v>15.8275127410889</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676570892334</v>
+        <v>15.9676561355591</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.46839427948</v>
+        <v>15.4683933258057</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413887023926</v>
+        <v>15.3413877487183</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.354528427124</v>
+        <v>15.3545274734497</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421340942383</v>
+        <v>14.2421350479126</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684024810791</v>
+        <v>14.8684034347534</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501462936401</v>
+        <v>15.3501472473145</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.424599647522</v>
+        <v>15.4246006011963</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056573867798</v>
+        <v>12.8056583404541</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355852127075</v>
+        <v>12.7355861663818</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326629638672</v>
+        <v>12.9326639175415</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.814416885376</v>
+        <v>12.8144178390503</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574825286865</v>
+        <v>12.7574834823608</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224565505981</v>
+        <v>12.1224555969238</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.245080947876</v>
+        <v>12.2450819015503</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.021728515625</v>
+        <v>12.0217275619507</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830411911011</v>
+        <v>12.0830402374268</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282928466797</v>
+        <v>12.3282918930054</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.223183631897</v>
+        <v>12.2231845855713</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.868444442749</v>
+        <v>11.8684453964233</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618719100952</v>
+        <v>12.1618709564209</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764677047729</v>
+        <v>12.3764667510986</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385074615479</v>
+        <v>12.5385084152222</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553066253662</v>
+        <v>11.8553056716919</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407108306885</v>
+        <v>11.6407117843628</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516563415527</v>
+        <v>11.9516553878784</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472761154175</v>
+        <v>11.9472770690918</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348745346069</v>
+        <v>11.4348754882812</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370687484741</v>
+        <v>11.1370677947998</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786773681641</v>
+        <v>10.8786783218384</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173728942871</v>
+        <v>10.2173738479614</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629409790039</v>
+        <v>9.16629314422607</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93417930603027</v>
+        <v>8.93418025970459</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862350463867</v>
+        <v>9.60862255096436</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804706573486</v>
+        <v>9.04804611206055</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652191162109</v>
+        <v>8.53652095794678</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.37010097503662</v>
+        <v>8.3701000213623</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740249633789</v>
+        <v>8.17740345001221</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813564300537</v>
+        <v>7.91813611984253</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441318511963</v>
+        <v>7.94441270828247</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813968658447</v>
+        <v>7.67813873291016</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.044264793396</v>
+        <v>8.04426574707031</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274059295654</v>
+        <v>7.53274011611938</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806346893311</v>
+        <v>7.84806394577026</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398109436035</v>
+        <v>7.52398061752319</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498962402344</v>
+        <v>8.50498867034912</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282869338989</v>
+        <v>6.40282917022705</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449819564819</v>
+        <v>7.05449867248535</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500911712646</v>
+        <v>7.06500959396362</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055969238281</v>
+        <v>6.87055921554565</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668622970581</v>
+        <v>7.23668575286865</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916723251343</v>
+        <v>7.21916770935059</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419713973999</v>
+        <v>7.73419666290283</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923274993896</v>
+        <v>7.76923322677612</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.70091247558594</v>
+        <v>7.7009129524231</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098417282104</v>
+        <v>7.77098512649536</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791650772095</v>
+        <v>7.94791698455811</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222610473633</v>
+        <v>7.76222658157349</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376100540161</v>
+        <v>7.55376148223877</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.4661717414856</v>
+        <v>7.46617126464844</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267150878906</v>
+        <v>7.22267198562622</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.3347864151001</v>
+        <v>7.33478593826294</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18238019943237</v>
+        <v>7.18237972259521</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755254745483</v>
+        <v>7.83755302429199</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908935546875</v>
+        <v>7.62908887863159</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784837722778</v>
+        <v>7.63784790039062</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.7464599609375</v>
+        <v>7.74645948410034</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412496566772</v>
+        <v>7.66412544250488</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157487869263</v>
+        <v>7.37157440185547</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.56952810287476</v>
+        <v>7.5695276260376</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230445861816</v>
+        <v>7.35230493545532</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675745010376</v>
+        <v>7.30675792694092</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456371307373</v>
+        <v>7.60456418991089</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142339706421</v>
+        <v>7.71142387390137</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.5169734954834</v>
+        <v>7.51697397232056</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755611419678</v>
+        <v>7.59755659103394</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047777175903</v>
+        <v>7.52047729492188</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448892593384</v>
+        <v>7.77448844909668</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711380004883</v>
+        <v>7.89711427688599</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.674635887146</v>
+        <v>7.67463541030884</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81477975845337</v>
+        <v>7.81478023529053</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.64660692214966</v>
+        <v>7.6466064453125</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981893539429</v>
+        <v>7.60981941223145</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952453613281</v>
+        <v>7.80952501296997</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602382659912</v>
+        <v>7.56602430343628</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427192687988</v>
+        <v>7.56427240371704</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945592880249</v>
+        <v>7.49945640563965</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500650405884</v>
+        <v>7.30500602722168</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.3610634803772</v>
+        <v>7.36106443405151</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.40836238861084</v>
+        <v>7.408362865448</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587995529175</v>
+        <v>7.42587947845459</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617792129517</v>
+        <v>6.98617839813232</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129283905029</v>
+        <v>6.61129331588745</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881135940552</v>
+        <v>6.62881088256836</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76369953155518</v>
+        <v>6.76370000839233</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997659683228</v>
+        <v>6.78997707366943</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632535934448</v>
+        <v>6.88632583618164</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355209350586</v>
+        <v>6.86355257034302</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997303009033</v>
+        <v>7.02997350692749</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.12106704711914</v>
+        <v>7.1210675239563</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.6220817565918</v>
+        <v>7.62208127975464</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011381149292</v>
+        <v>7.41011428833008</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252359390259</v>
+        <v>7.32252407073975</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055255889893</v>
+        <v>7.35055303573608</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953428268433</v>
+        <v>7.08953475952148</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092674255371</v>
+        <v>6.74092626571655</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107370376587</v>
+        <v>6.64107322692871</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414232254028</v>
+        <v>6.46414184570312</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698728561401</v>
+        <v>6.55698776245117</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961715698242</v>
+        <v>6.43961668014526</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662023544312</v>
+        <v>6.68662071228027</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713163375854</v>
+        <v>6.69713115692139</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450580596924</v>
+        <v>6.57450532913208</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501625061035</v>
+        <v>6.58501672744751</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143766403198</v>
+        <v>6.75143718719482</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.5201997756958</v>
+        <v>6.52019929885864</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815608978271</v>
+        <v>6.47815656661987</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020286560059</v>
+        <v>6.28020334243774</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502290725708</v>
+        <v>6.10502243041992</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260646820068</v>
+        <v>6.67260599136353</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224298477173</v>
+        <v>6.56224250793457</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.70939350128174</v>
+        <v>6.7093939781189</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932228088379</v>
+        <v>6.63932180404663</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070713043213</v>
+        <v>6.77070665359497</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.17509508132935</v>
+        <v>6.1750955581665</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203002929688</v>
+        <v>6.11203050613403</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.15407371520996</v>
+        <v>6.1540732383728</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.81597566604614</v>
+        <v>5.8159761428833</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313070297241</v>
+        <v>5.72313022613525</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210886001587</v>
+        <v>5.70210933685303</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896902084351</v>
+        <v>5.80896854400635</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466608047485</v>
+        <v>5.51466655731201</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474229812622</v>
+        <v>5.34474182128906</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496452331543</v>
+        <v>5.07496500015259</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.8314642906189</v>
+        <v>4.83146381378174</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423755645752</v>
+        <v>4.85423803329468</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642511367798</v>
+        <v>5.03642463684082</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.63203716278076</v>
+        <v>5.6320366859436</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066253662109</v>
+        <v>4.78066205978394</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912668228149</v>
+        <v>4.98912620544434</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867723464966</v>
+        <v>5.76867771148682</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626388549805</v>
+        <v>6.09626436233521</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458463668823</v>
+        <v>6.16458415985107</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268529891968</v>
+        <v>6.26268482208252</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523538589478</v>
+        <v>6.55523586273193</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640419006348</v>
+        <v>6.47640466690063</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034721374512</v>
+        <v>6.42034673690796</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947233200073</v>
+        <v>6.29947280883789</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078952789307</v>
+        <v>6.12078905105591</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589683532715</v>
+        <v>6.22589731216431</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779260635376</v>
+        <v>6.36779308319092</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385410308838</v>
+        <v>6.18385362625122</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516677856445</v>
+        <v>6.24516725540161</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.90006256103516</v>
+        <v>5.900062084198</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583227157593</v>
+        <v>5.67583179473877</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670976638794</v>
+        <v>5.55670928955078</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415515899658</v>
+        <v>5.50415563583374</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569458007812</v>
+        <v>5.05569505691528</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868793487549</v>
+        <v>5.04868745803833</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116941452026</v>
+        <v>5.03116989135742</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920146942139</v>
+        <v>4.81920194625854</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686742782593</v>
+        <v>4.73686695098877</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.93482065200806</v>
+        <v>4.9348201751709</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102602005005</v>
+        <v>4.89102554321289</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320953369141</v>
+        <v>5.31320905685425</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919124603271</v>
+        <v>5.53919172286987</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145763397217</v>
+        <v>5.31145811080933</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.3990478515625</v>
+        <v>5.39904737472534</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.13802909851074</v>
+        <v>5.1380295753479</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.95584201812744</v>
+        <v>4.9558424949646</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766561508179</v>
+        <v>5.02766609191895</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795740127563</v>
+        <v>5.06795692443848</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927007675171</v>
+        <v>5.12927055358887</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678859710693</v>
+        <v>5.14678812026978</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707990646362</v>
+        <v>5.18707942962646</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248565673828</v>
+        <v>4.85248613357544</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.09248304367065</v>
+        <v>5.0924825668335</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.42357301712036</v>
+        <v>5.4235725402832</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.4778790473938</v>
+        <v>5.47787857055664</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488569259644</v>
+        <v>5.48488616943359</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174537658691</v>
+        <v>5.59174585342407</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693199157715</v>
+        <v>5.28693246841431</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941751480103</v>
+        <v>5.02941799163818</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423398971558</v>
+        <v>5.09423446655273</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.13627767562866</v>
+        <v>5.1362771987915</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.22211599349976</v>
+        <v>5.2221155166626</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189590454102</v>
+        <v>5.25189638137817</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.1905837059021</v>
+        <v>5.19058322906494</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613332748413</v>
+        <v>4.99613380432129</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350749969482</v>
+        <v>4.87350797653198</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569862365723</v>
+        <v>4.81569814682007</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657564163208</v>
+        <v>4.69657611846924</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314401626587</v>
+        <v>4.76314449310303</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.9821195602417</v>
+        <v>4.98211908340454</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649681091309</v>
+        <v>5.10649728775024</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416276931763</v>
+        <v>5.02416229248047</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628076553345</v>
+        <v>4.89628124237061</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088119506836</v>
+        <v>4.75088167190552</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803623199463</v>
+        <v>4.65803575515747</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.5967230796814</v>
+        <v>4.59672355651855</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979122161865</v>
+        <v>4.41979169845581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.1176061630249</v>
+        <v>4.11760568618774</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008562088013</v>
+        <v>4.22008609771729</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826095581055</v>
+        <v>4.26826047897339</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.3094277381897</v>
+        <v>4.30942821502686</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030523300171</v>
+        <v>4.19030570983887</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.19731283187866</v>
+        <v>4.1973123550415</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359477043152</v>
+        <v>3.86359453201294</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958028793335</v>
+        <v>3.84958052635193</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147403717041</v>
+        <v>4.11147451400757</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118118286133</v>
+        <v>4.19118165969849</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789901733398</v>
+        <v>4.03789949417114</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556295394897</v>
+        <v>4.07556247711182</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.432053565979</v>
+        <v>4.43205404281616</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.491614818573</v>
+        <v>4.49161529541016</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110485076904</v>
+        <v>4.48110437393188</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592084884644</v>
+        <v>4.54592132568359</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59119009971619</v>
+        <v>3.59118986129761</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512884140015</v>
+        <v>3.77512907981873</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.7033052444458</v>
+        <v>3.70330548286438</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746205329895</v>
+        <v>3.97746181488037</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819187164307</v>
+        <v>3.95819234848022</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483289718628</v>
+        <v>4.09483242034912</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.5056300163269</v>
+        <v>4.50562953948975</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504335403442</v>
+        <v>4.66504383087158</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358324050903</v>
+        <v>4.70358276367188</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365446090698</v>
+        <v>4.77365493774414</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387407302856</v>
+        <v>4.74387454986572</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -49486,6 +49486,32 @@
         <v>4.14099979400635</v>
       </c>
       <c r="H1889" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1890" t="n">
+        <v>3631960</v>
+      </c>
+      <c r="C1890" t="n">
+        <v>4.17199993133545</v>
+      </c>
+      <c r="D1890" t="n">
+        <v>4.10699987411499</v>
+      </c>
+      <c r="E1890" t="n">
+        <v>4.14099979400635</v>
+      </c>
+      <c r="F1890" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G1890" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="H1890" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -49500,7 +49500,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="D1890" t="n">
-        <v>4.10699987411499</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="E1890" t="n">
         <v>4.14099979400635</v>
@@ -49512,6 +49512,32 @@
         <v>4.09999990463257</v>
       </c>
       <c r="H1890" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1891" t="n">
+        <v>3223024</v>
+      </c>
+      <c r="C1891" t="n">
+        <v>4.20499992370605</v>
+      </c>
+      <c r="D1891" t="n">
+        <v>4.11700010299683</v>
+      </c>
+      <c r="E1891" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F1891" t="n">
+        <v>4.16699981689453</v>
+      </c>
+      <c r="G1891" t="n">
+        <v>4.16699981689453</v>
+      </c>
+      <c r="H1891" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -49590,6 +49590,32 @@
         <v>4.13399982452393</v>
       </c>
       <c r="H1893" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1894" t="n">
+        <v>3800374</v>
+      </c>
+      <c r="C1894" t="n">
+        <v>4.21099996566772</v>
+      </c>
+      <c r="D1894" t="n">
+        <v>4.15500020980835</v>
+      </c>
+      <c r="E1894" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F1894" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="G1894" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="H1894" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -43996,8 +43996,31 @@
       <c r="E1897" t="n">
         <v>4.07100009918213</v>
       </c>
-      <c r="F1897"/>
+      <c r="F1897" t="n">
+        <v>4.04400014877319</v>
+      </c>
       <c r="G1897" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1898" t="n">
+        <v>6328580</v>
+      </c>
+      <c r="C1898" t="n">
+        <v>4.20499992370605</v>
+      </c>
+      <c r="D1898" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="E1898" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="F1898"/>
+      <c r="G1898" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -44019,8 +44019,31 @@
       <c r="E1898" t="n">
         <v>4.04500007629395</v>
       </c>
-      <c r="F1898"/>
+      <c r="F1898" t="n">
+        <v>4.15999984741211</v>
+      </c>
       <c r="G1898" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1899" t="n">
+        <v>4048535</v>
+      </c>
+      <c r="C1899" t="n">
+        <v>4.18699979782104</v>
+      </c>
+      <c r="D1899" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E1899" t="n">
+        <v>4.13199996948242</v>
+      </c>
+      <c r="F1899"/>
+      <c r="G1899" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -44042,8 +44042,31 @@
       <c r="E1899" t="n">
         <v>4.13199996948242</v>
       </c>
-      <c r="F1899"/>
+      <c r="F1899" t="n">
+        <v>4.16200017929077</v>
+      </c>
       <c r="G1899" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1900" t="n">
+        <v>4361942</v>
+      </c>
+      <c r="C1900" t="n">
+        <v>4.18100023269653</v>
+      </c>
+      <c r="D1900" t="n">
+        <v>4.09899997711182</v>
+      </c>
+      <c r="E1900" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="F1900"/>
+      <c r="G1900" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -44065,8 +44065,31 @@
       <c r="E1900" t="n">
         <v>4.15000009536743</v>
       </c>
-      <c r="F1900"/>
+      <c r="F1900" t="n">
+        <v>4.12900018692017</v>
+      </c>
       <c r="G1900" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1901" t="n">
+        <v>7154634</v>
+      </c>
+      <c r="C1901" t="n">
+        <v>4.26599979400635</v>
+      </c>
+      <c r="D1901" t="n">
+        <v>4.15399980545044</v>
+      </c>
+      <c r="E1901" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="F1901"/>
+      <c r="G1901" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -44095,6 +44095,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1902">
+      <c r="A1902" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1902" t="n">
+        <v>7383988</v>
+      </c>
+      <c r="C1902" t="n">
+        <v>4.31300020217896</v>
+      </c>
+      <c r="D1902" t="n">
+        <v>4.21400022506714</v>
+      </c>
+      <c r="E1902" t="n">
+        <v>4.21400022506714</v>
+      </c>
+      <c r="F1902" t="n">
+        <v>4.30800008773804</v>
+      </c>
+      <c r="G1902" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -49876,6 +49876,32 @@
         <v>4.26100015640259</v>
       </c>
       <c r="H1904" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1905" t="n">
+        <v>6063961</v>
+      </c>
+      <c r="C1905" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>4.23299980163574</v>
+      </c>
+      <c r="E1905" t="n">
+        <v>4.24200010299683</v>
+      </c>
+      <c r="F1905" t="n">
+        <v>4.30100011825562</v>
+      </c>
+      <c r="G1905" t="n">
+        <v>4.30100011825562</v>
+      </c>
+      <c r="H1905" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35755968093872</v>
+        <v>7.35756015777588</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.46354389190674</v>
+        <v>7.4635443687439</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0404839515686</v>
+        <v>7.04048442840576</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.19551849365234</v>
+        <v>7.1955189704895</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.36631870269775</v>
+        <v>7.3663182258606</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65098571777344</v>
+        <v>7.6509861946106</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047325134277</v>
+        <v>7.76047372817993</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638624191284</v>
+        <v>7.79638576507568</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813718795776</v>
+        <v>7.79813766479492</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62032985687256</v>
+        <v>7.6203293800354</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675174713135</v>
+        <v>7.78675127029419</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214775085449</v>
+        <v>8.17214679718018</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521339416504</v>
+        <v>8.11521434783936</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287887573242</v>
+        <v>8.03287792205811</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.1160888671875</v>
+        <v>8.11608982086182</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295307159424</v>
+        <v>7.98295259475708</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718954086304</v>
+        <v>7.72718906402588</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.82091093063354</v>
+        <v>7.8209114074707</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010763168335</v>
+        <v>7.89010715484619</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528961181641</v>
+        <v>7.94528913497925</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00484943389893</v>
+        <v>8.00485038757324</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9838285446167</v>
+        <v>7.98382806777954</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907913208008</v>
+        <v>8.34907817840576</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5032377243042</v>
+        <v>8.50323677062988</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411426544189</v>
+        <v>8.38411521911621</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732723236084</v>
+        <v>8.34732627868652</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39375019073486</v>
+        <v>8.39374923706055</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644866943359</v>
+        <v>8.58644771575928</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703330993652</v>
+        <v>8.54703235626221</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535358428955</v>
+        <v>8.61535263061523</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40864086151123</v>
+        <v>8.40863990783691</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206737518311</v>
+        <v>8.70206642150879</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330680847168</v>
+        <v>8.81330585479736</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790580749512</v>
+        <v>8.66790676116943</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.69330787658691</v>
+        <v>8.6933069229126</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.7046947479248</v>
+        <v>8.70469379425049</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856868743896</v>
+        <v>8.33856773376465</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827796936035</v>
+        <v>8.17827892303467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294498443604</v>
+        <v>8.46294593811035</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207557678223</v>
+        <v>8.10207462310791</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944416046143</v>
+        <v>8.33944320678711</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973796844482</v>
+        <v>8.25973701477051</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.47871208190918</v>
+        <v>8.4787130355835</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995555877686</v>
+        <v>8.34995460510254</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470092773438</v>
+        <v>8.22470188140869</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207260131836</v>
+        <v>8.22207355499268</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688087463379</v>
+        <v>8.88688182830811</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184169769287</v>
+        <v>9.09184265136719</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05155086517334</v>
+        <v>9.05154991149902</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.6348991394043</v>
+        <v>9.63490009307861</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429214477539</v>
+        <v>10.1429224014282</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256153106689</v>
+        <v>9.79256248474121</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409881591797</v>
+        <v>9.58409786224365</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235050201416</v>
+        <v>10.2235040664673</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754684448242</v>
+        <v>10.6754693984985</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471460342407</v>
+        <v>10.8471450805664</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141557693481</v>
+        <v>10.6141567230225</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224729537964</v>
+        <v>10.9224739074707</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027616500854</v>
+        <v>11.2027606964111</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652364730835</v>
+        <v>11.6652355194092</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793991088867</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422815322876</v>
+        <v>14.1422805786133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5273990631104</v>
+        <v>13.5274000167847</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789394378662</v>
+        <v>13.0789384841919</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718181610107</v>
+        <v>10.7718191146851</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716648101807</v>
+        <v>9.40716552734375</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651054382324</v>
+        <v>10.5651063919067</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632061004639</v>
+        <v>10.6632070541382</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788940429688</v>
+        <v>9.86788845062256</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743072509766</v>
+        <v>10.2743062973022</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779502868652</v>
+        <v>10.7779493331909</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421770095825</v>
+        <v>11.2421760559082</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.3648023605347</v>
+        <v>11.364803314209</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969161987305</v>
+        <v>11.5969152450562</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064037322998</v>
+        <v>11.7064027786255</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.41588306427</v>
+        <v>12.4158821105957</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.109317779541</v>
+        <v>12.1093168258667</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925359725952</v>
+        <v>11.5925369262695</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961790084839</v>
+        <v>12.0961799621582</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.437780380249</v>
+        <v>12.4377794265747</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633197784424</v>
+        <v>12.9633207321167</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297325134277</v>
+        <v>13.7297334671021</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027433395386</v>
+        <v>12.4027442932129</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421504974365</v>
+        <v>13.0421514511108</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173309326172</v>
+        <v>13.2173318862915</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0844717025757</v>
+        <v>14.08447265625</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676826477051</v>
+        <v>14.1676816940308</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830238342285</v>
+        <v>13.2830228805542</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640478134155</v>
+        <v>13.0640487670898</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3092994689941</v>
+        <v>13.3093004226685</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.347240447998</v>
+        <v>14.3472414016724</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589159011841</v>
+        <v>14.7589149475098</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129251480103</v>
+        <v>15.0129261016846</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326374053955</v>
+        <v>14.7326364517212</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.8070907592773</v>
+        <v>14.807089805603</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.828987121582</v>
+        <v>14.8289880752563</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.271315574646</v>
+        <v>15.2713165283203</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720701217651</v>
+        <v>13.5720710754395</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195251464844</v>
+        <v>12.9195241928101</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268194198608</v>
+        <v>13.3268184661865</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866659164429</v>
+        <v>13.7866649627686</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457853317261</v>
+        <v>14.1457843780518</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647603988647</v>
+        <v>14.3647594451904</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.887393951416</v>
+        <v>13.8873949050903</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348489761353</v>
+        <v>13.2348480224609</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925113677979</v>
+        <v>13.3925104141235</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122226715088</v>
+        <v>13.1122236251831</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027351379395</v>
+        <v>13.0027360916138</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450727462769</v>
+        <v>12.8450736999512</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516380310059</v>
+        <v>13.1516389846802</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.7662420272827</v>
+        <v>12.766242980957</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202531814575</v>
+        <v>13.0202541351318</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049211502075</v>
+        <v>13.3049201965332</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260904312134</v>
+        <v>13.2260894775391</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.4275465011597</v>
+        <v>13.427547454834</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005336761475</v>
+        <v>13.9005327224731</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618381500244</v>
+        <v>14.5618371963501</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465061187744</v>
+        <v>14.8465051651001</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3223972320557</v>
+        <v>16.322395324707</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056053161621</v>
+        <v>16.4056072235107</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968395233154</v>
+        <v>16.9968414306641</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.475679397583</v>
+        <v>16.4756774902344</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588975906372</v>
+        <v>15.9588966369629</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348142623901</v>
+        <v>15.6348161697388</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640068054199</v>
+        <v>16.0640048980713</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793315887451</v>
+        <v>16.3793296813965</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362712860107</v>
+        <v>15.8362722396851</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.8625497817993</v>
+        <v>15.862548828125</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034303665161</v>
+        <v>15.5034313201904</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581787109375</v>
+        <v>15.2581777572632</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756967544556</v>
+        <v>15.2756958007812</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662082672119</v>
+        <v>15.1662092208862</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771518707275</v>
+        <v>15.4771528244019</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552555084229</v>
+        <v>15.4552564620972</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443017959595</v>
+        <v>15.7443027496338</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.884446144104</v>
+        <v>15.8844470977783</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304340362549</v>
+        <v>15.6304349899292</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.6435747146606</v>
+        <v>15.643575668335</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275136947632</v>
+        <v>15.8275127410889</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676570892334</v>
+        <v>15.9676561355591</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.46839427948</v>
+        <v>15.4683933258057</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413887023926</v>
+        <v>15.3413877487183</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.354528427124</v>
+        <v>15.3545274734497</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421340942383</v>
+        <v>14.2421350479126</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684024810791</v>
+        <v>14.8684034347534</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501462936401</v>
+        <v>15.3501472473145</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.424599647522</v>
+        <v>15.4246006011963</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056573867798</v>
+        <v>12.8056583404541</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355852127075</v>
+        <v>12.7355861663818</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326629638672</v>
+        <v>12.9326639175415</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.814416885376</v>
+        <v>12.8144178390503</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574825286865</v>
+        <v>12.7574834823608</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224565505981</v>
+        <v>12.1224555969238</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.245080947876</v>
+        <v>12.2450819015503</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.021728515625</v>
+        <v>12.0217275619507</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830411911011</v>
+        <v>12.0830402374268</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282928466797</v>
+        <v>12.3282918930054</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.223183631897</v>
+        <v>12.2231845855713</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.868444442749</v>
+        <v>11.8684453964233</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618719100952</v>
+        <v>12.1618709564209</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764677047729</v>
+        <v>12.3764667510986</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385074615479</v>
+        <v>12.5385084152222</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553066253662</v>
+        <v>11.8553056716919</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407108306885</v>
+        <v>11.6407117843628</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516563415527</v>
+        <v>11.9516553878784</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472761154175</v>
+        <v>11.9472770690918</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348745346069</v>
+        <v>11.4348754882812</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370687484741</v>
+        <v>11.1370677947998</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786773681641</v>
+        <v>10.8786783218384</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173728942871</v>
+        <v>10.2173738479614</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629409790039</v>
+        <v>9.16629314422607</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93417930603027</v>
+        <v>8.93418025970459</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862350463867</v>
+        <v>9.60862255096436</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804706573486</v>
+        <v>9.04804611206055</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652191162109</v>
+        <v>8.53652095794678</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.37010097503662</v>
+        <v>8.3701000213623</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740249633789</v>
+        <v>8.17740345001221</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813564300537</v>
+        <v>7.91813611984253</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441318511963</v>
+        <v>7.94441270828247</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813968658447</v>
+        <v>7.67813873291016</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.044264793396</v>
+        <v>8.04426574707031</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274059295654</v>
+        <v>7.53274011611938</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806346893311</v>
+        <v>7.84806394577026</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398109436035</v>
+        <v>7.52398061752319</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498962402344</v>
+        <v>8.50498867034912</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282869338989</v>
+        <v>6.40282917022705</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449819564819</v>
+        <v>7.05449867248535</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500911712646</v>
+        <v>7.06500959396362</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055969238281</v>
+        <v>6.87055921554565</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668622970581</v>
+        <v>7.23668575286865</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916723251343</v>
+        <v>7.21916770935059</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419713973999</v>
+        <v>7.73419666290283</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923274993896</v>
+        <v>7.76923322677612</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.70091247558594</v>
+        <v>7.7009129524231</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098417282104</v>
+        <v>7.77098512649536</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791650772095</v>
+        <v>7.94791698455811</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222610473633</v>
+        <v>7.76222658157349</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376100540161</v>
+        <v>7.55376148223877</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.4661717414856</v>
+        <v>7.46617126464844</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267150878906</v>
+        <v>7.22267198562622</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.3347864151001</v>
+        <v>7.33478593826294</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18238019943237</v>
+        <v>7.18237972259521</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755254745483</v>
+        <v>7.83755302429199</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908935546875</v>
+        <v>7.62908887863159</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784837722778</v>
+        <v>7.63784790039062</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.7464599609375</v>
+        <v>7.74645948410034</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412496566772</v>
+        <v>7.66412544250488</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157487869263</v>
+        <v>7.37157440185547</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.56952810287476</v>
+        <v>7.5695276260376</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230445861816</v>
+        <v>7.35230493545532</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675745010376</v>
+        <v>7.30675792694092</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456371307373</v>
+        <v>7.60456418991089</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142339706421</v>
+        <v>7.71142387390137</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.5169734954834</v>
+        <v>7.51697397232056</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755611419678</v>
+        <v>7.59755659103394</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047777175903</v>
+        <v>7.52047729492188</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448892593384</v>
+        <v>7.77448844909668</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711380004883</v>
+        <v>7.89711427688599</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.674635887146</v>
+        <v>7.67463541030884</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81477975845337</v>
+        <v>7.81478023529053</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.64660692214966</v>
+        <v>7.6466064453125</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981893539429</v>
+        <v>7.60981941223145</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952453613281</v>
+        <v>7.80952501296997</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602382659912</v>
+        <v>7.56602430343628</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427192687988</v>
+        <v>7.56427240371704</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945592880249</v>
+        <v>7.49945640563965</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500650405884</v>
+        <v>7.30500602722168</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.3610634803772</v>
+        <v>7.36106443405151</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.40836238861084</v>
+        <v>7.408362865448</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587995529175</v>
+        <v>7.42587947845459</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617792129517</v>
+        <v>6.98617839813232</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129283905029</v>
+        <v>6.61129331588745</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881135940552</v>
+        <v>6.62881088256836</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76369953155518</v>
+        <v>6.76370000839233</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997659683228</v>
+        <v>6.78997707366943</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632535934448</v>
+        <v>6.88632583618164</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355209350586</v>
+        <v>6.86355257034302</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997303009033</v>
+        <v>7.02997350692749</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.12106704711914</v>
+        <v>7.1210675239563</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.6220817565918</v>
+        <v>7.62208127975464</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011381149292</v>
+        <v>7.41011428833008</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252359390259</v>
+        <v>7.32252407073975</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055255889893</v>
+        <v>7.35055303573608</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953428268433</v>
+        <v>7.08953475952148</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092674255371</v>
+        <v>6.74092626571655</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107370376587</v>
+        <v>6.64107322692871</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414232254028</v>
+        <v>6.46414184570312</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698728561401</v>
+        <v>6.55698776245117</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961715698242</v>
+        <v>6.43961668014526</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662023544312</v>
+        <v>6.68662071228027</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713163375854</v>
+        <v>6.69713115692139</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450580596924</v>
+        <v>6.57450532913208</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501625061035</v>
+        <v>6.58501672744751</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143766403198</v>
+        <v>6.75143718719482</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.5201997756958</v>
+        <v>6.52019929885864</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815608978271</v>
+        <v>6.47815656661987</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020286560059</v>
+        <v>6.28020334243774</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502290725708</v>
+        <v>6.10502243041992</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260646820068</v>
+        <v>6.67260599136353</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224298477173</v>
+        <v>6.56224250793457</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.70939350128174</v>
+        <v>6.7093939781189</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932228088379</v>
+        <v>6.63932180404663</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070713043213</v>
+        <v>6.77070665359497</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.17509508132935</v>
+        <v>6.1750955581665</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203002929688</v>
+        <v>6.11203050613403</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.15407371520996</v>
+        <v>6.1540732383728</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.81597566604614</v>
+        <v>5.8159761428833</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313070297241</v>
+        <v>5.72313022613525</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210886001587</v>
+        <v>5.70210933685303</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896902084351</v>
+        <v>5.80896854400635</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466608047485</v>
+        <v>5.51466655731201</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474229812622</v>
+        <v>5.34474182128906</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496452331543</v>
+        <v>5.07496500015259</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.8314642906189</v>
+        <v>4.83146381378174</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423755645752</v>
+        <v>4.85423803329468</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642511367798</v>
+        <v>5.03642463684082</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.63203716278076</v>
+        <v>5.6320366859436</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066253662109</v>
+        <v>4.78066205978394</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912668228149</v>
+        <v>4.98912620544434</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867723464966</v>
+        <v>5.76867771148682</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626388549805</v>
+        <v>6.09626436233521</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458463668823</v>
+        <v>6.16458415985107</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268529891968</v>
+        <v>6.26268482208252</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523538589478</v>
+        <v>6.55523586273193</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640419006348</v>
+        <v>6.47640466690063</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034721374512</v>
+        <v>6.42034673690796</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947233200073</v>
+        <v>6.29947280883789</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078952789307</v>
+        <v>6.12078905105591</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589683532715</v>
+        <v>6.22589731216431</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779260635376</v>
+        <v>6.36779308319092</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385410308838</v>
+        <v>6.18385362625122</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516677856445</v>
+        <v>6.24516725540161</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.90006256103516</v>
+        <v>5.900062084198</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583227157593</v>
+        <v>5.67583179473877</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670976638794</v>
+        <v>5.55670928955078</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415515899658</v>
+        <v>5.50415563583374</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569458007812</v>
+        <v>5.05569505691528</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868793487549</v>
+        <v>5.04868745803833</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116941452026</v>
+        <v>5.03116989135742</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920146942139</v>
+        <v>4.81920194625854</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686742782593</v>
+        <v>4.73686695098877</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.93482065200806</v>
+        <v>4.9348201751709</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102602005005</v>
+        <v>4.89102554321289</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320953369141</v>
+        <v>5.31320905685425</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919124603271</v>
+        <v>5.53919172286987</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145763397217</v>
+        <v>5.31145811080933</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.3990478515625</v>
+        <v>5.39904737472534</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.13802909851074</v>
+        <v>5.1380295753479</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.95584201812744</v>
+        <v>4.9558424949646</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766561508179</v>
+        <v>5.02766609191895</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795740127563</v>
+        <v>5.06795692443848</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927007675171</v>
+        <v>5.12927055358887</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678859710693</v>
+        <v>5.14678812026978</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707990646362</v>
+        <v>5.18707942962646</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248565673828</v>
+        <v>4.85248613357544</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.09248304367065</v>
+        <v>5.0924825668335</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.42357301712036</v>
+        <v>5.4235725402832</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.4778790473938</v>
+        <v>5.47787857055664</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488569259644</v>
+        <v>5.48488616943359</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174537658691</v>
+        <v>5.59174585342407</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693199157715</v>
+        <v>5.28693246841431</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941751480103</v>
+        <v>5.02941799163818</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423398971558</v>
+        <v>5.09423446655273</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.13627767562866</v>
+        <v>5.1362771987915</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.22211599349976</v>
+        <v>5.2221155166626</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189590454102</v>
+        <v>5.25189638137817</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.1905837059021</v>
+        <v>5.19058322906494</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613332748413</v>
+        <v>4.99613380432129</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350749969482</v>
+        <v>4.87350797653198</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569862365723</v>
+        <v>4.81569814682007</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657564163208</v>
+        <v>4.69657611846924</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314401626587</v>
+        <v>4.76314449310303</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.9821195602417</v>
+        <v>4.98211908340454</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649681091309</v>
+        <v>5.10649728775024</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416276931763</v>
+        <v>5.02416229248047</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628076553345</v>
+        <v>4.89628124237061</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088119506836</v>
+        <v>4.75088167190552</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803623199463</v>
+        <v>4.65803575515747</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.5967230796814</v>
+        <v>4.59672355651855</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979122161865</v>
+        <v>4.41979169845581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.1176061630249</v>
+        <v>4.11760568618774</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008562088013</v>
+        <v>4.22008609771729</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826095581055</v>
+        <v>4.26826047897339</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.3094277381897</v>
+        <v>4.30942821502686</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030523300171</v>
+        <v>4.19030570983887</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.19731283187866</v>
+        <v>4.1973123550415</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359477043152</v>
+        <v>3.86359453201294</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958028793335</v>
+        <v>3.84958052635193</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147403717041</v>
+        <v>4.11147451400757</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118118286133</v>
+        <v>4.19118165969849</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789901733398</v>
+        <v>4.03789949417114</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556295394897</v>
+        <v>4.07556247711182</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.432053565979</v>
+        <v>4.43205404281616</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.491614818573</v>
+        <v>4.49161529541016</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110485076904</v>
+        <v>4.48110437393188</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592084884644</v>
+        <v>4.54592132568359</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59119009971619</v>
+        <v>3.59118986129761</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512884140015</v>
+        <v>3.77512907981873</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.7033052444458</v>
+        <v>3.70330548286438</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746205329895</v>
+        <v>3.97746181488037</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819187164307</v>
+        <v>3.95819234848022</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483289718628</v>
+        <v>4.09483242034912</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.5056300163269</v>
+        <v>4.50562953948975</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504335403442</v>
+        <v>4.66504383087158</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358324050903</v>
+        <v>4.70358276367188</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365446090698</v>
+        <v>4.77365493774414</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387407302856</v>
+        <v>4.74387454986572</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -49902,6 +49902,32 @@
         <v>4.30100011825562</v>
       </c>
       <c r="H1905" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1906" t="n">
+        <v>8002561</v>
+      </c>
+      <c r="C1906" t="n">
+        <v>4.43699979782104</v>
+      </c>
+      <c r="D1906" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="E1906" t="n">
+        <v>4.34299993515015</v>
+      </c>
+      <c r="F1906" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="G1906" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="H1906" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35755968093872</v>
+        <v>7.35756015777588</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.46354389190674</v>
+        <v>7.4635443687439</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0404839515686</v>
+        <v>7.04048442840576</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.19551849365234</v>
+        <v>7.1955189704895</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.36631870269775</v>
+        <v>7.3663182258606</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65098571777344</v>
+        <v>7.6509861946106</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047325134277</v>
+        <v>7.76047372817993</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638624191284</v>
+        <v>7.79638576507568</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813718795776</v>
+        <v>7.79813766479492</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62032985687256</v>
+        <v>7.6203293800354</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675174713135</v>
+        <v>7.78675127029419</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214775085449</v>
+        <v>8.17214679718018</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521339416504</v>
+        <v>8.11521434783936</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287887573242</v>
+        <v>8.03287792205811</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.1160888671875</v>
+        <v>8.11608982086182</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295307159424</v>
+        <v>7.98295259475708</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718954086304</v>
+        <v>7.72718906402588</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.82091093063354</v>
+        <v>7.8209114074707</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010763168335</v>
+        <v>7.89010715484619</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528961181641</v>
+        <v>7.94528913497925</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00484943389893</v>
+        <v>8.00485038757324</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9838285446167</v>
+        <v>7.98382806777954</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907913208008</v>
+        <v>8.34907817840576</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5032377243042</v>
+        <v>8.50323677062988</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411426544189</v>
+        <v>8.38411521911621</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732723236084</v>
+        <v>8.34732627868652</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39375019073486</v>
+        <v>8.39374923706055</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644866943359</v>
+        <v>8.58644771575928</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703330993652</v>
+        <v>8.54703235626221</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535358428955</v>
+        <v>8.61535263061523</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40864086151123</v>
+        <v>8.40863990783691</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206737518311</v>
+        <v>8.70206642150879</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330680847168</v>
+        <v>8.81330585479736</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790580749512</v>
+        <v>8.66790676116943</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.69330787658691</v>
+        <v>8.6933069229126</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.7046947479248</v>
+        <v>8.70469379425049</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856868743896</v>
+        <v>8.33856773376465</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827796936035</v>
+        <v>8.17827892303467</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294498443604</v>
+        <v>8.46294593811035</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207557678223</v>
+        <v>8.10207462310791</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944416046143</v>
+        <v>8.33944320678711</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973796844482</v>
+        <v>8.25973701477051</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.47871208190918</v>
+        <v>8.4787130355835</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995555877686</v>
+        <v>8.34995460510254</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470092773438</v>
+        <v>8.22470188140869</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207260131836</v>
+        <v>8.22207355499268</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688087463379</v>
+        <v>8.88688182830811</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184169769287</v>
+        <v>9.09184265136719</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05155086517334</v>
+        <v>9.05154991149902</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.6348991394043</v>
+        <v>9.63490009307861</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429214477539</v>
+        <v>10.1429224014282</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256153106689</v>
+        <v>9.79256248474121</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409881591797</v>
+        <v>9.58409786224365</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235050201416</v>
+        <v>10.2235040664673</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754684448242</v>
+        <v>10.6754693984985</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471460342407</v>
+        <v>10.8471450805664</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141557693481</v>
+        <v>10.6141567230225</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224729537964</v>
+        <v>10.9224739074707</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027616500854</v>
+        <v>11.2027606964111</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652364730835</v>
+        <v>11.6652355194092</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793991088867</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422815322876</v>
+        <v>14.1422805786133</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5273990631104</v>
+        <v>13.5274000167847</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789394378662</v>
+        <v>13.0789384841919</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718181610107</v>
+        <v>10.7718191146851</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716648101807</v>
+        <v>9.40716552734375</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651054382324</v>
+        <v>10.5651063919067</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632061004639</v>
+        <v>10.6632070541382</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788940429688</v>
+        <v>9.86788845062256</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743072509766</v>
+        <v>10.2743062973022</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779502868652</v>
+        <v>10.7779493331909</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421770095825</v>
+        <v>11.2421760559082</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.3648023605347</v>
+        <v>11.364803314209</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969161987305</v>
+        <v>11.5969152450562</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064037322998</v>
+        <v>11.7064027786255</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.41588306427</v>
+        <v>12.4158821105957</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.109317779541</v>
+        <v>12.1093168258667</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925359725952</v>
+        <v>11.5925369262695</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961790084839</v>
+        <v>12.0961799621582</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.437780380249</v>
+        <v>12.4377794265747</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633197784424</v>
+        <v>12.9633207321167</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297325134277</v>
+        <v>13.7297334671021</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027433395386</v>
+        <v>12.4027442932129</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421504974365</v>
+        <v>13.0421514511108</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173309326172</v>
+        <v>13.2173318862915</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0844717025757</v>
+        <v>14.08447265625</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676826477051</v>
+        <v>14.1676816940308</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830238342285</v>
+        <v>13.2830228805542</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640478134155</v>
+        <v>13.0640487670898</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3092994689941</v>
+        <v>13.3093004226685</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.347240447998</v>
+        <v>14.3472414016724</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589159011841</v>
+        <v>14.7589149475098</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129251480103</v>
+        <v>15.0129261016846</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326374053955</v>
+        <v>14.7326364517212</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.8070907592773</v>
+        <v>14.807089805603</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.828987121582</v>
+        <v>14.8289880752563</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.271315574646</v>
+        <v>15.2713165283203</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720701217651</v>
+        <v>13.5720710754395</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195251464844</v>
+        <v>12.9195241928101</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268194198608</v>
+        <v>13.3268184661865</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866659164429</v>
+        <v>13.7866649627686</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457853317261</v>
+        <v>14.1457843780518</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647603988647</v>
+        <v>14.3647594451904</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.887393951416</v>
+        <v>13.8873949050903</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348489761353</v>
+        <v>13.2348480224609</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925113677979</v>
+        <v>13.3925104141235</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122226715088</v>
+        <v>13.1122236251831</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027351379395</v>
+        <v>13.0027360916138</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450727462769</v>
+        <v>12.8450736999512</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516380310059</v>
+        <v>13.1516389846802</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.7662420272827</v>
+        <v>12.766242980957</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202531814575</v>
+        <v>13.0202541351318</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049211502075</v>
+        <v>13.3049201965332</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260904312134</v>
+        <v>13.2260894775391</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.4275465011597</v>
+        <v>13.427547454834</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005336761475</v>
+        <v>13.9005327224731</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618381500244</v>
+        <v>14.5618371963501</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465061187744</v>
+        <v>14.8465051651001</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3223972320557</v>
+        <v>16.322395324707</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056053161621</v>
+        <v>16.4056072235107</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968395233154</v>
+        <v>16.9968414306641</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.475679397583</v>
+        <v>16.4756774902344</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588975906372</v>
+        <v>15.9588966369629</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348142623901</v>
+        <v>15.6348161697388</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640068054199</v>
+        <v>16.0640048980713</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793315887451</v>
+        <v>16.3793296813965</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362712860107</v>
+        <v>15.8362722396851</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.8625497817993</v>
+        <v>15.862548828125</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034303665161</v>
+        <v>15.5034313201904</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581787109375</v>
+        <v>15.2581777572632</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756967544556</v>
+        <v>15.2756958007812</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662082672119</v>
+        <v>15.1662092208862</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771518707275</v>
+        <v>15.4771528244019</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552555084229</v>
+        <v>15.4552564620972</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443017959595</v>
+        <v>15.7443027496338</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.884446144104</v>
+        <v>15.8844470977783</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304340362549</v>
+        <v>15.6304349899292</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.6435747146606</v>
+        <v>15.643575668335</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275136947632</v>
+        <v>15.8275127410889</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676570892334</v>
+        <v>15.9676561355591</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.46839427948</v>
+        <v>15.4683933258057</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413887023926</v>
+        <v>15.3413877487183</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.354528427124</v>
+        <v>15.3545274734497</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421340942383</v>
+        <v>14.2421350479126</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684024810791</v>
+        <v>14.8684034347534</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501462936401</v>
+        <v>15.3501472473145</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.424599647522</v>
+        <v>15.4246006011963</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056573867798</v>
+        <v>12.8056583404541</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355852127075</v>
+        <v>12.7355861663818</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326629638672</v>
+        <v>12.9326639175415</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.814416885376</v>
+        <v>12.8144178390503</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574825286865</v>
+        <v>12.7574834823608</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224565505981</v>
+        <v>12.1224555969238</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.245080947876</v>
+        <v>12.2450819015503</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.021728515625</v>
+        <v>12.0217275619507</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830411911011</v>
+        <v>12.0830402374268</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282928466797</v>
+        <v>12.3282918930054</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.223183631897</v>
+        <v>12.2231845855713</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.868444442749</v>
+        <v>11.8684453964233</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618719100952</v>
+        <v>12.1618709564209</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764677047729</v>
+        <v>12.3764667510986</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385074615479</v>
+        <v>12.5385084152222</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553066253662</v>
+        <v>11.8553056716919</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407108306885</v>
+        <v>11.6407117843628</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516563415527</v>
+        <v>11.9516553878784</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472761154175</v>
+        <v>11.9472770690918</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348745346069</v>
+        <v>11.4348754882812</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370687484741</v>
+        <v>11.1370677947998</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786773681641</v>
+        <v>10.8786783218384</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173728942871</v>
+        <v>10.2173738479614</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629409790039</v>
+        <v>9.16629314422607</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93417930603027</v>
+        <v>8.93418025970459</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862350463867</v>
+        <v>9.60862255096436</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804706573486</v>
+        <v>9.04804611206055</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652191162109</v>
+        <v>8.53652095794678</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.37010097503662</v>
+        <v>8.3701000213623</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740249633789</v>
+        <v>8.17740345001221</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813564300537</v>
+        <v>7.91813611984253</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441318511963</v>
+        <v>7.94441270828247</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813968658447</v>
+        <v>7.67813873291016</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.044264793396</v>
+        <v>8.04426574707031</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274059295654</v>
+        <v>7.53274011611938</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806346893311</v>
+        <v>7.84806394577026</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398109436035</v>
+        <v>7.52398061752319</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498962402344</v>
+        <v>8.50498867034912</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282869338989</v>
+        <v>6.40282917022705</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449819564819</v>
+        <v>7.05449867248535</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500911712646</v>
+        <v>7.06500959396362</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055969238281</v>
+        <v>6.87055921554565</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668622970581</v>
+        <v>7.23668575286865</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916723251343</v>
+        <v>7.21916770935059</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419713973999</v>
+        <v>7.73419666290283</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923274993896</v>
+        <v>7.76923322677612</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.70091247558594</v>
+        <v>7.7009129524231</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098417282104</v>
+        <v>7.77098512649536</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791650772095</v>
+        <v>7.94791698455811</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222610473633</v>
+        <v>7.76222658157349</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376100540161</v>
+        <v>7.55376148223877</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.4661717414856</v>
+        <v>7.46617126464844</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267150878906</v>
+        <v>7.22267198562622</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.3347864151001</v>
+        <v>7.33478593826294</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18238019943237</v>
+        <v>7.18237972259521</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755254745483</v>
+        <v>7.83755302429199</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908935546875</v>
+        <v>7.62908887863159</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784837722778</v>
+        <v>7.63784790039062</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.7464599609375</v>
+        <v>7.74645948410034</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412496566772</v>
+        <v>7.66412544250488</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157487869263</v>
+        <v>7.37157440185547</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.56952810287476</v>
+        <v>7.5695276260376</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230445861816</v>
+        <v>7.35230493545532</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675745010376</v>
+        <v>7.30675792694092</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456371307373</v>
+        <v>7.60456418991089</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142339706421</v>
+        <v>7.71142387390137</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.5169734954834</v>
+        <v>7.51697397232056</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755611419678</v>
+        <v>7.59755659103394</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047777175903</v>
+        <v>7.52047729492188</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448892593384</v>
+        <v>7.77448844909668</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711380004883</v>
+        <v>7.89711427688599</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.674635887146</v>
+        <v>7.67463541030884</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81477975845337</v>
+        <v>7.81478023529053</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.64660692214966</v>
+        <v>7.6466064453125</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981893539429</v>
+        <v>7.60981941223145</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952453613281</v>
+        <v>7.80952501296997</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602382659912</v>
+        <v>7.56602430343628</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427192687988</v>
+        <v>7.56427240371704</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945592880249</v>
+        <v>7.49945640563965</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500650405884</v>
+        <v>7.30500602722168</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.3610634803772</v>
+        <v>7.36106443405151</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.40836238861084</v>
+        <v>7.408362865448</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587995529175</v>
+        <v>7.42587947845459</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617792129517</v>
+        <v>6.98617839813232</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129283905029</v>
+        <v>6.61129331588745</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881135940552</v>
+        <v>6.62881088256836</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76369953155518</v>
+        <v>6.76370000839233</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997659683228</v>
+        <v>6.78997707366943</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632535934448</v>
+        <v>6.88632583618164</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355209350586</v>
+        <v>6.86355257034302</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997303009033</v>
+        <v>7.02997350692749</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.12106704711914</v>
+        <v>7.1210675239563</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.6220817565918</v>
+        <v>7.62208127975464</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011381149292</v>
+        <v>7.41011428833008</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252359390259</v>
+        <v>7.32252407073975</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055255889893</v>
+        <v>7.35055303573608</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953428268433</v>
+        <v>7.08953475952148</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092674255371</v>
+        <v>6.74092626571655</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107370376587</v>
+        <v>6.64107322692871</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414232254028</v>
+        <v>6.46414184570312</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698728561401</v>
+        <v>6.55698776245117</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961715698242</v>
+        <v>6.43961668014526</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662023544312</v>
+        <v>6.68662071228027</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713163375854</v>
+        <v>6.69713115692139</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450580596924</v>
+        <v>6.57450532913208</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501625061035</v>
+        <v>6.58501672744751</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143766403198</v>
+        <v>6.75143718719482</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.5201997756958</v>
+        <v>6.52019929885864</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815608978271</v>
+        <v>6.47815656661987</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020286560059</v>
+        <v>6.28020334243774</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502290725708</v>
+        <v>6.10502243041992</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260646820068</v>
+        <v>6.67260599136353</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224298477173</v>
+        <v>6.56224250793457</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.70939350128174</v>
+        <v>6.7093939781189</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932228088379</v>
+        <v>6.63932180404663</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070713043213</v>
+        <v>6.77070665359497</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.17509508132935</v>
+        <v>6.1750955581665</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203002929688</v>
+        <v>6.11203050613403</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.15407371520996</v>
+        <v>6.1540732383728</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.81597566604614</v>
+        <v>5.8159761428833</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313070297241</v>
+        <v>5.72313022613525</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210886001587</v>
+        <v>5.70210933685303</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896902084351</v>
+        <v>5.80896854400635</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466608047485</v>
+        <v>5.51466655731201</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474229812622</v>
+        <v>5.34474182128906</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496452331543</v>
+        <v>5.07496500015259</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.8314642906189</v>
+        <v>4.83146381378174</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423755645752</v>
+        <v>4.85423803329468</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642511367798</v>
+        <v>5.03642463684082</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.63203716278076</v>
+        <v>5.6320366859436</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066253662109</v>
+        <v>4.78066205978394</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912668228149</v>
+        <v>4.98912620544434</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867723464966</v>
+        <v>5.76867771148682</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626388549805</v>
+        <v>6.09626436233521</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458463668823</v>
+        <v>6.16458415985107</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268529891968</v>
+        <v>6.26268482208252</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523538589478</v>
+        <v>6.55523586273193</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640419006348</v>
+        <v>6.47640466690063</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034721374512</v>
+        <v>6.42034673690796</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947233200073</v>
+        <v>6.29947280883789</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078952789307</v>
+        <v>6.12078905105591</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589683532715</v>
+        <v>6.22589731216431</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779260635376</v>
+        <v>6.36779308319092</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385410308838</v>
+        <v>6.18385362625122</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516677856445</v>
+        <v>6.24516725540161</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.90006256103516</v>
+        <v>5.900062084198</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583227157593</v>
+        <v>5.67583179473877</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670976638794</v>
+        <v>5.55670928955078</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415515899658</v>
+        <v>5.50415563583374</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569458007812</v>
+        <v>5.05569505691528</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868793487549</v>
+        <v>5.04868745803833</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116941452026</v>
+        <v>5.03116989135742</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920146942139</v>
+        <v>4.81920194625854</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686742782593</v>
+        <v>4.73686695098877</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.93482065200806</v>
+        <v>4.9348201751709</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102602005005</v>
+        <v>4.89102554321289</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320953369141</v>
+        <v>5.31320905685425</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919124603271</v>
+        <v>5.53919172286987</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145763397217</v>
+        <v>5.31145811080933</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.3990478515625</v>
+        <v>5.39904737472534</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.13802909851074</v>
+        <v>5.1380295753479</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.95584201812744</v>
+        <v>4.9558424949646</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766561508179</v>
+        <v>5.02766609191895</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795740127563</v>
+        <v>5.06795692443848</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927007675171</v>
+        <v>5.12927055358887</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678859710693</v>
+        <v>5.14678812026978</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707990646362</v>
+        <v>5.18707942962646</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248565673828</v>
+        <v>4.85248613357544</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.09248304367065</v>
+        <v>5.0924825668335</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.42357301712036</v>
+        <v>5.4235725402832</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.4778790473938</v>
+        <v>5.47787857055664</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488569259644</v>
+        <v>5.48488616943359</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174537658691</v>
+        <v>5.59174585342407</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693199157715</v>
+        <v>5.28693246841431</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941751480103</v>
+        <v>5.02941799163818</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423398971558</v>
+        <v>5.09423446655273</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.13627767562866</v>
+        <v>5.1362771987915</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.22211599349976</v>
+        <v>5.2221155166626</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189590454102</v>
+        <v>5.25189638137817</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.1905837059021</v>
+        <v>5.19058322906494</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613332748413</v>
+        <v>4.99613380432129</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350749969482</v>
+        <v>4.87350797653198</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569862365723</v>
+        <v>4.81569814682007</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657564163208</v>
+        <v>4.69657611846924</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314401626587</v>
+        <v>4.76314449310303</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.9821195602417</v>
+        <v>4.98211908340454</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649681091309</v>
+        <v>5.10649728775024</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416276931763</v>
+        <v>5.02416229248047</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628076553345</v>
+        <v>4.89628124237061</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088119506836</v>
+        <v>4.75088167190552</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803623199463</v>
+        <v>4.65803575515747</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.5967230796814</v>
+        <v>4.59672355651855</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979122161865</v>
+        <v>4.41979169845581</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.1176061630249</v>
+        <v>4.11760568618774</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008562088013</v>
+        <v>4.22008609771729</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826095581055</v>
+        <v>4.26826047897339</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.3094277381897</v>
+        <v>4.30942821502686</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030523300171</v>
+        <v>4.19030570983887</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.19731283187866</v>
+        <v>4.1973123550415</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359477043152</v>
+        <v>3.86359453201294</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958028793335</v>
+        <v>3.84958052635193</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147403717041</v>
+        <v>4.11147451400757</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118118286133</v>
+        <v>4.19118165969849</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789901733398</v>
+        <v>4.03789949417114</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556295394897</v>
+        <v>4.07556247711182</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.432053565979</v>
+        <v>4.43205404281616</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.491614818573</v>
+        <v>4.49161529541016</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110485076904</v>
+        <v>4.48110437393188</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592084884644</v>
+        <v>4.54592132568359</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59119009971619</v>
+        <v>3.59118986129761</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512884140015</v>
+        <v>3.77512907981873</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.7033052444458</v>
+        <v>3.70330548286438</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746205329895</v>
+        <v>3.97746181488037</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819187164307</v>
+        <v>3.95819234848022</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483289718628</v>
+        <v>4.09483242034912</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.5056300163269</v>
+        <v>4.50562953948975</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504335403442</v>
+        <v>4.66504383087158</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358324050903</v>
+        <v>4.70358276367188</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365446090698</v>
+        <v>4.77365493774414</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387407302856</v>
+        <v>4.74387454986572</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55649,6 +55649,64 @@
         <v>8002561</v>
       </c>
       <c r="I1906" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1907" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1907" t="n">
+        <v>4.39400005340576</v>
+      </c>
+      <c r="D1907" t="n">
+        <v>4.4210000038147</v>
+      </c>
+      <c r="E1907" t="n">
+        <v>4.30200004577637</v>
+      </c>
+      <c r="F1907" t="n">
+        <v>4.41699981689453</v>
+      </c>
+      <c r="G1907" t="n">
+        <v>4.41699981689453</v>
+      </c>
+      <c r="H1907" t="n">
+        <v>4887216</v>
+      </c>
+      <c r="I1907" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1908" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1908" t="n">
+        <v>4.41499996185303</v>
+      </c>
+      <c r="D1908" t="n">
+        <v>4.45599985122681</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>4.39699983596802</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>4.41200017929077</v>
+      </c>
+      <c r="G1908" t="n">
+        <v>4.41200017929077</v>
+      </c>
+      <c r="H1908" t="n">
+        <v>6029110</v>
+      </c>
+      <c r="I1908" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55707,6 +55707,35 @@
         <v>6029110</v>
       </c>
       <c r="I1908" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1909" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1909" t="n">
+        <v>4.37400007247925</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>4.29400014877319</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="G1909" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="H1909" t="n">
+        <v>5437280</v>
+      </c>
+      <c r="I1909" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35755968093872</v>
+        <v>7.35756015777588</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.46354389190674</v>
+        <v>7.4635443687439</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0404839515686</v>
+        <v>7.04048442840576</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.19551849365234</v>
+        <v>7.1955189704895</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.36631870269775</v>
+        <v>7.3663182258606</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65098571777344</v>
+        <v>7.6509861946106</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047325134277</v>
+        <v>7.76047372817993</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638624191284</v>
+        <v>7.79638576507568</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813718795776</v>
+        <v>7.79813766479492</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62032985687256</v>
+        <v>7.6203293800354</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675174713135</v>
+        <v>7.78675127029419</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214775085449</v>
+        <v>8.17214679718018</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521339416504</v>
+        <v>8.11521434783936</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287887573242</v>
+        <v>8.03287792205811</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.1160888671875</v>
+        <v>8.11608982086182</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295307159424</v>
+        <v>7.98295259475708</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718954086304</v>
+        <v>7.72718906402588</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.82091093063354</v>
+        <v>7.8209114074707</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010763168335</v>
+        <v>7.89010715484619</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528961181641</v>
+        <v>7.94528913497925</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00484943389893</v>
+        <v>8.00485038757324</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9838285446167</v>
+        <v>7.98382806777954</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907913208008</v>
+        <v>8.34907817840576</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5032377243042</v>
+        <v>8.50323677062988</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411426544189</v>
+        <v>8.38411521911621</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732723236084</v>
+        <v>8.34732627868652</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39375019073486</v>
+        <v>8.39374923706055</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644866943359</v>
+        <v>8.58644771575928</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703330993652</v>
+        <v>8.54703235626221</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535358428955</v>
+        <v>8.61535263061523</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40864086151123</v>
+        <v>8.40863990783691</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206737518311</v>
+        <v>8.70206642150879</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330680847168</v>
+        <v>8.81330585479736</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790580749512</v>
+        <v>8.66790676116943</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.69330787658691</v>
+        <v>8.6933069229126</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.7046947479248</v>
+        <v>8.70469379425049</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856868743896</v>
+        <v>8.33856773376465</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827796936035</v>
+        <v>8.17827892303467</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294498443604</v>
+        <v>8.46294593811035</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207557678223</v>
+        <v>8.10207462310791</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944416046143</v>
+        <v>8.33944320678711</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973796844482</v>
+        <v>8.25973701477051</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.47871208190918</v>
+        <v>8.4787130355835</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995555877686</v>
+        <v>8.34995460510254</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470092773438</v>
+        <v>8.22470188140869</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207260131836</v>
+        <v>8.22207355499268</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688087463379</v>
+        <v>8.88688182830811</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184169769287</v>
+        <v>9.09184265136719</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05155086517334</v>
+        <v>9.05154991149902</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.6348991394043</v>
+        <v>9.63490009307861</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429214477539</v>
+        <v>10.1429224014282</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256153106689</v>
+        <v>9.79256248474121</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409881591797</v>
+        <v>9.58409786224365</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235050201416</v>
+        <v>10.2235040664673</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754684448242</v>
+        <v>10.6754693984985</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471460342407</v>
+        <v>10.8471450805664</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141557693481</v>
+        <v>10.6141567230225</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224729537964</v>
+        <v>10.9224739074707</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027616500854</v>
+        <v>11.2027606964111</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652364730835</v>
+        <v>11.6652355194092</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793991088867</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422815322876</v>
+        <v>14.1422805786133</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5273990631104</v>
+        <v>13.5274000167847</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789394378662</v>
+        <v>13.0789384841919</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718181610107</v>
+        <v>10.7718191146851</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716648101807</v>
+        <v>9.40716552734375</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651054382324</v>
+        <v>10.5651063919067</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632061004639</v>
+        <v>10.6632070541382</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788940429688</v>
+        <v>9.86788845062256</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743072509766</v>
+        <v>10.2743062973022</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779502868652</v>
+        <v>10.7779493331909</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421770095825</v>
+        <v>11.2421760559082</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.3648023605347</v>
+        <v>11.364803314209</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969161987305</v>
+        <v>11.5969152450562</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064037322998</v>
+        <v>11.7064027786255</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.41588306427</v>
+        <v>12.4158821105957</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.109317779541</v>
+        <v>12.1093168258667</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925359725952</v>
+        <v>11.5925369262695</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961790084839</v>
+        <v>12.0961799621582</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.437780380249</v>
+        <v>12.4377794265747</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633197784424</v>
+        <v>12.9633207321167</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297325134277</v>
+        <v>13.7297334671021</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027433395386</v>
+        <v>12.4027442932129</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421504974365</v>
+        <v>13.0421514511108</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173309326172</v>
+        <v>13.2173318862915</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0844717025757</v>
+        <v>14.08447265625</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676826477051</v>
+        <v>14.1676816940308</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830238342285</v>
+        <v>13.2830228805542</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640478134155</v>
+        <v>13.0640487670898</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3092994689941</v>
+        <v>13.3093004226685</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.347240447998</v>
+        <v>14.3472414016724</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589159011841</v>
+        <v>14.7589149475098</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129251480103</v>
+        <v>15.0129261016846</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326374053955</v>
+        <v>14.7326364517212</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.8070907592773</v>
+        <v>14.807089805603</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.828987121582</v>
+        <v>14.8289880752563</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.271315574646</v>
+        <v>15.2713165283203</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720701217651</v>
+        <v>13.5720710754395</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195251464844</v>
+        <v>12.9195241928101</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268194198608</v>
+        <v>13.3268184661865</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866659164429</v>
+        <v>13.7866649627686</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457853317261</v>
+        <v>14.1457843780518</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647603988647</v>
+        <v>14.3647594451904</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.887393951416</v>
+        <v>13.8873949050903</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348489761353</v>
+        <v>13.2348480224609</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925113677979</v>
+        <v>13.3925104141235</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122226715088</v>
+        <v>13.1122236251831</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027351379395</v>
+        <v>13.0027360916138</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450727462769</v>
+        <v>12.8450736999512</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516380310059</v>
+        <v>13.1516389846802</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.7662420272827</v>
+        <v>12.766242980957</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202531814575</v>
+        <v>13.0202541351318</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049211502075</v>
+        <v>13.3049201965332</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260904312134</v>
+        <v>13.2260894775391</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.4275465011597</v>
+        <v>13.427547454834</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005336761475</v>
+        <v>13.9005327224731</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618381500244</v>
+        <v>14.5618371963501</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465061187744</v>
+        <v>14.8465051651001</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3223972320557</v>
+        <v>16.322395324707</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056053161621</v>
+        <v>16.4056072235107</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968395233154</v>
+        <v>16.9968414306641</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.475679397583</v>
+        <v>16.4756774902344</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588975906372</v>
+        <v>15.9588966369629</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348142623901</v>
+        <v>15.6348161697388</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640068054199</v>
+        <v>16.0640048980713</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793315887451</v>
+        <v>16.3793296813965</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362712860107</v>
+        <v>15.8362722396851</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.8625497817993</v>
+        <v>15.862548828125</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034303665161</v>
+        <v>15.5034313201904</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581787109375</v>
+        <v>15.2581777572632</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756967544556</v>
+        <v>15.2756958007812</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662082672119</v>
+        <v>15.1662092208862</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771518707275</v>
+        <v>15.4771528244019</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552555084229</v>
+        <v>15.4552564620972</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443017959595</v>
+        <v>15.7443027496338</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.884446144104</v>
+        <v>15.8844470977783</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304340362549</v>
+        <v>15.6304349899292</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.6435747146606</v>
+        <v>15.643575668335</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275136947632</v>
+        <v>15.8275127410889</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676570892334</v>
+        <v>15.9676561355591</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.46839427948</v>
+        <v>15.4683933258057</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413887023926</v>
+        <v>15.3413877487183</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.354528427124</v>
+        <v>15.3545274734497</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421340942383</v>
+        <v>14.2421350479126</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684024810791</v>
+        <v>14.8684034347534</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501462936401</v>
+        <v>15.3501472473145</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.424599647522</v>
+        <v>15.4246006011963</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056573867798</v>
+        <v>12.8056583404541</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355852127075</v>
+        <v>12.7355861663818</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326629638672</v>
+        <v>12.9326639175415</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.814416885376</v>
+        <v>12.8144178390503</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574825286865</v>
+        <v>12.7574834823608</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224565505981</v>
+        <v>12.1224555969238</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.245080947876</v>
+        <v>12.2450819015503</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.021728515625</v>
+        <v>12.0217275619507</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830411911011</v>
+        <v>12.0830402374268</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282928466797</v>
+        <v>12.3282918930054</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.223183631897</v>
+        <v>12.2231845855713</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.868444442749</v>
+        <v>11.8684453964233</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618719100952</v>
+        <v>12.1618709564209</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764677047729</v>
+        <v>12.3764667510986</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385074615479</v>
+        <v>12.5385084152222</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553066253662</v>
+        <v>11.8553056716919</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407108306885</v>
+        <v>11.6407117843628</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516563415527</v>
+        <v>11.9516553878784</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472761154175</v>
+        <v>11.9472770690918</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348745346069</v>
+        <v>11.4348754882812</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370687484741</v>
+        <v>11.1370677947998</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786773681641</v>
+        <v>10.8786783218384</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173728942871</v>
+        <v>10.2173738479614</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629409790039</v>
+        <v>9.16629314422607</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93417930603027</v>
+        <v>8.93418025970459</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862350463867</v>
+        <v>9.60862255096436</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804706573486</v>
+        <v>9.04804611206055</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652191162109</v>
+        <v>8.53652095794678</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.37010097503662</v>
+        <v>8.3701000213623</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740249633789</v>
+        <v>8.17740345001221</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813564300537</v>
+        <v>7.91813611984253</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441318511963</v>
+        <v>7.94441270828247</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813968658447</v>
+        <v>7.67813873291016</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.044264793396</v>
+        <v>8.04426574707031</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274059295654</v>
+        <v>7.53274011611938</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806346893311</v>
+        <v>7.84806394577026</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398109436035</v>
+        <v>7.52398061752319</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498962402344</v>
+        <v>8.50498867034912</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282869338989</v>
+        <v>6.40282917022705</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449819564819</v>
+        <v>7.05449867248535</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500911712646</v>
+        <v>7.06500959396362</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055969238281</v>
+        <v>6.87055921554565</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668622970581</v>
+        <v>7.23668575286865</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916723251343</v>
+        <v>7.21916770935059</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419713973999</v>
+        <v>7.73419666290283</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923274993896</v>
+        <v>7.76923322677612</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.70091247558594</v>
+        <v>7.7009129524231</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098417282104</v>
+        <v>7.77098512649536</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791650772095</v>
+        <v>7.94791698455811</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222610473633</v>
+        <v>7.76222658157349</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376100540161</v>
+        <v>7.55376148223877</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.4661717414856</v>
+        <v>7.46617126464844</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267150878906</v>
+        <v>7.22267198562622</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.3347864151001</v>
+        <v>7.33478593826294</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18238019943237</v>
+        <v>7.18237972259521</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755254745483</v>
+        <v>7.83755302429199</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908935546875</v>
+        <v>7.62908887863159</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784837722778</v>
+        <v>7.63784790039062</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.7464599609375</v>
+        <v>7.74645948410034</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412496566772</v>
+        <v>7.66412544250488</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157487869263</v>
+        <v>7.37157440185547</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.56952810287476</v>
+        <v>7.5695276260376</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230445861816</v>
+        <v>7.35230493545532</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675745010376</v>
+        <v>7.30675792694092</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456371307373</v>
+        <v>7.60456418991089</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142339706421</v>
+        <v>7.71142387390137</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.5169734954834</v>
+        <v>7.51697397232056</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755611419678</v>
+        <v>7.59755659103394</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047777175903</v>
+        <v>7.52047729492188</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448892593384</v>
+        <v>7.77448844909668</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711380004883</v>
+        <v>7.89711427688599</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.674635887146</v>
+        <v>7.67463541030884</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81477975845337</v>
+        <v>7.81478023529053</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.64660692214966</v>
+        <v>7.6466064453125</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981893539429</v>
+        <v>7.60981941223145</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952453613281</v>
+        <v>7.80952501296997</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602382659912</v>
+        <v>7.56602430343628</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427192687988</v>
+        <v>7.56427240371704</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945592880249</v>
+        <v>7.49945640563965</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500650405884</v>
+        <v>7.30500602722168</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.3610634803772</v>
+        <v>7.36106443405151</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.40836238861084</v>
+        <v>7.408362865448</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587995529175</v>
+        <v>7.42587947845459</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617792129517</v>
+        <v>6.98617839813232</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129283905029</v>
+        <v>6.61129331588745</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881135940552</v>
+        <v>6.62881088256836</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76369953155518</v>
+        <v>6.76370000839233</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997659683228</v>
+        <v>6.78997707366943</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632535934448</v>
+        <v>6.88632583618164</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355209350586</v>
+        <v>6.86355257034302</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997303009033</v>
+        <v>7.02997350692749</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.12106704711914</v>
+        <v>7.1210675239563</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.6220817565918</v>
+        <v>7.62208127975464</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011381149292</v>
+        <v>7.41011428833008</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252359390259</v>
+        <v>7.32252407073975</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055255889893</v>
+        <v>7.35055303573608</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953428268433</v>
+        <v>7.08953475952148</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092674255371</v>
+        <v>6.74092626571655</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107370376587</v>
+        <v>6.64107322692871</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414232254028</v>
+        <v>6.46414184570312</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698728561401</v>
+        <v>6.55698776245117</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961715698242</v>
+        <v>6.43961668014526</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662023544312</v>
+        <v>6.68662071228027</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713163375854</v>
+        <v>6.69713115692139</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450580596924</v>
+        <v>6.57450532913208</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501625061035</v>
+        <v>6.58501672744751</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143766403198</v>
+        <v>6.75143718719482</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.5201997756958</v>
+        <v>6.52019929885864</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815608978271</v>
+        <v>6.47815656661987</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020286560059</v>
+        <v>6.28020334243774</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502290725708</v>
+        <v>6.10502243041992</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260646820068</v>
+        <v>6.67260599136353</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224298477173</v>
+        <v>6.56224250793457</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.70939350128174</v>
+        <v>6.7093939781189</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932228088379</v>
+        <v>6.63932180404663</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070713043213</v>
+        <v>6.77070665359497</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.17509508132935</v>
+        <v>6.1750955581665</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203002929688</v>
+        <v>6.11203050613403</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.15407371520996</v>
+        <v>6.1540732383728</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.81597566604614</v>
+        <v>5.8159761428833</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313070297241</v>
+        <v>5.72313022613525</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210886001587</v>
+        <v>5.70210933685303</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896902084351</v>
+        <v>5.80896854400635</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466608047485</v>
+        <v>5.51466655731201</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474229812622</v>
+        <v>5.34474182128906</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496452331543</v>
+        <v>5.07496500015259</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.8314642906189</v>
+        <v>4.83146381378174</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423755645752</v>
+        <v>4.85423803329468</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642511367798</v>
+        <v>5.03642463684082</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.63203716278076</v>
+        <v>5.6320366859436</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066253662109</v>
+        <v>4.78066205978394</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912668228149</v>
+        <v>4.98912620544434</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867723464966</v>
+        <v>5.76867771148682</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626388549805</v>
+        <v>6.09626436233521</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458463668823</v>
+        <v>6.16458415985107</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268529891968</v>
+        <v>6.26268482208252</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523538589478</v>
+        <v>6.55523586273193</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640419006348</v>
+        <v>6.47640466690063</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034721374512</v>
+        <v>6.42034673690796</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947233200073</v>
+        <v>6.29947280883789</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078952789307</v>
+        <v>6.12078905105591</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589683532715</v>
+        <v>6.22589731216431</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779260635376</v>
+        <v>6.36779308319092</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385410308838</v>
+        <v>6.18385362625122</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516677856445</v>
+        <v>6.24516725540161</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.90006256103516</v>
+        <v>5.900062084198</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583227157593</v>
+        <v>5.67583179473877</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670976638794</v>
+        <v>5.55670928955078</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415515899658</v>
+        <v>5.50415563583374</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569458007812</v>
+        <v>5.05569505691528</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868793487549</v>
+        <v>5.04868745803833</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116941452026</v>
+        <v>5.03116989135742</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920146942139</v>
+        <v>4.81920194625854</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686742782593</v>
+        <v>4.73686695098877</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.93482065200806</v>
+        <v>4.9348201751709</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102602005005</v>
+        <v>4.89102554321289</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320953369141</v>
+        <v>5.31320905685425</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919124603271</v>
+        <v>5.53919172286987</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145763397217</v>
+        <v>5.31145811080933</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.3990478515625</v>
+        <v>5.39904737472534</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.13802909851074</v>
+        <v>5.1380295753479</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.95584201812744</v>
+        <v>4.9558424949646</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766561508179</v>
+        <v>5.02766609191895</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795740127563</v>
+        <v>5.06795692443848</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927007675171</v>
+        <v>5.12927055358887</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678859710693</v>
+        <v>5.14678812026978</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707990646362</v>
+        <v>5.18707942962646</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248565673828</v>
+        <v>4.85248613357544</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.09248304367065</v>
+        <v>5.0924825668335</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.42357301712036</v>
+        <v>5.4235725402832</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.4778790473938</v>
+        <v>5.47787857055664</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488569259644</v>
+        <v>5.48488616943359</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174537658691</v>
+        <v>5.59174585342407</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693199157715</v>
+        <v>5.28693246841431</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941751480103</v>
+        <v>5.02941799163818</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423398971558</v>
+        <v>5.09423446655273</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.13627767562866</v>
+        <v>5.1362771987915</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.22211599349976</v>
+        <v>5.2221155166626</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189590454102</v>
+        <v>5.25189638137817</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.1905837059021</v>
+        <v>5.19058322906494</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613332748413</v>
+        <v>4.99613380432129</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350749969482</v>
+        <v>4.87350797653198</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569862365723</v>
+        <v>4.81569814682007</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657564163208</v>
+        <v>4.69657611846924</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314401626587</v>
+        <v>4.76314449310303</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.9821195602417</v>
+        <v>4.98211908340454</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649681091309</v>
+        <v>5.10649728775024</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416276931763</v>
+        <v>5.02416229248047</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628076553345</v>
+        <v>4.89628124237061</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088119506836</v>
+        <v>4.75088167190552</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803623199463</v>
+        <v>4.65803575515747</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.5967230796814</v>
+        <v>4.59672355651855</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979122161865</v>
+        <v>4.41979169845581</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.1176061630249</v>
+        <v>4.11760568618774</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008562088013</v>
+        <v>4.22008609771729</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826095581055</v>
+        <v>4.26826047897339</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.3094277381897</v>
+        <v>4.30942821502686</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030523300171</v>
+        <v>4.19030570983887</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.19731283187866</v>
+        <v>4.1973123550415</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359477043152</v>
+        <v>3.86359453201294</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958028793335</v>
+        <v>3.84958052635193</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147403717041</v>
+        <v>4.11147451400757</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118118286133</v>
+        <v>4.19118165969849</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789901733398</v>
+        <v>4.03789949417114</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556295394897</v>
+        <v>4.07556247711182</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.432053565979</v>
+        <v>4.43205404281616</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.491614818573</v>
+        <v>4.49161529541016</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110485076904</v>
+        <v>4.48110437393188</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592084884644</v>
+        <v>4.54592132568359</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59119009971619</v>
+        <v>3.59118986129761</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512884140015</v>
+        <v>3.77512907981873</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.7033052444458</v>
+        <v>3.70330548286438</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746205329895</v>
+        <v>3.97746181488037</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819187164307</v>
+        <v>3.95819234848022</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483289718628</v>
+        <v>4.09483242034912</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.5056300163269</v>
+        <v>4.50562953948975</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504335403442</v>
+        <v>4.66504383087158</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358324050903</v>
+        <v>4.70358276367188</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365446090698</v>
+        <v>4.77365493774414</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387407302856</v>
+        <v>4.74387454986572</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55721,7 +55721,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="D1909" t="n">
-        <v>4.44999980926514</v>
+        <v>4.46000003814697</v>
       </c>
       <c r="E1909" t="n">
         <v>4.29400014877319</v>
@@ -55736,6 +55736,35 @@
         <v>5437280</v>
       </c>
       <c r="I1909" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1910" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1910" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>4.44700002670288</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>4.37400007247925</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>4.43100023269653</v>
+      </c>
+      <c r="G1910" t="n">
+        <v>4.43100023269653</v>
+      </c>
+      <c r="H1910" t="n">
+        <v>5875134</v>
+      </c>
+      <c r="I1910" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -55768,6 +55768,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1911">
+      <c r="A1911" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1911" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1911" t="n">
+        <v>4.35300016403198</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>4.43200016021729</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>4.39300012588501</v>
+      </c>
+      <c r="G1911" t="n">
+        <v>4.39300012588501</v>
+      </c>
+      <c r="H1911" t="n">
+        <v>4879261</v>
+      </c>
+      <c r="I1911" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -55797,6 +55797,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1912">
+      <c r="A1912" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1912" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1912" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="E1912" t="n">
+        <v>4.33699989318848</v>
+      </c>
+      <c r="F1912" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="G1912" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="H1912" t="n">
+        <v>4454047</v>
+      </c>
+      <c r="I1912" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55823,6 +55823,35 @@
         <v>4454047</v>
       </c>
       <c r="I1912" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1913" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1913" t="n">
+        <v>4.35200023651123</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>4.3899998664856</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>4.31799983978271</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>4.36199998855591</v>
+      </c>
+      <c r="G1913" t="n">
+        <v>4.36199998855591</v>
+      </c>
+      <c r="H1913" t="n">
+        <v>3524733</v>
+      </c>
+      <c r="I1913" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -55855,6 +55855,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1914">
+      <c r="A1914" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1914" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1914" t="n">
+        <v>4.36700010299683</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>4.39499998092651</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>4.31699991226196</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>4.39099979400635</v>
+      </c>
+      <c r="G1914" t="n">
+        <v>4.39099979400635</v>
+      </c>
+      <c r="H1914" t="n">
+        <v>3815926</v>
+      </c>
+      <c r="I1914" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35755968093872</v>
+        <v>7.35756015777588</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.46354389190674</v>
+        <v>7.4635443687439</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0404839515686</v>
+        <v>7.04048442840576</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.19551849365234</v>
+        <v>7.1955189704895</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.36631870269775</v>
+        <v>7.3663182258606</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65098571777344</v>
+        <v>7.6509861946106</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047325134277</v>
+        <v>7.76047372817993</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638624191284</v>
+        <v>7.79638576507568</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813718795776</v>
+        <v>7.79813766479492</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62032985687256</v>
+        <v>7.6203293800354</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441579818726</v>
+        <v>7.70441627502441</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675174713135</v>
+        <v>7.78675127029419</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214775085449</v>
+        <v>8.17214679718018</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521339416504</v>
+        <v>8.11521434783936</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287887573242</v>
+        <v>8.03287792205811</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.1160888671875</v>
+        <v>8.11608982086182</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295307159424</v>
+        <v>7.98295259475708</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718954086304</v>
+        <v>7.72718906402588</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.82091093063354</v>
+        <v>7.8209114074707</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010763168335</v>
+        <v>7.89010715484619</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528961181641</v>
+        <v>7.94528913497925</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00484943389893</v>
+        <v>8.00485038757324</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9838285446167</v>
+        <v>7.98382806777954</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907913208008</v>
+        <v>8.34907817840576</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5032377243042</v>
+        <v>8.50323677062988</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411426544189</v>
+        <v>8.38411521911621</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732723236084</v>
+        <v>8.34732627868652</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39375019073486</v>
+        <v>8.39374923706055</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644866943359</v>
+        <v>8.58644771575928</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703330993652</v>
+        <v>8.54703235626221</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535358428955</v>
+        <v>8.61535263061523</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40864086151123</v>
+        <v>8.40863990783691</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206737518311</v>
+        <v>8.70206642150879</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330680847168</v>
+        <v>8.81330585479736</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790580749512</v>
+        <v>8.66790676116943</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.69330787658691</v>
+        <v>8.6933069229126</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.7046947479248</v>
+        <v>8.70469379425049</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856868743896</v>
+        <v>8.33856773376465</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827796936035</v>
+        <v>8.17827892303467</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294498443604</v>
+        <v>8.46294593811035</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207557678223</v>
+        <v>8.10207462310791</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944416046143</v>
+        <v>8.33944320678711</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973796844482</v>
+        <v>8.25973701477051</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.47871208190918</v>
+        <v>8.4787130355835</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995555877686</v>
+        <v>8.34995460510254</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.32104969024658</v>
+        <v>8.3210506439209</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470092773438</v>
+        <v>8.22470188140869</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207260131836</v>
+        <v>8.22207355499268</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688087463379</v>
+        <v>8.88688182830811</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184169769287</v>
+        <v>9.09184265136719</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05155086517334</v>
+        <v>9.05154991149902</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.6348991394043</v>
+        <v>9.63490009307861</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429214477539</v>
+        <v>10.1429224014282</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256153106689</v>
+        <v>9.79256248474121</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409881591797</v>
+        <v>9.58409786224365</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235050201416</v>
+        <v>10.2235040664673</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754684448242</v>
+        <v>10.6754693984985</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471460342407</v>
+        <v>10.8471450805664</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141557693481</v>
+        <v>10.6141567230225</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224729537964</v>
+        <v>10.9224739074707</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.036340713501</v>
+        <v>11.0363397598267</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027616500854</v>
+        <v>11.2027606964111</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652364730835</v>
+        <v>11.6652355194092</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793991088867</v>
+        <v>11.5793981552124</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422815322876</v>
+        <v>14.1422805786133</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5273990631104</v>
+        <v>13.5274000167847</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789394378662</v>
+        <v>13.0789384841919</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718181610107</v>
+        <v>10.7718191146851</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716648101807</v>
+        <v>9.40716552734375</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025768280029</v>
+        <v>7.55025815963745</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651054382324</v>
+        <v>10.5651063919067</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632061004639</v>
+        <v>10.6632070541382</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788940429688</v>
+        <v>9.86788845062256</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743072509766</v>
+        <v>10.2743062973022</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779502868652</v>
+        <v>10.7779493331909</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421770095825</v>
+        <v>11.2421760559082</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.3648023605347</v>
+        <v>11.364803314209</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969161987305</v>
+        <v>11.5969152450562</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064037322998</v>
+        <v>11.7064027786255</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.41588306427</v>
+        <v>12.4158821105957</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.109317779541</v>
+        <v>12.1093168258667</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925359725952</v>
+        <v>11.5925369262695</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961790084839</v>
+        <v>12.0961799621582</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.437780380249</v>
+        <v>12.4377794265747</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633197784424</v>
+        <v>12.9633207321167</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297325134277</v>
+        <v>13.7297334671021</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027433395386</v>
+        <v>12.4027442932129</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421504974365</v>
+        <v>13.0421514511108</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173309326172</v>
+        <v>13.2173318862915</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0844717025757</v>
+        <v>14.08447265625</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676826477051</v>
+        <v>14.1676816940308</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830238342285</v>
+        <v>13.2830228805542</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640478134155</v>
+        <v>13.0640487670898</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3092994689941</v>
+        <v>13.3093004226685</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698841094971</v>
+        <v>13.2698850631714</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.347240447998</v>
+        <v>14.3472414016724</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589159011841</v>
+        <v>14.7589149475098</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129251480103</v>
+        <v>15.0129261016846</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326374053955</v>
+        <v>14.7326364517212</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.8070907592773</v>
+        <v>14.807089805603</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048965454102</v>
+        <v>15.1048955917358</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.828987121582</v>
+        <v>14.8289880752563</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.271315574646</v>
+        <v>15.2713165283203</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720701217651</v>
+        <v>13.5720710754395</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903335571289</v>
+        <v>12.4903345108032</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.792519569397</v>
+        <v>12.7925186157227</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720802307129</v>
+        <v>12.9720792770386</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195251464844</v>
+        <v>12.9195241928101</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268194198608</v>
+        <v>13.3268184661865</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866659164429</v>
+        <v>13.7866649627686</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457853317261</v>
+        <v>14.1457843780518</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019906997681</v>
+        <v>14.1019897460938</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706039428711</v>
+        <v>13.9706048965454</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268093109131</v>
+        <v>13.9268102645874</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647603988647</v>
+        <v>14.3647594451904</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.887393951416</v>
+        <v>13.8873949050903</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.1866750717163</v>
+        <v>13.186674118042</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567544937134</v>
+        <v>12.6567554473877</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348489761353</v>
+        <v>13.2348480224609</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377721786499</v>
+        <v>13.0377712249756</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925113677979</v>
+        <v>13.3925104141235</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122226715088</v>
+        <v>13.1122236251831</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027351379395</v>
+        <v>13.0027360916138</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450727462769</v>
+        <v>12.8450736999512</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516380310059</v>
+        <v>13.1516389846802</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.7662420272827</v>
+        <v>12.766242980957</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187971115112</v>
+        <v>12.8187961578369</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202531814575</v>
+        <v>13.0202541351318</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049211502075</v>
+        <v>13.3049201965332</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669618606567</v>
+        <v>13.4669628143311</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260904312134</v>
+        <v>13.2260894775391</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830146789551</v>
+        <v>13.8830156326294</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.4275465011597</v>
+        <v>13.427547454834</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786445617676</v>
+        <v>13.2786436080933</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005336761475</v>
+        <v>13.9005327224731</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618381500244</v>
+        <v>14.5618371963501</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523506164551</v>
+        <v>14.4523496627808</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465061187744</v>
+        <v>14.8465051651001</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537984848022</v>
+        <v>15.2537994384766</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3223972320557</v>
+        <v>16.322395324707</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056053161621</v>
+        <v>16.4056072235107</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968395233154</v>
+        <v>16.9968414306641</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.475679397583</v>
+        <v>16.4756774902344</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588975906372</v>
+        <v>15.9588966369629</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348142623901</v>
+        <v>15.6348161697388</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640068054199</v>
+        <v>16.0640048980713</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6420993804932</v>
+        <v>16.6421012878418</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793315887451</v>
+        <v>16.3793296813965</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362712860107</v>
+        <v>15.8362722396851</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.8625497817993</v>
+        <v>15.862548828125</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034303665161</v>
+        <v>15.5034313201904</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581787109375</v>
+        <v>15.2581777572632</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756967544556</v>
+        <v>15.2756958007812</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238716125488</v>
+        <v>15.3238706588745</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662082672119</v>
+        <v>15.1662092208862</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027013778687</v>
+        <v>15.4027004241943</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771518707275</v>
+        <v>15.4771528244019</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3764247894287</v>
+        <v>15.376425743103</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552555084229</v>
+        <v>15.4552564620972</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443017959595</v>
+        <v>15.7443027496338</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.884446144104</v>
+        <v>15.8844470977783</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873693466187</v>
+        <v>15.6873683929443</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304340362549</v>
+        <v>15.6304349899292</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.6435747146606</v>
+        <v>15.643575668335</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275136947632</v>
+        <v>15.8275127410889</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676570892334</v>
+        <v>15.9676561355591</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.46839427948</v>
+        <v>15.4683933258057</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413887023926</v>
+        <v>15.3413877487183</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.354528427124</v>
+        <v>15.3545274734497</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421340942383</v>
+        <v>14.2421350479126</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684024810791</v>
+        <v>14.8684034347534</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530694961548</v>
+        <v>15.1530685424805</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501462936401</v>
+        <v>15.3501472473145</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.424599647522</v>
+        <v>15.4246006011963</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056573867798</v>
+        <v>12.8056583404541</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355852127075</v>
+        <v>12.7355861663818</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326629638672</v>
+        <v>12.9326639175415</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640396118164</v>
+        <v>13.6640405654907</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319267272949</v>
+        <v>13.4319257736206</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.814416885376</v>
+        <v>12.8144178390503</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574825286865</v>
+        <v>12.7574834823608</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224565505981</v>
+        <v>12.1224555969238</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.245080947876</v>
+        <v>12.2450819015503</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.021728515625</v>
+        <v>12.0217275619507</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830411911011</v>
+        <v>12.0830402374268</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.043625831604</v>
+        <v>12.0436248779297</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282928466797</v>
+        <v>12.3282918930054</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.223183631897</v>
+        <v>12.2231845855713</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.868444442749</v>
+        <v>11.8684453964233</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618719100952</v>
+        <v>12.1618709564209</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764677047729</v>
+        <v>12.3764667510986</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538404464722</v>
+        <v>12.2538414001465</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385074615479</v>
+        <v>12.5385084152222</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348653793335</v>
+        <v>12.0348663330078</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553066253662</v>
+        <v>11.8553056716919</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407108306885</v>
+        <v>11.6407117843628</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516563415527</v>
+        <v>11.9516553878784</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472761154175</v>
+        <v>11.9472770690918</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348745346069</v>
+        <v>11.4348754882812</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370687484741</v>
+        <v>11.1370677947998</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932741165161</v>
+        <v>11.0932731628418</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786773681641</v>
+        <v>10.8786783218384</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173728942871</v>
+        <v>10.2173738479614</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629409790039</v>
+        <v>9.16629314422607</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93417930603027</v>
+        <v>8.93418025970459</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862350463867</v>
+        <v>9.60862255096436</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804706573486</v>
+        <v>9.04804611206055</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652191162109</v>
+        <v>8.53652095794678</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.37010097503662</v>
+        <v>8.3701000213623</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126930236816</v>
+        <v>8.29126834869385</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740249633789</v>
+        <v>8.17740345001221</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813564300537</v>
+        <v>7.91813611984253</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441318511963</v>
+        <v>7.94441270828247</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813968658447</v>
+        <v>7.67813873291016</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448535919189</v>
+        <v>8.01448440551758</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097846984863</v>
+        <v>8.25097751617432</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.044264793396</v>
+        <v>8.04426574707031</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842742919922</v>
+        <v>7.95842790603638</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274059295654</v>
+        <v>7.53274011611938</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806346893311</v>
+        <v>7.84806394577026</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398109436035</v>
+        <v>7.52398061752319</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49623012542725</v>
+        <v>8.49622917175293</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498962402344</v>
+        <v>8.50498867034912</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282869338989</v>
+        <v>6.40282917022705</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829378128052</v>
+        <v>7.09829330444336</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449819564819</v>
+        <v>7.05449867248535</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500911712646</v>
+        <v>7.06500959396362</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055969238281</v>
+        <v>6.87055921554565</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668622970581</v>
+        <v>7.23668575286865</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916723251343</v>
+        <v>7.21916770935059</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419713973999</v>
+        <v>7.73419666290283</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923274993896</v>
+        <v>7.76923322677612</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.70091247558594</v>
+        <v>7.7009129524231</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098417282104</v>
+        <v>7.77098512649536</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791650772095</v>
+        <v>7.94791698455811</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222610473633</v>
+        <v>7.76222658157349</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376100540161</v>
+        <v>7.55376148223877</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.4661717414856</v>
+        <v>7.46617126464844</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267150878906</v>
+        <v>7.22267198562622</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.3347864151001</v>
+        <v>7.33478593826294</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18238019943237</v>
+        <v>7.18237972259521</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543811798096</v>
+        <v>7.72543716430664</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755254745483</v>
+        <v>7.83755302429199</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908935546875</v>
+        <v>7.62908887863159</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784837722778</v>
+        <v>7.63784790039062</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.7464599609375</v>
+        <v>7.74645948410034</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412496566772</v>
+        <v>7.66412544250488</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157487869263</v>
+        <v>7.37157440185547</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.56952810287476</v>
+        <v>7.5695276260376</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230445861816</v>
+        <v>7.35230493545532</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675745010376</v>
+        <v>7.30675792694092</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456371307373</v>
+        <v>7.60456418991089</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142339706421</v>
+        <v>7.71142387390137</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.5169734954834</v>
+        <v>7.51697397232056</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755611419678</v>
+        <v>7.59755659103394</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047777175903</v>
+        <v>7.52047729492188</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448892593384</v>
+        <v>7.77448844909668</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703853607178</v>
+        <v>8.06703948974609</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711380004883</v>
+        <v>7.89711427688599</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.674635887146</v>
+        <v>7.67463541030884</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81477975845337</v>
+        <v>7.81478023529053</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171518325806</v>
+        <v>7.75171566009521</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.64660692214966</v>
+        <v>7.6466064453125</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981893539429</v>
+        <v>7.60981941223145</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.8831000328064</v>
+        <v>7.88309955596924</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952453613281</v>
+        <v>7.80952501296997</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602382659912</v>
+        <v>7.56602430343628</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427192687988</v>
+        <v>7.56427240371704</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945592880249</v>
+        <v>7.49945640563965</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500650405884</v>
+        <v>7.30500602722168</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.3610634803772</v>
+        <v>7.36106443405151</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.40836238861084</v>
+        <v>7.408362865448</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587995529175</v>
+        <v>7.42587947845459</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953832626343</v>
+        <v>6.84953784942627</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617792129517</v>
+        <v>6.98617839813232</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129283905029</v>
+        <v>6.61129331588745</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881135940552</v>
+        <v>6.62881088256836</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76369953155518</v>
+        <v>6.76370000839233</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997659683228</v>
+        <v>6.78997707366943</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632535934448</v>
+        <v>6.88632583618164</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355209350586</v>
+        <v>6.86355257034302</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551742553711</v>
+        <v>7.31551694869995</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.3032546043396</v>
+        <v>7.30325412750244</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997303009033</v>
+        <v>7.02997350692749</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.12106704711914</v>
+        <v>7.1210675239563</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.6220817565918</v>
+        <v>7.62208127975464</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011381149292</v>
+        <v>7.41011428833008</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252359390259</v>
+        <v>7.32252407073975</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055255889893</v>
+        <v>7.35055303573608</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953428268433</v>
+        <v>7.08953475952148</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092674255371</v>
+        <v>6.74092626571655</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107370376587</v>
+        <v>6.64107322692871</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414232254028</v>
+        <v>6.46414184570312</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698728561401</v>
+        <v>6.55698776245117</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961715698242</v>
+        <v>6.43961668014526</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114944458008</v>
+        <v>6.47114896774292</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312000274658</v>
+        <v>6.44312047958374</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662023544312</v>
+        <v>6.68662071228027</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713163375854</v>
+        <v>6.69713115692139</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450580596924</v>
+        <v>6.57450532913208</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399749755859</v>
+        <v>6.32399797439575</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501625061035</v>
+        <v>6.58501672744751</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888257980347</v>
+        <v>6.69888305664062</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143766403198</v>
+        <v>6.75143718719482</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924654006958</v>
+        <v>6.80924701690674</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.5201997756958</v>
+        <v>6.52019929885864</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078596115112</v>
+        <v>6.36078548431396</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662380218506</v>
+        <v>6.44662427902222</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815608978271</v>
+        <v>6.47815656661987</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020286560059</v>
+        <v>6.28020334243774</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502290725708</v>
+        <v>6.10502243041992</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260646820068</v>
+        <v>6.67260599136353</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48165988922119</v>
+        <v>6.48166036605835</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224298477173</v>
+        <v>6.56224250793457</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.70939350128174</v>
+        <v>6.7093939781189</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932228088379</v>
+        <v>6.63932180404663</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070713043213</v>
+        <v>6.77070665359497</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.8320198059082</v>
+        <v>6.83202028274536</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.17509508132935</v>
+        <v>6.1750955581665</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203002929688</v>
+        <v>6.11203050613403</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.15407371520996</v>
+        <v>6.1540732383728</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.81597566604614</v>
+        <v>5.8159761428833</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313070297241</v>
+        <v>5.72313022613525</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210886001587</v>
+        <v>5.70210933685303</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896902084351</v>
+        <v>5.80896854400635</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145050048828</v>
+        <v>5.79145097732544</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466608047485</v>
+        <v>5.51466655731201</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474229812622</v>
+        <v>5.34474182128906</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496452331543</v>
+        <v>5.07496500015259</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.8314642906189</v>
+        <v>4.83146381378174</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423755645752</v>
+        <v>4.85423803329468</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642511367798</v>
+        <v>5.03642463684082</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.63203716278076</v>
+        <v>5.6320366859436</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066253662109</v>
+        <v>4.78066205978394</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912668228149</v>
+        <v>4.98912620544434</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867723464966</v>
+        <v>5.76867771148682</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122827529907</v>
+        <v>6.06122779846191</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626388549805</v>
+        <v>6.09626436233521</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458463668823</v>
+        <v>6.16458415985107</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268529891968</v>
+        <v>6.26268482208252</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713472366333</v>
+        <v>6.45713520050049</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523538589478</v>
+        <v>6.55523586273193</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640419006348</v>
+        <v>6.47640466690063</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691558837891</v>
+        <v>6.48691511154175</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034721374512</v>
+        <v>6.42034673690796</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947233200073</v>
+        <v>6.29947280883789</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078952789307</v>
+        <v>6.12078905105591</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005542755127</v>
+        <v>6.38005590438843</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888662338257</v>
+        <v>6.45888710021973</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589683532715</v>
+        <v>6.22589731216431</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21889019012451</v>
+        <v>6.21888971328735</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779260635376</v>
+        <v>6.36779308319092</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385410308838</v>
+        <v>6.18385362625122</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516677856445</v>
+        <v>6.24516725540161</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239351272583</v>
+        <v>6.22239398956299</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.90006256103516</v>
+        <v>5.900062084198</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583227157593</v>
+        <v>5.67583179473877</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.6583137512207</v>
+        <v>5.65831422805786</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670976638794</v>
+        <v>5.55670928955078</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415515899658</v>
+        <v>5.50415563583374</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569458007812</v>
+        <v>5.05569505691528</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868793487549</v>
+        <v>5.04868745803833</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116941452026</v>
+        <v>5.03116989135742</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920146942139</v>
+        <v>4.81920194625854</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686742782593</v>
+        <v>4.73686695098877</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.93482065200806</v>
+        <v>4.9348201751709</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102602005005</v>
+        <v>4.89102554321289</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320953369141</v>
+        <v>5.31320905685425</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919124603271</v>
+        <v>5.53919172286987</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021308898926</v>
+        <v>5.56021356582642</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145763397217</v>
+        <v>5.31145811080933</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.3990478515625</v>
+        <v>5.39904737472534</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.13802909851074</v>
+        <v>5.1380295753479</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.95584201812744</v>
+        <v>4.9558424949646</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766561508179</v>
+        <v>5.02766609191895</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795740127563</v>
+        <v>5.06795692443848</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927007675171</v>
+        <v>5.12927055358887</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678859710693</v>
+        <v>5.14678812026978</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707990646362</v>
+        <v>5.18707942962646</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051509857178</v>
+        <v>4.88051462173462</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248565673828</v>
+        <v>4.85248613357544</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.09248304367065</v>
+        <v>5.0924825668335</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547235488892</v>
+        <v>5.32547187805176</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926746368408</v>
+        <v>5.36926698684692</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.42357301712036</v>
+        <v>5.4235725402832</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.4778790473938</v>
+        <v>5.47787857055664</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488569259644</v>
+        <v>5.48488616943359</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641798019409</v>
+        <v>5.51641845703125</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51817035675049</v>
+        <v>5.51816987991333</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174537658691</v>
+        <v>5.59174585342407</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795026779175</v>
+        <v>5.54795074462891</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693199157715</v>
+        <v>5.28693246841431</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36225986480713</v>
+        <v>5.36226034164429</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941751480103</v>
+        <v>5.02941799163818</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423398971558</v>
+        <v>5.09423446655273</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.13627767562866</v>
+        <v>5.1362771987915</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.22211599349976</v>
+        <v>5.2221155166626</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189590454102</v>
+        <v>5.25189638137817</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.1905837059021</v>
+        <v>5.19058322906494</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613332748413</v>
+        <v>4.99613380432129</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.01365184783936</v>
+        <v>5.0136513710022</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.0329213142395</v>
+        <v>5.03292083740234</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350749969482</v>
+        <v>4.87350797653198</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569862365723</v>
+        <v>4.81569814682007</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657564163208</v>
+        <v>4.69657611846924</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.798180103302</v>
+        <v>4.79818058013916</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314401626587</v>
+        <v>4.76314449310303</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.9821195602417</v>
+        <v>4.98211908340454</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649681091309</v>
+        <v>5.10649728775024</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146072387695</v>
+        <v>5.07146120071411</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416276931763</v>
+        <v>5.02416229248047</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628076553345</v>
+        <v>4.89628124237061</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533514022827</v>
+        <v>4.70533466339111</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.80518770217896</v>
+        <v>4.8051872253418</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088119506836</v>
+        <v>4.75088167190552</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803623199463</v>
+        <v>4.65803575515747</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.5967230796814</v>
+        <v>4.59672355651855</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979122161865</v>
+        <v>4.41979169845581</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.1176061630249</v>
+        <v>4.11760568618774</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008562088013</v>
+        <v>4.22008609771729</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826095581055</v>
+        <v>4.26826047897339</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.3094277381897</v>
+        <v>4.30942821502686</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030523300171</v>
+        <v>4.19030570983887</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.19731283187866</v>
+        <v>4.1973123550415</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359477043152</v>
+        <v>3.86359453201294</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958028793335</v>
+        <v>3.84958052635193</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147403717041</v>
+        <v>4.11147451400757</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118118286133</v>
+        <v>4.19118165969849</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789901733398</v>
+        <v>4.03789949417114</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556295394897</v>
+        <v>4.07556247711182</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.432053565979</v>
+        <v>4.43205404281616</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.491614818573</v>
+        <v>4.49161529541016</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110485076904</v>
+        <v>4.48110437393188</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592084884644</v>
+        <v>4.54592132568359</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59119009971619</v>
+        <v>3.59118986129761</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512884140015</v>
+        <v>3.77512907981873</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.7033052444458</v>
+        <v>3.70330548286438</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746205329895</v>
+        <v>3.97746181488037</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819187164307</v>
+        <v>3.95819234848022</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483289718628</v>
+        <v>4.09483242034912</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.5056300163269</v>
+        <v>4.50562953948975</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504335403442</v>
+        <v>4.66504383087158</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358324050903</v>
+        <v>4.70358276367188</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365446090698</v>
+        <v>4.77365493774414</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387407302856</v>
+        <v>4.74387454986572</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55881,6 +55881,35 @@
         <v>3815926</v>
       </c>
       <c r="I1914" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1915" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1915" t="n">
+        <v>4.39099979400635</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>4.41599988937378</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>4.38700008392334</v>
+      </c>
+      <c r="G1915" t="n">
+        <v>4.38700008392334</v>
+      </c>
+      <c r="H1915" t="n">
+        <v>3644967</v>
+      </c>
+      <c r="I1915" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NEXI.MI.xlsx
+++ b/data/NEXI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>7.35756015777588</v>
+        <v>7.35755968093872</v>
       </c>
       <c r="H3" t="n">
         <v>2495817</v>
@@ -485,7 +485,7 @@
         <v>8.52099990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4635443687439</v>
+        <v>7.46354389190674</v>
       </c>
       <c r="H4" t="n">
         <v>2017525</v>
@@ -543,7 +543,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G6" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H6" t="n">
         <v>3477583</v>
@@ -601,7 +601,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04048442840576</v>
+        <v>7.0404839515686</v>
       </c>
       <c r="H8" t="n">
         <v>1523490</v>
@@ -688,7 +688,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1955189704895</v>
+        <v>7.19551849365234</v>
       </c>
       <c r="H11" t="n">
         <v>1338361</v>
@@ -891,7 +891,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3663182258606</v>
+        <v>7.36631870269775</v>
       </c>
       <c r="H18" t="n">
         <v>1382606</v>
@@ -920,7 +920,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6509861946106</v>
+        <v>7.65098571777344</v>
       </c>
       <c r="H19" t="n">
         <v>2613005</v>
@@ -978,7 +978,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G21" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H21" t="n">
         <v>1182584</v>
@@ -1036,7 +1036,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H23" t="n">
         <v>2209531</v>
@@ -1065,7 +1065,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>7.76047372817993</v>
+        <v>7.76047325134277</v>
       </c>
       <c r="H24" t="n">
         <v>2775252</v>
@@ -1094,7 +1094,7 @@
         <v>8.90100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>7.79638576507568</v>
+        <v>7.79638624191284</v>
       </c>
       <c r="H25" t="n">
         <v>1712850</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H26" t="n">
         <v>918665</v>
@@ -1152,7 +1152,7 @@
         <v>8.90299987792969</v>
       </c>
       <c r="G27" t="n">
-        <v>7.79813766479492</v>
+        <v>7.79813718795776</v>
       </c>
       <c r="H27" t="n">
         <v>1088282</v>
@@ -1181,7 +1181,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H28" t="n">
         <v>945447</v>
@@ -1210,7 +1210,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G29" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H29" t="n">
         <v>588794</v>
@@ -1239,7 +1239,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6203293800354</v>
+        <v>7.62032985687256</v>
       </c>
       <c r="H30" t="n">
         <v>1739763</v>
@@ -1268,7 +1268,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G31" t="n">
-        <v>7.70441627502441</v>
+        <v>7.70441579818726</v>
       </c>
       <c r="H31" t="n">
         <v>528054</v>
@@ -1297,7 +1297,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>7.78675127029419</v>
+        <v>7.78675174713135</v>
       </c>
       <c r="H32" t="n">
         <v>435646</v>
@@ -1413,7 +1413,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>8.17214679718018</v>
+        <v>8.17214775085449</v>
       </c>
       <c r="H36" t="n">
         <v>1259328</v>
@@ -1442,7 +1442,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G37" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H37" t="n">
         <v>1078771</v>
@@ -1500,7 +1500,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G39" t="n">
-        <v>8.11521434783936</v>
+        <v>8.11521339416504</v>
       </c>
       <c r="H39" t="n">
         <v>831391</v>
@@ -1529,7 +1529,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H40" t="n">
         <v>373448</v>
@@ -1558,7 +1558,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G41" t="n">
-        <v>8.03287792205811</v>
+        <v>8.03287887573242</v>
       </c>
       <c r="H41" t="n">
         <v>298772</v>
@@ -1587,7 +1587,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G42" t="n">
-        <v>8.11608982086182</v>
+        <v>8.1160888671875</v>
       </c>
       <c r="H42" t="n">
         <v>923039</v>
@@ -1674,7 +1674,7 @@
         <v>9.11400032043457</v>
       </c>
       <c r="G45" t="n">
-        <v>7.98295259475708</v>
+        <v>7.98295307159424</v>
       </c>
       <c r="H45" t="n">
         <v>5887530</v>
@@ -1732,7 +1732,7 @@
         <v>8.82199954986572</v>
       </c>
       <c r="G47" t="n">
-        <v>7.72718906402588</v>
+        <v>7.72718954086304</v>
       </c>
       <c r="H47" t="n">
         <v>1402048</v>
@@ -1761,7 +1761,7 @@
         <v>8.92899990081787</v>
       </c>
       <c r="G48" t="n">
-        <v>7.8209114074707</v>
+        <v>7.82091093063354</v>
       </c>
       <c r="H48" t="n">
         <v>1115123</v>
@@ -1790,7 +1790,7 @@
         <v>9.00800037384033</v>
       </c>
       <c r="G49" t="n">
-        <v>7.89010715484619</v>
+        <v>7.89010763168335</v>
       </c>
       <c r="H49" t="n">
         <v>387110</v>
@@ -1877,7 +1877,7 @@
         <v>9.07100009918213</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94528913497925</v>
+        <v>7.94528961181641</v>
       </c>
       <c r="H52" t="n">
         <v>847838</v>
@@ -1906,7 +1906,7 @@
         <v>9.13899993896484</v>
       </c>
       <c r="G53" t="n">
-        <v>8.00485038757324</v>
+        <v>8.00484943389893</v>
       </c>
       <c r="H53" t="n">
         <v>1352053</v>
@@ -1964,7 +1964,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G55" t="n">
-        <v>7.98382806777954</v>
+        <v>7.9838285446167</v>
       </c>
       <c r="H55" t="n">
         <v>1295292</v>
@@ -2051,7 +2051,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G58" t="n">
-        <v>8.34907817840576</v>
+        <v>8.34907913208008</v>
       </c>
       <c r="H58" t="n">
         <v>2208583</v>
@@ -2196,7 +2196,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G63" t="n">
-        <v>8.50323677062988</v>
+        <v>8.5032377243042</v>
       </c>
       <c r="H63" t="n">
         <v>611066</v>
@@ -2254,7 +2254,7 @@
         <v>9.57199954986572</v>
       </c>
       <c r="G65" t="n">
-        <v>8.38411521911621</v>
+        <v>8.38411426544189</v>
       </c>
       <c r="H65" t="n">
         <v>851736</v>
@@ -2283,7 +2283,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G66" t="n">
-        <v>8.34732627868652</v>
+        <v>8.34732723236084</v>
       </c>
       <c r="H66" t="n">
         <v>608896</v>
@@ -2312,7 +2312,7 @@
         <v>9.58300018310547</v>
       </c>
       <c r="G67" t="n">
-        <v>8.39374923706055</v>
+        <v>8.39375019073486</v>
       </c>
       <c r="H67" t="n">
         <v>752165</v>
@@ -2399,7 +2399,7 @@
         <v>9.80300045013428</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58644771575928</v>
+        <v>8.58644866943359</v>
       </c>
       <c r="H70" t="n">
         <v>1182422</v>
@@ -2428,7 +2428,7 @@
         <v>9.75800037384033</v>
       </c>
       <c r="G71" t="n">
-        <v>8.54703235626221</v>
+        <v>8.54703330993652</v>
       </c>
       <c r="H71" t="n">
         <v>1865592</v>
@@ -2515,7 +2515,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G74" t="n">
-        <v>8.61535263061523</v>
+        <v>8.61535358428955</v>
       </c>
       <c r="H74" t="n">
         <v>1499481</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H75" t="n">
         <v>1313271</v>
@@ -2602,7 +2602,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>8.40863990783691</v>
+        <v>8.40864086151123</v>
       </c>
       <c r="H77" t="n">
         <v>981036</v>
@@ -2834,7 +2834,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>8.70206642150879</v>
+        <v>8.70206737518311</v>
       </c>
       <c r="H85" t="n">
         <v>763160</v>
@@ -2892,7 +2892,7 @@
         <v>10.0620002746582</v>
       </c>
       <c r="G87" t="n">
-        <v>8.81330585479736</v>
+        <v>8.81330680847168</v>
       </c>
       <c r="H87" t="n">
         <v>1423245</v>
@@ -3124,7 +3124,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G95" t="n">
-        <v>8.66790676116943</v>
+        <v>8.66790580749512</v>
       </c>
       <c r="H95" t="n">
         <v>621190</v>
@@ -3153,7 +3153,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6933069229126</v>
+        <v>8.69330787658691</v>
       </c>
       <c r="H96" t="n">
         <v>754322</v>
@@ -3182,7 +3182,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G97" t="n">
-        <v>8.70469379425049</v>
+        <v>8.7046947479248</v>
       </c>
       <c r="H97" t="n">
         <v>937622</v>
@@ -3327,7 +3327,7 @@
         <v>9.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H102" t="n">
         <v>2145641</v>
@@ -3356,7 +3356,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>8.33856773376465</v>
+        <v>8.33856868743896</v>
       </c>
       <c r="H103" t="n">
         <v>1462077</v>
@@ -3414,7 +3414,7 @@
         <v>9.33699989318848</v>
       </c>
       <c r="G105" t="n">
-        <v>8.17827892303467</v>
+        <v>8.17827796936035</v>
       </c>
       <c r="H105" t="n">
         <v>1466653</v>
@@ -3472,7 +3472,7 @@
         <v>9.66199970245361</v>
       </c>
       <c r="G107" t="n">
-        <v>8.46294593811035</v>
+        <v>8.46294498443604</v>
       </c>
       <c r="H107" t="n">
         <v>1367779</v>
@@ -3849,7 +3849,7 @@
         <v>9.25</v>
       </c>
       <c r="G120" t="n">
-        <v>8.10207462310791</v>
+        <v>8.10207557678223</v>
       </c>
       <c r="H120" t="n">
         <v>996025</v>
@@ -3936,7 +3936,7 @@
         <v>9.52099990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>8.33944320678711</v>
+        <v>8.33944416046143</v>
       </c>
       <c r="H123" t="n">
         <v>1627958</v>
@@ -4023,7 +4023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G126" t="n">
-        <v>8.25973701477051</v>
+        <v>8.25973796844482</v>
       </c>
       <c r="H126" t="n">
         <v>1158230</v>
@@ -4052,7 +4052,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G127" t="n">
-        <v>8.4787130355835</v>
+        <v>8.47871208190918</v>
       </c>
       <c r="H127" t="n">
         <v>1493276</v>
@@ -4081,7 +4081,7 @@
         <v>9.53299999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34995460510254</v>
+        <v>8.34995555877686</v>
       </c>
       <c r="H128" t="n">
         <v>948473</v>
@@ -4110,7 +4110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H129" t="n">
         <v>2276375</v>
@@ -4255,7 +4255,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H134" t="n">
         <v>745699</v>
@@ -4284,7 +4284,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G135" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H135" t="n">
         <v>640611</v>
@@ -4313,7 +4313,7 @@
         <v>9.5</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3210506439209</v>
+        <v>8.32104969024658</v>
       </c>
       <c r="H136" t="n">
         <v>462446</v>
@@ -4342,7 +4342,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G137" t="n">
-        <v>8.22470188140869</v>
+        <v>8.22470092773438</v>
       </c>
       <c r="H137" t="n">
         <v>523225</v>
@@ -4487,7 +4487,7 @@
         <v>9.38700008392334</v>
       </c>
       <c r="G142" t="n">
-        <v>8.22207355499268</v>
+        <v>8.22207260131836</v>
       </c>
       <c r="H142" t="n">
         <v>775009</v>
@@ -4893,7 +4893,7 @@
         <v>10.1459999084473</v>
       </c>
       <c r="G156" t="n">
-        <v>8.88688182830811</v>
+        <v>8.88688087463379</v>
       </c>
       <c r="H156" t="n">
         <v>1535830</v>
@@ -5038,7 +5038,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>9.09184265136719</v>
+        <v>9.09184169769287</v>
       </c>
       <c r="H161" t="n">
         <v>1817108</v>
@@ -5067,7 +5067,7 @@
         <v>10.3339996337891</v>
       </c>
       <c r="G162" t="n">
-        <v>9.05154991149902</v>
+        <v>9.05155086517334</v>
       </c>
       <c r="H162" t="n">
         <v>1895180</v>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="G167" t="n">
-        <v>9.63490009307861</v>
+        <v>9.6348991394043</v>
       </c>
       <c r="H167" t="n">
         <v>2791674</v>
@@ -5299,7 +5299,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>10.1429224014282</v>
+        <v>10.1429214477539</v>
       </c>
       <c r="H170" t="n">
         <v>1898875</v>
@@ -5328,7 +5328,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>9.79256248474121</v>
+        <v>9.79256153106689</v>
       </c>
       <c r="H171" t="n">
         <v>3507762</v>
@@ -5357,7 +5357,7 @@
         <v>10.9420003890991</v>
       </c>
       <c r="G172" t="n">
-        <v>9.58409786224365</v>
+        <v>9.58409881591797</v>
       </c>
       <c r="H172" t="n">
         <v>2050128</v>
@@ -5415,7 +5415,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G174" t="n">
-        <v>10.2235040664673</v>
+        <v>10.2235050201416</v>
       </c>
       <c r="H174" t="n">
         <v>14466576</v>
@@ -5531,7 +5531,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H178" t="n">
         <v>2562005</v>
@@ -5647,7 +5647,7 @@
         <v>12.1879997253418</v>
       </c>
       <c r="G182" t="n">
-        <v>10.6754693984985</v>
+        <v>10.6754684448242</v>
       </c>
       <c r="H182" t="n">
         <v>2271372</v>
@@ -5676,7 +5676,7 @@
         <v>12.3839998245239</v>
       </c>
       <c r="G183" t="n">
-        <v>10.8471450805664</v>
+        <v>10.8471460342407</v>
       </c>
       <c r="H183" t="n">
         <v>2388935</v>
@@ -5705,7 +5705,7 @@
         <v>12.1180000305176</v>
       </c>
       <c r="G184" t="n">
-        <v>10.6141567230225</v>
+        <v>10.6141557693481</v>
       </c>
       <c r="H184" t="n">
         <v>8888924</v>
@@ -5763,7 +5763,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G186" t="n">
-        <v>10.9224739074707</v>
+        <v>10.9224729537964</v>
       </c>
       <c r="H186" t="n">
         <v>5815945</v>
@@ -5908,7 +5908,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.0363397598267</v>
+        <v>11.036340713501</v>
       </c>
       <c r="H191" t="n">
         <v>1414224</v>
@@ -5937,7 +5937,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>11.2027606964111</v>
+        <v>11.2027616500854</v>
       </c>
       <c r="H192" t="n">
         <v>1263376</v>
@@ -6227,7 +6227,7 @@
         <v>13.3179998397827</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6652355194092</v>
+        <v>11.6652364730835</v>
       </c>
       <c r="H202" t="n">
         <v>4451231</v>
@@ -6256,7 +6256,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5793981552124</v>
+        <v>11.5793991088867</v>
       </c>
       <c r="H203" t="n">
         <v>2411208</v>
@@ -6459,7 +6459,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H210" t="n">
         <v>6405101</v>
@@ -6575,7 +6575,7 @@
         <v>16.1459999084473</v>
       </c>
       <c r="G214" t="n">
-        <v>14.1422805786133</v>
+        <v>14.1422815322876</v>
       </c>
       <c r="H214" t="n">
         <v>4144741</v>
@@ -6662,7 +6662,7 @@
         <v>15.4440002441406</v>
       </c>
       <c r="G217" t="n">
-        <v>13.5274000167847</v>
+        <v>13.5273990631104</v>
       </c>
       <c r="H217" t="n">
         <v>5073540</v>
@@ -6778,7 +6778,7 @@
         <v>14.9320001602173</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0789384841919</v>
+        <v>13.0789394378662</v>
       </c>
       <c r="H221" t="n">
         <v>4533070</v>
@@ -6952,7 +6952,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G227" t="n">
-        <v>10.7718191146851</v>
+        <v>10.7718181610107</v>
       </c>
       <c r="H227" t="n">
         <v>4536578</v>
@@ -7010,7 +7010,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.40716552734375</v>
+        <v>9.40716648101807</v>
       </c>
       <c r="H229" t="n">
         <v>6405789</v>
@@ -7126,7 +7126,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>7.55025815963745</v>
+        <v>7.55025768280029</v>
       </c>
       <c r="H233" t="n">
         <v>4187743</v>
@@ -7213,7 +7213,7 @@
         <v>12.0620002746582</v>
       </c>
       <c r="G236" t="n">
-        <v>10.5651063919067</v>
+        <v>10.5651054382324</v>
       </c>
       <c r="H236" t="n">
         <v>5773602</v>
@@ -7271,7 +7271,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G238" t="n">
-        <v>10.6632070541382</v>
+        <v>10.6632061004639</v>
       </c>
       <c r="H238" t="n">
         <v>2764922</v>
@@ -7300,7 +7300,7 @@
         <v>11.2659997940063</v>
       </c>
       <c r="G239" t="n">
-        <v>9.86788845062256</v>
+        <v>9.86788940429688</v>
       </c>
       <c r="H239" t="n">
         <v>3090483</v>
@@ -7387,7 +7387,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>10.2743062973022</v>
+        <v>10.2743072509766</v>
       </c>
       <c r="H242" t="n">
         <v>1514023</v>
@@ -7445,7 +7445,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G244" t="n">
-        <v>10.7779493331909</v>
+        <v>10.7779502868652</v>
       </c>
       <c r="H244" t="n">
         <v>1984750</v>
@@ -7532,7 +7532,7 @@
         <v>12.835000038147</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2421760559082</v>
+        <v>11.2421770095825</v>
       </c>
       <c r="H247" t="n">
         <v>2121501</v>
@@ -7561,7 +7561,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>11.364803314209</v>
+        <v>11.3648023605347</v>
       </c>
       <c r="H248" t="n">
         <v>1451807</v>
@@ -7590,7 +7590,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G249" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H249" t="n">
         <v>1758416</v>
@@ -7706,7 +7706,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G253" t="n">
-        <v>11.5969152450562</v>
+        <v>11.5969161987305</v>
       </c>
       <c r="H253" t="n">
         <v>2241663</v>
@@ -7793,7 +7793,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7064027786255</v>
+        <v>11.7064037322998</v>
       </c>
       <c r="H256" t="n">
         <v>1216893</v>
@@ -7851,7 +7851,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4158821105957</v>
+        <v>12.41588306427</v>
       </c>
       <c r="H258" t="n">
         <v>1932782</v>
@@ -7938,7 +7938,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>12.1093168258667</v>
+        <v>12.109317779541</v>
       </c>
       <c r="H261" t="n">
         <v>1747187</v>
@@ -7996,7 +7996,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>11.5925369262695</v>
+        <v>11.5925359725952</v>
       </c>
       <c r="H263" t="n">
         <v>958247</v>
@@ -8054,7 +8054,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G265" t="n">
-        <v>12.0961799621582</v>
+        <v>12.0961790084839</v>
       </c>
       <c r="H265" t="n">
         <v>1434728</v>
@@ -8228,7 +8228,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>12.4377794265747</v>
+        <v>12.437780380249</v>
       </c>
       <c r="H271" t="n">
         <v>1908938</v>
@@ -8286,7 +8286,7 @@
         <v>13.75</v>
       </c>
       <c r="G273" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H273" t="n">
         <v>2775322</v>
@@ -8344,7 +8344,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9633207321167</v>
+        <v>12.9633197784424</v>
       </c>
       <c r="H275" t="n">
         <v>5535828</v>
@@ -8402,7 +8402,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>13.7297334671021</v>
+        <v>13.7297325134277</v>
       </c>
       <c r="H277" t="n">
         <v>1882233</v>
@@ -8779,7 +8779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H290" t="n">
         <v>2146952</v>
@@ -8808,7 +8808,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G291" t="n">
-        <v>12.4027442932129</v>
+        <v>12.4027433395386</v>
       </c>
       <c r="H291" t="n">
         <v>1927982</v>
@@ -8866,7 +8866,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0421514511108</v>
+        <v>13.0421504974365</v>
       </c>
       <c r="H293" t="n">
         <v>2273544</v>
@@ -9011,7 +9011,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G298" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H298" t="n">
         <v>1951339</v>
@@ -9069,7 +9069,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G300" t="n">
-        <v>13.2173318862915</v>
+        <v>13.2173309326172</v>
       </c>
       <c r="H300" t="n">
         <v>2681030</v>
@@ -9098,7 +9098,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H301" t="n">
         <v>1976724</v>
@@ -9243,7 +9243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H306" t="n">
         <v>789545</v>
@@ -9272,7 +9272,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>14.08447265625</v>
+        <v>14.0844717025757</v>
       </c>
       <c r="H307" t="n">
         <v>1481451</v>
@@ -9301,7 +9301,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>14.1676816940308</v>
+        <v>14.1676826477051</v>
       </c>
       <c r="H308" t="n">
         <v>1427993</v>
@@ -9649,7 +9649,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H320" t="n">
         <v>751306</v>
@@ -9736,7 +9736,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H323" t="n">
         <v>1347320</v>
@@ -9823,7 +9823,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2830228805542</v>
+        <v>13.2830238342285</v>
       </c>
       <c r="H326" t="n">
         <v>2302146</v>
@@ -9997,7 +9997,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H332" t="n">
         <v>1586679</v>
@@ -10113,7 +10113,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H336" t="n">
         <v>1426352</v>
@@ -10432,7 +10432,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>13.0640487670898</v>
+        <v>13.0640478134155</v>
       </c>
       <c r="H347" t="n">
         <v>1338759</v>
@@ -10461,7 +10461,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G348" t="n">
-        <v>13.3093004226685</v>
+        <v>13.3092994689941</v>
       </c>
       <c r="H348" t="n">
         <v>1559177</v>
@@ -10490,7 +10490,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2698850631714</v>
+        <v>13.2698841094971</v>
       </c>
       <c r="H349" t="n">
         <v>1544266</v>
@@ -10519,7 +10519,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G350" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H350" t="n">
         <v>1972210</v>
@@ -10635,7 +10635,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H354" t="n">
         <v>1346763</v>
@@ -10664,7 +10664,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G355" t="n">
-        <v>14.3472414016724</v>
+        <v>14.347240447998</v>
       </c>
       <c r="H355" t="n">
         <v>5409872</v>
@@ -10751,7 +10751,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.7589149475098</v>
+        <v>14.7589159011841</v>
       </c>
       <c r="H358" t="n">
         <v>1934006</v>
@@ -10780,7 +10780,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G359" t="n">
-        <v>15.0129261016846</v>
+        <v>15.0129251480103</v>
       </c>
       <c r="H359" t="n">
         <v>3312824</v>
@@ -10809,7 +10809,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G360" t="n">
-        <v>14.7326364517212</v>
+        <v>14.7326374053955</v>
       </c>
       <c r="H360" t="n">
         <v>2172743</v>
@@ -10838,7 +10838,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H361" t="n">
         <v>6220421</v>
@@ -10867,7 +10867,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>14.807089805603</v>
+        <v>14.8070907592773</v>
       </c>
       <c r="H362" t="n">
         <v>1859135</v>
@@ -10925,7 +10925,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G364" t="n">
-        <v>15.1048955917358</v>
+        <v>15.1048965454102</v>
       </c>
       <c r="H364" t="n">
         <v>2468365</v>
@@ -10954,7 +10954,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>14.8289880752563</v>
+        <v>14.828987121582</v>
       </c>
       <c r="H365" t="n">
         <v>2076177</v>
@@ -11099,7 +11099,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>15.2713165283203</v>
+        <v>15.271315574646</v>
       </c>
       <c r="H370" t="n">
         <v>1621092</v>
@@ -11157,7 +11157,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G372" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H372" t="n">
         <v>9316387</v>
@@ -11215,7 +11215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H374" t="n">
         <v>11767886</v>
@@ -11418,7 +11418,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G381" t="n">
-        <v>13.5720710754395</v>
+        <v>13.5720701217651</v>
       </c>
       <c r="H381" t="n">
         <v>2422964</v>
@@ -11824,7 +11824,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G395" t="n">
-        <v>12.4903345108032</v>
+        <v>12.4903335571289</v>
       </c>
       <c r="H395" t="n">
         <v>2903678</v>
@@ -11853,7 +11853,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>12.7925186157227</v>
+        <v>12.792519569397</v>
       </c>
       <c r="H396" t="n">
         <v>3122264</v>
@@ -11911,7 +11911,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H398" t="n">
         <v>4107139</v>
@@ -12027,7 +12027,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G402" t="n">
-        <v>12.9720792770386</v>
+        <v>12.9720802307129</v>
       </c>
       <c r="H402" t="n">
         <v>5169259</v>
@@ -12056,7 +12056,7 @@
         <v>14.75</v>
       </c>
       <c r="G403" t="n">
-        <v>12.9195241928101</v>
+        <v>12.9195251464844</v>
       </c>
       <c r="H403" t="n">
         <v>2543067</v>
@@ -12085,7 +12085,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3268184661865</v>
+        <v>13.3268194198608</v>
       </c>
       <c r="H404" t="n">
         <v>4310917</v>
@@ -12172,7 +12172,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H407" t="n">
         <v>2089039</v>
@@ -12259,7 +12259,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G410" t="n">
-        <v>13.7866649627686</v>
+        <v>13.7866659164429</v>
       </c>
       <c r="H410" t="n">
         <v>1109598</v>
@@ -12462,7 +12462,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>14.1457843780518</v>
+        <v>14.1457853317261</v>
       </c>
       <c r="H417" t="n">
         <v>2242500</v>
@@ -12607,7 +12607,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>14.1019897460938</v>
+        <v>14.1019906997681</v>
       </c>
       <c r="H422" t="n">
         <v>1989341</v>
@@ -12636,7 +12636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>13.9706048965454</v>
+        <v>13.9706039428711</v>
       </c>
       <c r="H423" t="n">
         <v>2142576</v>
@@ -12694,7 +12694,7 @@
         <v>16.5</v>
       </c>
       <c r="G425" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H425" t="n">
         <v>1983336</v>
@@ -12752,7 +12752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>13.9268102645874</v>
+        <v>13.9268093109131</v>
       </c>
       <c r="H427" t="n">
         <v>2084445</v>
@@ -12839,7 +12839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>14.3647594451904</v>
+        <v>14.3647603988647</v>
       </c>
       <c r="H430" t="n">
         <v>866995</v>
@@ -13042,7 +13042,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8873949050903</v>
+        <v>13.887393951416</v>
       </c>
       <c r="H437" t="n">
         <v>1424464</v>
@@ -13216,7 +13216,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G443" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H443" t="n">
         <v>868815</v>
@@ -13332,7 +13332,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>13.186674118042</v>
+        <v>13.1866750717163</v>
       </c>
       <c r="H447" t="n">
         <v>1723759</v>
@@ -13361,7 +13361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>12.6567554473877</v>
+        <v>12.6567544937134</v>
       </c>
       <c r="H448" t="n">
         <v>2492374</v>
@@ -13390,7 +13390,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H449" t="n">
         <v>2053607</v>
@@ -13535,7 +13535,7 @@
         <v>15.375</v>
       </c>
       <c r="G454" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H454" t="n">
         <v>1708403</v>
@@ -13680,7 +13680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H459" t="n">
         <v>2709406</v>
@@ -13999,7 +13999,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2348480224609</v>
+        <v>13.2348489761353</v>
       </c>
       <c r="H470" t="n">
         <v>2547572</v>
@@ -14057,7 +14057,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G472" t="n">
-        <v>13.0377712249756</v>
+        <v>13.0377721786499</v>
       </c>
       <c r="H472" t="n">
         <v>1878486</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>13.3925104141235</v>
+        <v>13.3925113677979</v>
       </c>
       <c r="H473" t="n">
         <v>2222285</v>
@@ -14289,7 +14289,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G480" t="n">
-        <v>13.1122236251831</v>
+        <v>13.1122226715088</v>
       </c>
       <c r="H480" t="n">
         <v>2250493</v>
@@ -14376,7 +14376,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G483" t="n">
-        <v>13.0027360916138</v>
+        <v>13.0027351379395</v>
       </c>
       <c r="H483" t="n">
         <v>3154224</v>
@@ -14492,7 +14492,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>12.8450736999512</v>
+        <v>12.8450727462769</v>
       </c>
       <c r="H487" t="n">
         <v>3568564</v>
@@ -14550,7 +14550,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G489" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H489" t="n">
         <v>1783861</v>
@@ -14579,7 +14579,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>13.1516389846802</v>
+        <v>13.1516380310059</v>
       </c>
       <c r="H490" t="n">
         <v>2030263</v>
@@ -14666,7 +14666,7 @@
         <v>14.5749998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>12.766242980957</v>
+        <v>12.7662420272827</v>
       </c>
       <c r="H493" t="n">
         <v>1059699</v>
@@ -14695,7 +14695,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G494" t="n">
-        <v>12.8187961578369</v>
+        <v>12.8187971115112</v>
       </c>
       <c r="H494" t="n">
         <v>1265651</v>
@@ -14753,7 +14753,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>13.0202541351318</v>
+        <v>13.0202531814575</v>
       </c>
       <c r="H496" t="n">
         <v>1214135</v>
@@ -14840,7 +14840,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>13.3049201965332</v>
+        <v>13.3049211502075</v>
       </c>
       <c r="H499" t="n">
         <v>3376944</v>
@@ -14869,7 +14869,7 @@
         <v>15.375</v>
       </c>
       <c r="G500" t="n">
-        <v>13.4669628143311</v>
+        <v>13.4669618606567</v>
       </c>
       <c r="H500" t="n">
         <v>2363121</v>
@@ -15101,7 +15101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G508" t="n">
-        <v>13.2260894775391</v>
+        <v>13.2260904312134</v>
       </c>
       <c r="H508" t="n">
         <v>1944425</v>
@@ -15130,7 +15130,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>13.8830156326294</v>
+        <v>13.8830146789551</v>
       </c>
       <c r="H509" t="n">
         <v>4613486</v>
@@ -15362,7 +15362,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G517" t="n">
-        <v>13.427547454834</v>
+        <v>13.4275465011597</v>
       </c>
       <c r="H517" t="n">
         <v>2397331</v>
@@ -15536,7 +15536,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>13.2786436080933</v>
+        <v>13.2786445617676</v>
       </c>
       <c r="H523" t="n">
         <v>1494446</v>
@@ -15652,7 +15652,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9005327224731</v>
+        <v>13.9005336761475</v>
       </c>
       <c r="H527" t="n">
         <v>1844844</v>
@@ -15971,7 +15971,7 @@
         <v>16.625</v>
       </c>
       <c r="G538" t="n">
-        <v>14.5618371963501</v>
+        <v>14.5618381500244</v>
       </c>
       <c r="H538" t="n">
         <v>792755</v>
@@ -16000,7 +16000,7 @@
         <v>16.5</v>
       </c>
       <c r="G539" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H539" t="n">
         <v>1139352</v>
@@ -16029,7 +16029,7 @@
         <v>16.5</v>
       </c>
       <c r="G540" t="n">
-        <v>14.4523496627808</v>
+        <v>14.4523506164551</v>
       </c>
       <c r="H540" t="n">
         <v>1023037</v>
@@ -16087,7 +16087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>14.8465051651001</v>
+        <v>14.8465061187744</v>
       </c>
       <c r="H542" t="n">
         <v>2528000</v>
@@ -16116,7 +16116,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2537994384766</v>
+        <v>15.2537984848022</v>
       </c>
       <c r="H543" t="n">
         <v>2974626</v>
@@ -16174,7 +16174,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H545" t="n">
         <v>1350509</v>
@@ -16203,7 +16203,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G546" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H546" t="n">
         <v>1405497</v>
@@ -16319,7 +16319,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G550" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H550" t="n">
         <v>3108460</v>
@@ -16406,7 +16406,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H553" t="n">
         <v>1599475</v>
@@ -16435,7 +16435,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G554" t="n">
-        <v>16.322395324707</v>
+        <v>16.3223972320557</v>
       </c>
       <c r="H554" t="n">
         <v>2723421</v>
@@ -16580,7 +16580,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G559" t="n">
-        <v>16.4056072235107</v>
+        <v>16.4056053161621</v>
       </c>
       <c r="H559" t="n">
         <v>2131180</v>
@@ -16609,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="G560" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H560" t="n">
         <v>2410116</v>
@@ -16638,7 +16638,7 @@
         <v>19</v>
       </c>
       <c r="G561" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H561" t="n">
         <v>1178309</v>
@@ -16696,7 +16696,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>16.9968414306641</v>
+        <v>16.9968395233154</v>
       </c>
       <c r="H563" t="n">
         <v>1682501</v>
@@ -16812,7 +16812,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G567" t="n">
-        <v>16.4756774902344</v>
+        <v>16.475679397583</v>
       </c>
       <c r="H567" t="n">
         <v>953443</v>
@@ -16870,7 +16870,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G569" t="n">
-        <v>15.9588966369629</v>
+        <v>15.9588975906372</v>
       </c>
       <c r="H569" t="n">
         <v>1179598</v>
@@ -16928,7 +16928,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>15.6348161697388</v>
+        <v>15.6348142623901</v>
       </c>
       <c r="H571" t="n">
         <v>1681505</v>
@@ -16986,7 +16986,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>16.0640048980713</v>
+        <v>16.0640068054199</v>
       </c>
       <c r="H573" t="n">
         <v>1129313</v>
@@ -17044,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="G575" t="n">
-        <v>16.6421012878418</v>
+        <v>16.6420993804932</v>
       </c>
       <c r="H575" t="n">
         <v>1260998</v>
@@ -17131,7 +17131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>16.3793296813965</v>
+        <v>16.3793315887451</v>
       </c>
       <c r="H578" t="n">
         <v>1184145</v>
@@ -17189,7 +17189,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G580" t="n">
-        <v>15.8362722396851</v>
+        <v>15.8362712860107</v>
       </c>
       <c r="H580" t="n">
         <v>2580554</v>
@@ -17218,7 +17218,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>15.862548828125</v>
+        <v>15.8625497817993</v>
       </c>
       <c r="H581" t="n">
         <v>1586660</v>
@@ -17247,7 +17247,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>15.5034313201904</v>
+        <v>15.5034303665161</v>
       </c>
       <c r="H582" t="n">
         <v>2081489</v>
@@ -17392,7 +17392,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>15.2581777572632</v>
+        <v>15.2581787109375</v>
       </c>
       <c r="H587" t="n">
         <v>976030</v>
@@ -17421,7 +17421,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>15.2756958007812</v>
+        <v>15.2756967544556</v>
       </c>
       <c r="H588" t="n">
         <v>1093429</v>
@@ -17450,7 +17450,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3238706588745</v>
+        <v>15.3238716125488</v>
       </c>
       <c r="H589" t="n">
         <v>1150543</v>
@@ -17508,7 +17508,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G591" t="n">
-        <v>15.1662092208862</v>
+        <v>15.1662082672119</v>
       </c>
       <c r="H591" t="n">
         <v>840155</v>
@@ -17595,7 +17595,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>15.4027004241943</v>
+        <v>15.4027013778687</v>
       </c>
       <c r="H594" t="n">
         <v>1145708</v>
@@ -17624,7 +17624,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H595" t="n">
         <v>846543</v>
@@ -17682,7 +17682,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G597" t="n">
-        <v>15.4771528244019</v>
+        <v>15.4771518707275</v>
       </c>
       <c r="H597" t="n">
         <v>1528852</v>
@@ -17711,7 +17711,7 @@
         <v>17.5550003051758</v>
       </c>
       <c r="G598" t="n">
-        <v>15.376425743103</v>
+        <v>15.3764247894287</v>
       </c>
       <c r="H598" t="n">
         <v>980332</v>
@@ -17827,7 +17827,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.4552564620972</v>
+        <v>15.4552555084229</v>
       </c>
       <c r="H602" t="n">
         <v>1140133</v>
@@ -17856,7 +17856,7 @@
         <v>17.9750003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>15.7443027496338</v>
+        <v>15.7443017959595</v>
       </c>
       <c r="H603" t="n">
         <v>1369897</v>
@@ -17972,7 +17972,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G607" t="n">
-        <v>15.8844470977783</v>
+        <v>15.884446144104</v>
       </c>
       <c r="H607" t="n">
         <v>1348033</v>
@@ -18030,7 +18030,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6873683929443</v>
+        <v>15.6873693466187</v>
       </c>
       <c r="H609" t="n">
         <v>1050825</v>
@@ -18059,7 +18059,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G610" t="n">
-        <v>15.6304349899292</v>
+        <v>15.6304340362549</v>
       </c>
       <c r="H610" t="n">
         <v>1064797</v>
@@ -18117,7 +18117,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G612" t="n">
-        <v>15.643575668335</v>
+        <v>15.6435747146606</v>
       </c>
       <c r="H612" t="n">
         <v>1086590</v>
@@ -18175,7 +18175,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>15.8275127410889</v>
+        <v>15.8275136947632</v>
       </c>
       <c r="H614" t="n">
         <v>1611355</v>
@@ -18204,7 +18204,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>15.9676561355591</v>
+        <v>15.9676570892334</v>
       </c>
       <c r="H615" t="n">
         <v>11373620</v>
@@ -18233,7 +18233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>15.4683933258057</v>
+        <v>15.46839427948</v>
       </c>
       <c r="H616" t="n">
         <v>1629554</v>
@@ -18291,7 +18291,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G618" t="n">
-        <v>15.3413877487183</v>
+        <v>15.3413887023926</v>
       </c>
       <c r="H618" t="n">
         <v>2389002</v>
@@ -18349,7 +18349,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G620" t="n">
-        <v>15.3545274734497</v>
+        <v>15.354528427124</v>
       </c>
       <c r="H620" t="n">
         <v>1403719</v>
@@ -18494,7 +18494,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>14.2421350479126</v>
+        <v>14.2421340942383</v>
       </c>
       <c r="H625" t="n">
         <v>1841714</v>
@@ -18871,7 +18871,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>14.8684034347534</v>
+        <v>14.8684024810791</v>
       </c>
       <c r="H638" t="n">
         <v>1070860</v>
@@ -18929,7 +18929,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>15.1530685424805</v>
+        <v>15.1530694961548</v>
       </c>
       <c r="H640" t="n">
         <v>1826178</v>
@@ -18958,7 +18958,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>15.3501472473145</v>
+        <v>15.3501462936401</v>
       </c>
       <c r="H641" t="n">
         <v>1427830</v>
@@ -18987,7 +18987,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G642" t="n">
-        <v>15.4246006011963</v>
+        <v>15.424599647522</v>
       </c>
       <c r="H642" t="n">
         <v>1649351</v>
@@ -19103,7 +19103,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8056583404541</v>
+        <v>12.8056573867798</v>
       </c>
       <c r="H646" t="n">
         <v>4487653</v>
@@ -19161,7 +19161,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G648" t="n">
-        <v>12.7355861663818</v>
+        <v>12.7355852127075</v>
       </c>
       <c r="H648" t="n">
         <v>6176580</v>
@@ -19190,7 +19190,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9326639175415</v>
+        <v>12.9326629638672</v>
       </c>
       <c r="H649" t="n">
         <v>4801454</v>
@@ -19364,7 +19364,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6640405654907</v>
+        <v>13.6640396118164</v>
       </c>
       <c r="H655" t="n">
         <v>4817037</v>
@@ -19422,7 +19422,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.4319257736206</v>
+        <v>13.4319267272949</v>
       </c>
       <c r="H657" t="n">
         <v>2524288</v>
@@ -19451,7 +19451,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G658" t="n">
-        <v>12.8144178390503</v>
+        <v>12.814416885376</v>
       </c>
       <c r="H658" t="n">
         <v>5154019</v>
@@ -19480,7 +19480,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>12.7574834823608</v>
+        <v>12.7574825286865</v>
       </c>
       <c r="H659" t="n">
         <v>3118735</v>
@@ -19538,7 +19538,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>12.1224555969238</v>
+        <v>12.1224565505981</v>
       </c>
       <c r="H661" t="n">
         <v>4296263</v>
@@ -19596,7 +19596,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G663" t="n">
-        <v>12.2450819015503</v>
+        <v>12.245080947876</v>
       </c>
       <c r="H663" t="n">
         <v>2825890</v>
@@ -19654,7 +19654,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.0217275619507</v>
+        <v>12.021728515625</v>
       </c>
       <c r="H665" t="n">
         <v>3364412</v>
@@ -19683,7 +19683,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>12.0830402374268</v>
+        <v>12.0830411911011</v>
       </c>
       <c r="H666" t="n">
         <v>2386822</v>
@@ -19770,7 +19770,7 @@
         <v>13.75</v>
       </c>
       <c r="G669" t="n">
-        <v>12.0436248779297</v>
+        <v>12.043625831604</v>
       </c>
       <c r="H669" t="n">
         <v>3052129</v>
@@ -19973,7 +19973,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>12.3282918930054</v>
+        <v>12.3282928466797</v>
       </c>
       <c r="H676" t="n">
         <v>1521649</v>
@@ -20089,7 +20089,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G680" t="n">
-        <v>12.2231845855713</v>
+        <v>12.223183631897</v>
       </c>
       <c r="H680" t="n">
         <v>3069336</v>
@@ -20118,7 +20118,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>11.8684453964233</v>
+        <v>11.868444442749</v>
       </c>
       <c r="H681" t="n">
         <v>1598437</v>
@@ -20176,7 +20176,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>12.1618709564209</v>
+        <v>12.1618719100952</v>
       </c>
       <c r="H683" t="n">
         <v>1392853</v>
@@ -20205,7 +20205,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G684" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H684" t="n">
         <v>1706869</v>
@@ -20263,7 +20263,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3764667510986</v>
+        <v>12.3764677047729</v>
       </c>
       <c r="H686" t="n">
         <v>1225193</v>
@@ -20321,7 +20321,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>12.2538414001465</v>
+        <v>12.2538404464722</v>
       </c>
       <c r="H688" t="n">
         <v>1316569</v>
@@ -20350,7 +20350,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G689" t="n">
-        <v>12.5385084152222</v>
+        <v>12.5385074615479</v>
       </c>
       <c r="H689" t="n">
         <v>2542343</v>
@@ -20553,7 +20553,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>12.0348663330078</v>
+        <v>12.0348653793335</v>
       </c>
       <c r="H696" t="n">
         <v>1311153</v>
@@ -20611,7 +20611,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>11.8553056716919</v>
+        <v>11.8553066253662</v>
       </c>
       <c r="H698" t="n">
         <v>1288376</v>
@@ -20669,7 +20669,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G700" t="n">
-        <v>11.6407117843628</v>
+        <v>11.6407108306885</v>
       </c>
       <c r="H700" t="n">
         <v>2357420</v>
@@ -20698,7 +20698,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G701" t="n">
-        <v>11.9516553878784</v>
+        <v>11.9516563415527</v>
       </c>
       <c r="H701" t="n">
         <v>2477698</v>
@@ -20756,7 +20756,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>11.9472770690918</v>
+        <v>11.9472761154175</v>
       </c>
       <c r="H703" t="n">
         <v>1586180</v>
@@ -20814,7 +20814,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G705" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H705" t="n">
         <v>2416590</v>
@@ -20843,7 +20843,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G706" t="n">
-        <v>11.4348754882812</v>
+        <v>11.4348745346069</v>
       </c>
       <c r="H706" t="n">
         <v>1813073</v>
@@ -20901,7 +20901,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>11.1370677947998</v>
+        <v>11.1370687484741</v>
       </c>
       <c r="H708" t="n">
         <v>2591864</v>
@@ -21191,7 +21191,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0932731628418</v>
+        <v>11.0932741165161</v>
       </c>
       <c r="H718" t="n">
         <v>5326328</v>
@@ -21365,7 +21365,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G724" t="n">
-        <v>10.8786783218384</v>
+        <v>10.8786773681641</v>
       </c>
       <c r="H724" t="n">
         <v>2057268</v>
@@ -21539,7 +21539,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G730" t="n">
-        <v>10.2173738479614</v>
+        <v>10.2173728942871</v>
       </c>
       <c r="H730" t="n">
         <v>3834386</v>
@@ -21626,7 +21626,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>9.16629314422607</v>
+        <v>9.16629409790039</v>
       </c>
       <c r="H733" t="n">
         <v>3834345</v>
@@ -21655,7 +21655,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>8.93418025970459</v>
+        <v>8.93417930603027</v>
       </c>
       <c r="H734" t="n">
         <v>5360128</v>
@@ -22148,7 +22148,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G751" t="n">
-        <v>9.60862255096436</v>
+        <v>9.60862350463867</v>
       </c>
       <c r="H751" t="n">
         <v>3193494</v>
@@ -22206,7 +22206,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G753" t="n">
-        <v>9.04804611206055</v>
+        <v>9.04804706573486</v>
       </c>
       <c r="H753" t="n">
         <v>3768221</v>
@@ -22293,7 +22293,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G756" t="n">
-        <v>8.53652095794678</v>
+        <v>8.53652191162109</v>
       </c>
       <c r="H756" t="n">
         <v>3814721</v>
@@ -22322,7 +22322,7 @@
         <v>9.55599975585938</v>
       </c>
       <c r="G757" t="n">
-        <v>8.3701000213623</v>
+        <v>8.37010097503662</v>
       </c>
       <c r="H757" t="n">
         <v>3362218</v>
@@ -22351,7 +22351,7 @@
         <v>9.46599960327148</v>
       </c>
       <c r="G758" t="n">
-        <v>8.29126834869385</v>
+        <v>8.29126930236816</v>
       </c>
       <c r="H758" t="n">
         <v>4531767</v>
@@ -22409,7 +22409,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G760" t="n">
-        <v>8.17740345001221</v>
+        <v>8.17740249633789</v>
       </c>
       <c r="H760" t="n">
         <v>3633642</v>
@@ -22438,7 +22438,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G761" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H761" t="n">
         <v>5379177</v>
@@ -22496,7 +22496,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>7.91813611984253</v>
+        <v>7.91813564300537</v>
       </c>
       <c r="H763" t="n">
         <v>2615780</v>
@@ -22583,7 +22583,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G766" t="n">
-        <v>7.94441270828247</v>
+        <v>7.94441318511963</v>
       </c>
       <c r="H766" t="n">
         <v>2412535</v>
@@ -22641,7 +22641,7 @@
         <v>8.76599979400635</v>
       </c>
       <c r="G768" t="n">
-        <v>7.67813873291016</v>
+        <v>7.67813968658447</v>
       </c>
       <c r="H768" t="n">
         <v>2278134</v>
@@ -22670,7 +22670,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G769" t="n">
-        <v>8.01448440551758</v>
+        <v>8.01448535919189</v>
       </c>
       <c r="H769" t="n">
         <v>3712991</v>
@@ -22815,7 +22815,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>8.25097751617432</v>
+        <v>8.25097846984863</v>
       </c>
       <c r="H774" t="n">
         <v>1375278</v>
@@ -22931,7 +22931,7 @@
         <v>9.18400001525879</v>
       </c>
       <c r="G778" t="n">
-        <v>8.04426574707031</v>
+        <v>8.044264793396</v>
       </c>
       <c r="H778" t="n">
         <v>2754791</v>
@@ -22989,7 +22989,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G780" t="n">
-        <v>7.95842790603638</v>
+        <v>7.95842742919922</v>
       </c>
       <c r="H780" t="n">
         <v>6585720</v>
@@ -23047,7 +23047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>7.53274011611938</v>
+        <v>7.53274059295654</v>
       </c>
       <c r="H782" t="n">
         <v>4812379</v>
@@ -23076,7 +23076,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>7.84806394577026</v>
+        <v>7.84806346893311</v>
       </c>
       <c r="H783" t="n">
         <v>5796601</v>
@@ -23105,7 +23105,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>7.52398061752319</v>
+        <v>7.52398109436035</v>
       </c>
       <c r="H784" t="n">
         <v>3843193</v>
@@ -23308,7 +23308,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G791" t="n">
-        <v>8.49622917175293</v>
+        <v>8.49623012542725</v>
       </c>
       <c r="H791" t="n">
         <v>2679229</v>
@@ -23337,7 +23337,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.50498867034912</v>
+        <v>8.50498962402344</v>
       </c>
       <c r="H792" t="n">
         <v>2515602</v>
@@ -23656,7 +23656,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>6.40282917022705</v>
+        <v>6.40282869338989</v>
       </c>
       <c r="H803" t="n">
         <v>4706601</v>
@@ -23743,7 +23743,7 @@
         <v>8.10400009155273</v>
       </c>
       <c r="G806" t="n">
-        <v>7.09829330444336</v>
+        <v>7.09829378128052</v>
       </c>
       <c r="H806" t="n">
         <v>4960400</v>
@@ -23917,7 +23917,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G812" t="n">
-        <v>7.05449867248535</v>
+        <v>7.05449819564819</v>
       </c>
       <c r="H812" t="n">
         <v>2012475</v>
@@ -23946,7 +23946,7 @@
         <v>8.06599998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>7.06500959396362</v>
+        <v>7.06500911712646</v>
       </c>
       <c r="H813" t="n">
         <v>2376055</v>
@@ -24033,7 +24033,7 @@
         <v>7.8439998626709</v>
       </c>
       <c r="G816" t="n">
-        <v>6.87055921554565</v>
+        <v>6.87055969238281</v>
       </c>
       <c r="H816" t="n">
         <v>1879813</v>
@@ -24062,7 +24062,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H817" t="n">
         <v>1250456</v>
@@ -24149,7 +24149,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>7.23668575286865</v>
+        <v>7.23668622970581</v>
       </c>
       <c r="H820" t="n">
         <v>2615104</v>
@@ -24236,7 +24236,7 @@
         <v>8.24199962615967</v>
       </c>
       <c r="G823" t="n">
-        <v>7.21916770935059</v>
+        <v>7.21916723251343</v>
       </c>
       <c r="H823" t="n">
         <v>1443312</v>
@@ -24555,7 +24555,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>7.73419666290283</v>
+        <v>7.73419713973999</v>
       </c>
       <c r="H834" t="n">
         <v>4534716</v>
@@ -24700,7 +24700,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G839" t="n">
-        <v>7.76923322677612</v>
+        <v>7.76923274993896</v>
       </c>
       <c r="H839" t="n">
         <v>1591546</v>
@@ -24845,7 +24845,7 @@
         <v>8.79199981689453</v>
       </c>
       <c r="G844" t="n">
-        <v>7.7009129524231</v>
+        <v>7.70091247558594</v>
       </c>
       <c r="H844" t="n">
         <v>1254654</v>
@@ -24874,7 +24874,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G845" t="n">
-        <v>7.77098512649536</v>
+        <v>7.77098417282104</v>
       </c>
       <c r="H845" t="n">
         <v>1599063</v>
@@ -24990,7 +24990,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G849" t="n">
-        <v>7.94791698455811</v>
+        <v>7.94791650772095</v>
       </c>
       <c r="H849" t="n">
         <v>2438094</v>
@@ -25019,7 +25019,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G850" t="n">
-        <v>7.76222658157349</v>
+        <v>7.76222610473633</v>
       </c>
       <c r="H850" t="n">
         <v>1947615</v>
@@ -25048,7 +25048,7 @@
         <v>8.62399959564209</v>
       </c>
       <c r="G851" t="n">
-        <v>7.55376148223877</v>
+        <v>7.55376100540161</v>
       </c>
       <c r="H851" t="n">
         <v>1501034</v>
@@ -25135,7 +25135,7 @@
         <v>8.52400016784668</v>
       </c>
       <c r="G854" t="n">
-        <v>7.46617126464844</v>
+        <v>7.4661717414856</v>
       </c>
       <c r="H854" t="n">
         <v>1162035</v>
@@ -25309,7 +25309,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G860" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H860" t="n">
         <v>1769750</v>
@@ -25338,7 +25338,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G861" t="n">
-        <v>7.22267198562622</v>
+        <v>7.22267150878906</v>
       </c>
       <c r="H861" t="n">
         <v>1253026</v>
@@ -25367,7 +25367,7 @@
         <v>8.37399959564209</v>
       </c>
       <c r="G862" t="n">
-        <v>7.33478593826294</v>
+        <v>7.3347864151001</v>
       </c>
       <c r="H862" t="n">
         <v>1335409</v>
@@ -25396,7 +25396,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>7.18237972259521</v>
+        <v>7.18238019943237</v>
       </c>
       <c r="H863" t="n">
         <v>1791220</v>
@@ -25541,7 +25541,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G868" t="n">
-        <v>7.72543716430664</v>
+        <v>7.72543811798096</v>
       </c>
       <c r="H868" t="n">
         <v>3777309</v>
@@ -25570,7 +25570,7 @@
         <v>8.94799995422363</v>
       </c>
       <c r="G869" t="n">
-        <v>7.83755302429199</v>
+        <v>7.83755254745483</v>
       </c>
       <c r="H869" t="n">
         <v>2087846</v>
@@ -25599,7 +25599,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>7.62908887863159</v>
+        <v>7.62908935546875</v>
       </c>
       <c r="H870" t="n">
         <v>4224077</v>
@@ -25628,7 +25628,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G871" t="n">
-        <v>7.63784790039062</v>
+        <v>7.63784837722778</v>
       </c>
       <c r="H871" t="n">
         <v>1662381</v>
@@ -25657,7 +25657,7 @@
         <v>8.8439998626709</v>
       </c>
       <c r="G872" t="n">
-        <v>7.74645948410034</v>
+        <v>7.7464599609375</v>
       </c>
       <c r="H872" t="n">
         <v>2180023</v>
@@ -25715,7 +25715,7 @@
         <v>8.75</v>
       </c>
       <c r="G874" t="n">
-        <v>7.66412544250488</v>
+        <v>7.66412496566772</v>
       </c>
       <c r="H874" t="n">
         <v>1817933</v>
@@ -25773,7 +25773,7 @@
         <v>8.41600036621094</v>
       </c>
       <c r="G876" t="n">
-        <v>7.37157440185547</v>
+        <v>7.37157487869263</v>
       </c>
       <c r="H876" t="n">
         <v>1841179</v>
@@ -25802,7 +25802,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G877" t="n">
-        <v>7.5695276260376</v>
+        <v>7.56952810287476</v>
       </c>
       <c r="H877" t="n">
         <v>4359444</v>
@@ -25831,7 +25831,7 @@
         <v>8.39400005340576</v>
       </c>
       <c r="G878" t="n">
-        <v>7.35230493545532</v>
+        <v>7.35230445861816</v>
       </c>
       <c r="H878" t="n">
         <v>2596029</v>
@@ -25889,7 +25889,7 @@
         <v>8.34200000762939</v>
       </c>
       <c r="G880" t="n">
-        <v>7.30675792694092</v>
+        <v>7.30675745010376</v>
       </c>
       <c r="H880" t="n">
         <v>1872375</v>
@@ -25976,7 +25976,7 @@
         <v>8.68200016021729</v>
       </c>
       <c r="G883" t="n">
-        <v>7.60456418991089</v>
+        <v>7.60456371307373</v>
       </c>
       <c r="H883" t="n">
         <v>2456429</v>
@@ -26005,7 +26005,7 @@
         <v>8.80399990081787</v>
       </c>
       <c r="G884" t="n">
-        <v>7.71142387390137</v>
+        <v>7.71142339706421</v>
       </c>
       <c r="H884" t="n">
         <v>2172994</v>
@@ -26034,7 +26034,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G885" t="n">
-        <v>7.51697397232056</v>
+        <v>7.5169734954834</v>
       </c>
       <c r="H885" t="n">
         <v>2338057</v>
@@ -26063,7 +26063,7 @@
         <v>8.67399978637695</v>
       </c>
       <c r="G886" t="n">
-        <v>7.59755659103394</v>
+        <v>7.59755611419678</v>
       </c>
       <c r="H886" t="n">
         <v>1977697</v>
@@ -26092,7 +26092,7 @@
         <v>8.58600044250488</v>
       </c>
       <c r="G887" t="n">
-        <v>7.52047729492188</v>
+        <v>7.52047777175903</v>
       </c>
       <c r="H887" t="n">
         <v>1474624</v>
@@ -26208,7 +26208,7 @@
         <v>8.87600040435791</v>
       </c>
       <c r="G891" t="n">
-        <v>7.77448844909668</v>
+        <v>7.77448892593384</v>
       </c>
       <c r="H891" t="n">
         <v>2084407</v>
@@ -26237,7 +26237,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>8.06703948974609</v>
+        <v>8.06703853607178</v>
       </c>
       <c r="H892" t="n">
         <v>2942222</v>
@@ -26295,7 +26295,7 @@
         <v>9.01599979400635</v>
       </c>
       <c r="G894" t="n">
-        <v>7.89711427688599</v>
+        <v>7.89711380004883</v>
       </c>
       <c r="H894" t="n">
         <v>1390375</v>
@@ -26324,7 +26324,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G895" t="n">
-        <v>7.67463541030884</v>
+        <v>7.674635887146</v>
       </c>
       <c r="H895" t="n">
         <v>2131072</v>
@@ -26353,7 +26353,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G896" t="n">
-        <v>7.81478023529053</v>
+        <v>7.81477975845337</v>
       </c>
       <c r="H896" t="n">
         <v>1778280</v>
@@ -26440,7 +26440,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G899" t="n">
-        <v>7.75171566009521</v>
+        <v>7.75171518325806</v>
       </c>
       <c r="H899" t="n">
         <v>1994551</v>
@@ -26469,7 +26469,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G900" t="n">
-        <v>7.6466064453125</v>
+        <v>7.64660692214966</v>
       </c>
       <c r="H900" t="n">
         <v>4086053</v>
@@ -26527,7 +26527,7 @@
         <v>8.6879997253418</v>
       </c>
       <c r="G902" t="n">
-        <v>7.60981941223145</v>
+        <v>7.60981893539429</v>
       </c>
       <c r="H902" t="n">
         <v>2012747</v>
@@ -26672,7 +26672,7 @@
         <v>9</v>
       </c>
       <c r="G907" t="n">
-        <v>7.88309955596924</v>
+        <v>7.8831000328064</v>
       </c>
       <c r="H907" t="n">
         <v>2005084</v>
@@ -26701,7 +26701,7 @@
         <v>8.91600036621094</v>
       </c>
       <c r="G908" t="n">
-        <v>7.80952501296997</v>
+        <v>7.80952453613281</v>
       </c>
       <c r="H908" t="n">
         <v>1722881</v>
@@ -26846,7 +26846,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G913" t="n">
-        <v>7.56602430343628</v>
+        <v>7.56602382659912</v>
       </c>
       <c r="H913" t="n">
         <v>6696047</v>
@@ -26904,7 +26904,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G915" t="n">
-        <v>7.56427240371704</v>
+        <v>7.56427192687988</v>
       </c>
       <c r="H915" t="n">
         <v>8360836</v>
@@ -26962,7 +26962,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G917" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H917" t="n">
         <v>4124433</v>
@@ -27049,7 +27049,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G920" t="n">
-        <v>7.49945640563965</v>
+        <v>7.49945592880249</v>
       </c>
       <c r="H920" t="n">
         <v>1758788</v>
@@ -27107,7 +27107,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>7.30500602722168</v>
+        <v>7.30500650405884</v>
       </c>
       <c r="H922" t="n">
         <v>2115103</v>
@@ -27136,7 +27136,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G923" t="n">
-        <v>7.36106443405151</v>
+        <v>7.3610634803772</v>
       </c>
       <c r="H923" t="n">
         <v>5292801</v>
@@ -27165,7 +27165,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G924" t="n">
-        <v>7.408362865448</v>
+        <v>7.40836238861084</v>
       </c>
       <c r="H924" t="n">
         <v>3630338</v>
@@ -27194,7 +27194,7 @@
         <v>8.47799968719482</v>
       </c>
       <c r="G925" t="n">
-        <v>7.42587947845459</v>
+        <v>7.42587995529175</v>
       </c>
       <c r="H925" t="n">
         <v>2397056</v>
@@ -27310,7 +27310,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G929" t="n">
-        <v>6.84953784942627</v>
+        <v>6.84953832626343</v>
       </c>
       <c r="H929" t="n">
         <v>2315074</v>
@@ -27397,7 +27397,7 @@
         <v>7.97599983215332</v>
       </c>
       <c r="G932" t="n">
-        <v>6.98617839813232</v>
+        <v>6.98617792129517</v>
       </c>
       <c r="H932" t="n">
         <v>4237933</v>
@@ -27484,7 +27484,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G935" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H935" t="n">
         <v>21129302</v>
@@ -27542,7 +27542,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G937" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H937" t="n">
         <v>2944585</v>
@@ -27600,7 +27600,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G939" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H939" t="n">
         <v>1511633</v>
@@ -27774,7 +27774,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G945" t="n">
-        <v>6.61129331588745</v>
+        <v>6.61129283905029</v>
       </c>
       <c r="H945" t="n">
         <v>1454723</v>
@@ -27803,7 +27803,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G946" t="n">
-        <v>6.62881088256836</v>
+        <v>6.62881135940552</v>
       </c>
       <c r="H946" t="n">
         <v>2105159</v>
@@ -27832,7 +27832,7 @@
         <v>7.72200012207031</v>
       </c>
       <c r="G947" t="n">
-        <v>6.76370000839233</v>
+        <v>6.76369953155518</v>
       </c>
       <c r="H947" t="n">
         <v>2334406</v>
@@ -27890,7 +27890,7 @@
         <v>7.7519998550415</v>
       </c>
       <c r="G949" t="n">
-        <v>6.78997707366943</v>
+        <v>6.78997659683228</v>
       </c>
       <c r="H949" t="n">
         <v>2631044</v>
@@ -27919,7 +27919,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G950" t="n">
-        <v>6.88632583618164</v>
+        <v>6.88632535934448</v>
       </c>
       <c r="H950" t="n">
         <v>3247942</v>
@@ -27948,7 +27948,7 @@
         <v>7.83599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>6.86355257034302</v>
+        <v>6.86355209350586</v>
       </c>
       <c r="H951" t="n">
         <v>2664326</v>
@@ -28064,7 +28064,7 @@
         <v>8.35200023651123</v>
       </c>
       <c r="G955" t="n">
-        <v>7.31551694869995</v>
+        <v>7.31551742553711</v>
       </c>
       <c r="H955" t="n">
         <v>2024274</v>
@@ -28093,7 +28093,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G956" t="n">
-        <v>7.30325412750244</v>
+        <v>7.3032546043396</v>
       </c>
       <c r="H956" t="n">
         <v>1782038</v>
@@ -28151,7 +28151,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>7.02997350692749</v>
+        <v>7.02997303009033</v>
       </c>
       <c r="H958" t="n">
         <v>3013902</v>
@@ -28325,7 +28325,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G964" t="n">
-        <v>7.1210675239563</v>
+        <v>7.12106704711914</v>
       </c>
       <c r="H964" t="n">
         <v>2411918</v>
@@ -28441,7 +28441,7 @@
         <v>8.70199966430664</v>
       </c>
       <c r="G968" t="n">
-        <v>7.62208127975464</v>
+        <v>7.6220817565918</v>
       </c>
       <c r="H968" t="n">
         <v>5989261</v>
@@ -28470,7 +28470,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>7.41011428833008</v>
+        <v>7.41011381149292</v>
       </c>
       <c r="H969" t="n">
         <v>4191111</v>
@@ -28499,7 +28499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G970" t="n">
-        <v>7.32252407073975</v>
+        <v>7.32252359390259</v>
       </c>
       <c r="H970" t="n">
         <v>3208842</v>
@@ -28528,7 +28528,7 @@
         <v>8.39200019836426</v>
       </c>
       <c r="G971" t="n">
-        <v>7.35055303573608</v>
+        <v>7.35055255889893</v>
       </c>
       <c r="H971" t="n">
         <v>2112796</v>
@@ -28615,7 +28615,7 @@
         <v>8.0939998626709</v>
       </c>
       <c r="G974" t="n">
-        <v>7.08953475952148</v>
+        <v>7.08953428268433</v>
       </c>
       <c r="H974" t="n">
         <v>5498182</v>
@@ -28673,7 +28673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H976" t="n">
         <v>5110690</v>
@@ -28702,7 +28702,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G977" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H977" t="n">
         <v>3267036</v>
@@ -28789,7 +28789,7 @@
         <v>7.69600009918213</v>
       </c>
       <c r="G980" t="n">
-        <v>6.74092626571655</v>
+        <v>6.74092674255371</v>
       </c>
       <c r="H980" t="n">
         <v>3585863</v>
@@ -29021,7 +29021,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G988" t="n">
-        <v>6.64107322692871</v>
+        <v>6.64107370376587</v>
       </c>
       <c r="H988" t="n">
         <v>3157288</v>
@@ -29108,7 +29108,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G991" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H991" t="n">
         <v>10771129</v>
@@ -29398,7 +29398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.46414184570312</v>
+        <v>6.46414232254028</v>
       </c>
       <c r="H1001" t="n">
         <v>3025996</v>
@@ -29485,7 +29485,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1004" t="n">
         <v>3494792</v>
@@ -29514,7 +29514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1005" t="n">
         <v>2518422</v>
@@ -29572,7 +29572,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1007" t="n">
         <v>1699798</v>
@@ -29630,7 +29630,7 @@
         <v>7.48600006103516</v>
       </c>
       <c r="G1009" t="n">
-        <v>6.55698776245117</v>
+        <v>6.55698728561401</v>
       </c>
       <c r="H1009" t="n">
         <v>2978856</v>
@@ -29688,7 +29688,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.43961668014526</v>
+        <v>6.43961715698242</v>
       </c>
       <c r="H1011" t="n">
         <v>2047446</v>
@@ -29746,7 +29746,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1013" t="n">
         <v>1512556</v>
@@ -29775,7 +29775,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.47114896774292</v>
+        <v>6.47114944458008</v>
       </c>
       <c r="H1014" t="n">
         <v>1866277</v>
@@ -29804,7 +29804,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>6.44312047958374</v>
+        <v>6.44312000274658</v>
       </c>
       <c r="H1015" t="n">
         <v>2025165</v>
@@ -29891,7 +29891,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.68662071228027</v>
+        <v>6.68662023544312</v>
       </c>
       <c r="H1018" t="n">
         <v>4636743</v>
@@ -30036,7 +30036,7 @@
         <v>7.64599990844727</v>
       </c>
       <c r="G1023" t="n">
-        <v>6.69713115692139</v>
+        <v>6.69713163375854</v>
       </c>
       <c r="H1023" t="n">
         <v>1826160</v>
@@ -30152,7 +30152,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G1027" t="n">
-        <v>6.57450532913208</v>
+        <v>6.57450580596924</v>
       </c>
       <c r="H1027" t="n">
         <v>2067807</v>
@@ -30239,7 +30239,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.32399797439575</v>
+        <v>6.32399749755859</v>
       </c>
       <c r="H1030" t="n">
         <v>2475818</v>
@@ -30355,7 +30355,7 @@
         <v>7.51800012588501</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.58501672744751</v>
+        <v>6.58501625061035</v>
       </c>
       <c r="H1034" t="n">
         <v>2071544</v>
@@ -30500,7 +30500,7 @@
         <v>7.64799976348877</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.69888305664062</v>
+        <v>6.69888257980347</v>
       </c>
       <c r="H1039" t="n">
         <v>1503048</v>
@@ -30558,7 +30558,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.75143718719482</v>
+        <v>6.75143766403198</v>
       </c>
       <c r="H1041" t="n">
         <v>2513946</v>
@@ -30616,7 +30616,7 @@
         <v>7.77400016784668</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80924701690674</v>
+        <v>6.80924654006958</v>
       </c>
       <c r="H1043" t="n">
         <v>1988489</v>
@@ -30761,7 +30761,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1048" t="n">
         <v>2461658</v>
@@ -30906,7 +30906,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1053" t="n">
         <v>1980867</v>
@@ -30935,7 +30935,7 @@
         <v>7.44399976730347</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52019929885864</v>
+        <v>6.5201997756958</v>
       </c>
       <c r="H1054" t="n">
         <v>2162129</v>
@@ -30964,7 +30964,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1055" t="n">
         <v>2099974</v>
@@ -30993,7 +30993,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.36078548431396</v>
+        <v>6.36078596115112</v>
       </c>
       <c r="H1056" t="n">
         <v>3493699</v>
@@ -31051,7 +31051,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.44662427902222</v>
+        <v>6.44662380218506</v>
       </c>
       <c r="H1058" t="n">
         <v>2381200</v>
@@ -31080,7 +31080,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.47815656661987</v>
+        <v>6.47815608978271</v>
       </c>
       <c r="H1059" t="n">
         <v>2696293</v>
@@ -31167,7 +31167,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1062" t="n">
         <v>2300239</v>
@@ -31196,7 +31196,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.28020334243774</v>
+        <v>6.28020286560059</v>
       </c>
       <c r="H1063" t="n">
         <v>2359706</v>
@@ -31225,7 +31225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1064" t="n">
         <v>2022911</v>
@@ -31283,7 +31283,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1066" t="n">
         <v>3103698</v>
@@ -31312,7 +31312,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.10502243041992</v>
+        <v>6.10502290725708</v>
       </c>
       <c r="H1067" t="n">
         <v>3137889</v>
@@ -31515,7 +31515,7 @@
         <v>7.61800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.67260599136353</v>
+        <v>6.67260646820068</v>
       </c>
       <c r="H1074" t="n">
         <v>5319958</v>
@@ -31747,7 +31747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.48166036605835</v>
+        <v>6.48165988922119</v>
       </c>
       <c r="H1082" t="n">
         <v>4092006</v>
@@ -31776,7 +31776,7 @@
         <v>7.49200010299683</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.56224250793457</v>
+        <v>6.56224298477173</v>
       </c>
       <c r="H1083" t="n">
         <v>2566331</v>
@@ -31834,7 +31834,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.7093939781189</v>
+        <v>6.70939350128174</v>
       </c>
       <c r="H1085" t="n">
         <v>3352608</v>
@@ -31892,7 +31892,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.63932180404663</v>
+        <v>6.63932228088379</v>
       </c>
       <c r="H1087" t="n">
         <v>1789676</v>
@@ -31950,7 +31950,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.77070665359497</v>
+        <v>6.77070713043213</v>
       </c>
       <c r="H1089" t="n">
         <v>4105478</v>
@@ -32008,7 +32008,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.83202028274536</v>
+        <v>6.8320198059082</v>
       </c>
       <c r="H1091" t="n">
         <v>2735698</v>
@@ -32153,7 +32153,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.1750955581665</v>
+        <v>6.17509508132935</v>
       </c>
       <c r="H1096" t="n">
         <v>4329812</v>
@@ -32240,7 +32240,7 @@
         <v>6.97800016403198</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.11203050613403</v>
+        <v>6.11203002929688</v>
       </c>
       <c r="H1099" t="n">
         <v>2435047</v>
@@ -32327,7 +32327,7 @@
         <v>7.02600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.1540732383728</v>
+        <v>6.15407371520996</v>
       </c>
       <c r="H1102" t="n">
         <v>1881021</v>
@@ -32385,7 +32385,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.8159761428833</v>
+        <v>5.81597566604614</v>
       </c>
       <c r="H1104" t="n">
         <v>8087070</v>
@@ -32414,7 +32414,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1105" t="n">
         <v>7149824</v>
@@ -32443,7 +32443,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.72313022613525</v>
+        <v>5.72313070297241</v>
       </c>
       <c r="H1106" t="n">
         <v>3699841</v>
@@ -32559,7 +32559,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.70210933685303</v>
+        <v>5.70210886001587</v>
       </c>
       <c r="H1110" t="n">
         <v>1923276</v>
@@ -32675,7 +32675,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.80896854400635</v>
+        <v>5.80896902084351</v>
       </c>
       <c r="H1114" t="n">
         <v>4361584</v>
@@ -32733,7 +32733,7 @@
         <v>6.61199998855591</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.79145097732544</v>
+        <v>5.79145050048828</v>
       </c>
       <c r="H1116" t="n">
         <v>2745181</v>
@@ -32849,7 +32849,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1120" t="n">
         <v>2591742</v>
@@ -32878,7 +32878,7 @@
         <v>6.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.51466655731201</v>
+        <v>5.51466608047485</v>
       </c>
       <c r="H1121" t="n">
         <v>2373106</v>
@@ -33052,7 +33052,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1127" t="n">
         <v>3872429</v>
@@ -33139,7 +33139,7 @@
         <v>6.10200023651123</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.34474182128906</v>
+        <v>5.34474229812622</v>
       </c>
       <c r="H1130" t="n">
         <v>3138958</v>
@@ -33255,7 +33255,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.07496500015259</v>
+        <v>5.07496452331543</v>
       </c>
       <c r="H1134" t="n">
         <v>2639141</v>
@@ -33371,7 +33371,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.83146381378174</v>
+        <v>4.8314642906189</v>
       </c>
       <c r="H1138" t="n">
         <v>7274589</v>
@@ -33400,7 +33400,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.85423803329468</v>
+        <v>4.85423755645752</v>
       </c>
       <c r="H1139" t="n">
         <v>4216549</v>
@@ -33487,7 +33487,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1142" t="n">
         <v>4794446</v>
@@ -33603,7 +33603,7 @@
         <v>5.75</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.03642463684082</v>
+        <v>5.03642511367798</v>
       </c>
       <c r="H1146" t="n">
         <v>3404327</v>
@@ -33690,7 +33690,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1149" t="n">
         <v>7674033</v>
@@ -33748,7 +33748,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.6320366859436</v>
+        <v>5.63203716278076</v>
       </c>
       <c r="H1151" t="n">
         <v>7222178</v>
@@ -33777,7 +33777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1152" t="n">
         <v>4327989</v>
@@ -33806,7 +33806,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.78066205978394</v>
+        <v>4.78066253662109</v>
       </c>
       <c r="H1153" t="n">
         <v>37061837</v>
@@ -33864,7 +33864,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1155" t="n">
         <v>4632608</v>
@@ -33951,7 +33951,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.98912620544434</v>
+        <v>4.98912668228149</v>
       </c>
       <c r="H1158" t="n">
         <v>6885010</v>
@@ -34009,7 +34009,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1160" t="n">
         <v>9957880</v>
@@ -34154,7 +34154,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.76867771148682</v>
+        <v>5.76867723464966</v>
       </c>
       <c r="H1165" t="n">
         <v>6651859</v>
@@ -34212,7 +34212,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1167" t="n">
         <v>8734883</v>
@@ -34270,7 +34270,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>6.06122779846191</v>
+        <v>6.06122827529907</v>
       </c>
       <c r="H1169" t="n">
         <v>4897787</v>
@@ -34386,7 +34386,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>6.09626436233521</v>
+        <v>6.09626388549805</v>
       </c>
       <c r="H1173" t="n">
         <v>2164935</v>
@@ -34502,7 +34502,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G1177" t="n">
-        <v>6.16458415985107</v>
+        <v>6.16458463668823</v>
       </c>
       <c r="H1177" t="n">
         <v>2453991</v>
@@ -34560,7 +34560,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.26268482208252</v>
+        <v>6.26268529891968</v>
       </c>
       <c r="H1179" t="n">
         <v>4001288</v>
@@ -34705,7 +34705,7 @@
         <v>7.37200021743774</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.45713520050049</v>
+        <v>6.45713472366333</v>
       </c>
       <c r="H1184" t="n">
         <v>2760680</v>
@@ -34879,7 +34879,7 @@
         <v>7.48400020599365</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.55523586273193</v>
+        <v>6.55523538589478</v>
       </c>
       <c r="H1190" t="n">
         <v>23790555</v>
@@ -34937,7 +34937,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.47640466690063</v>
+        <v>6.47640419006348</v>
       </c>
       <c r="H1192" t="n">
         <v>2568121</v>
@@ -34995,7 +34995,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1194" t="n">
         <v>2394145</v>
@@ -35111,7 +35111,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.48691511154175</v>
+        <v>6.48691558837891</v>
       </c>
       <c r="H1198" t="n">
         <v>2306182</v>
@@ -35285,7 +35285,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.42034673690796</v>
+        <v>6.42034721374512</v>
       </c>
       <c r="H1204" t="n">
         <v>3351396</v>
@@ -35372,7 +35372,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.29947280883789</v>
+        <v>6.29947233200073</v>
       </c>
       <c r="H1207" t="n">
         <v>2115582</v>
@@ -35459,7 +35459,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.12078905105591</v>
+        <v>6.12078952789307</v>
       </c>
       <c r="H1210" t="n">
         <v>2524158</v>
@@ -35575,7 +35575,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.38005590438843</v>
+        <v>6.38005542755127</v>
       </c>
       <c r="H1214" t="n">
         <v>1891608</v>
@@ -35604,7 +35604,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.45888710021973</v>
+        <v>6.45888662338257</v>
       </c>
       <c r="H1215" t="n">
         <v>3816451</v>
@@ -35807,7 +35807,7 @@
         <v>7.10799980163574</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.22589731216431</v>
+        <v>6.22589683532715</v>
       </c>
       <c r="H1222" t="n">
         <v>2102386</v>
@@ -35836,7 +35836,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.21888971328735</v>
+        <v>6.21889019012451</v>
       </c>
       <c r="H1223" t="n">
         <v>1572333</v>
@@ -35865,7 +35865,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1224" t="n">
         <v>2471564</v>
@@ -35981,7 +35981,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.36779308319092</v>
+        <v>6.36779260635376</v>
       </c>
       <c r="H1228" t="n">
         <v>3004169</v>
@@ -36010,7 +36010,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.18385362625122</v>
+        <v>6.18385410308838</v>
       </c>
       <c r="H1229" t="n">
         <v>2909852</v>
@@ -36242,7 +36242,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>6.24516725540161</v>
+        <v>6.24516677856445</v>
       </c>
       <c r="H1237" t="n">
         <v>3040302</v>
@@ -36271,7 +36271,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.22239398956299</v>
+        <v>6.22239351272583</v>
       </c>
       <c r="H1238" t="n">
         <v>2078604</v>
@@ -36416,7 +36416,7 @@
         <v>6.73600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.900062084198</v>
+        <v>5.90006256103516</v>
       </c>
       <c r="H1243" t="n">
         <v>5965996</v>
@@ -36503,7 +36503,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.67583179473877</v>
+        <v>5.67583227157593</v>
       </c>
       <c r="H1246" t="n">
         <v>20274021</v>
@@ -36590,7 +36590,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.65831422805786</v>
+        <v>5.6583137512207</v>
       </c>
       <c r="H1249" t="n">
         <v>4172978</v>
@@ -36648,7 +36648,7 @@
         <v>6.3439998626709</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.55670928955078</v>
+        <v>5.55670976638794</v>
       </c>
       <c r="H1251" t="n">
         <v>3696298</v>
@@ -36677,7 +36677,7 @@
         <v>6.28399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.50415563583374</v>
+        <v>5.50415515899658</v>
       </c>
       <c r="H1252" t="n">
         <v>8525305</v>
@@ -36793,7 +36793,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.05569505691528</v>
+        <v>5.05569458007812</v>
       </c>
       <c r="H1256" t="n">
         <v>14625156</v>
@@ -36967,7 +36967,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.04868745803833</v>
+        <v>5.04868793487549</v>
       </c>
       <c r="H1262" t="n">
         <v>8026303</v>
@@ -36996,7 +36996,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.03116989135742</v>
+        <v>5.03116941452026</v>
       </c>
       <c r="H1263" t="n">
         <v>5145464</v>
@@ -37112,7 +37112,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1267" t="n">
         <v>4709326</v>
@@ -37170,7 +37170,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.81920194625854</v>
+        <v>4.81920146942139</v>
       </c>
       <c r="H1269" t="n">
         <v>4146077</v>
@@ -37199,7 +37199,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1270" t="n">
         <v>4071813</v>
@@ -37344,7 +37344,7 @@
         <v>5.40799999237061</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.73686695098877</v>
+        <v>4.73686742782593</v>
       </c>
       <c r="H1275" t="n">
         <v>4695582</v>
@@ -37402,7 +37402,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.9348201751709</v>
+        <v>4.93482065200806</v>
       </c>
       <c r="H1277" t="n">
         <v>9772286</v>
@@ -37431,7 +37431,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1278" t="n">
         <v>3662373</v>
@@ -37489,7 +37489,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1280" t="n">
         <v>4901519</v>
@@ -37547,7 +37547,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1282" t="n">
         <v>3934942</v>
@@ -37605,7 +37605,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.89102554321289</v>
+        <v>4.89102602005005</v>
       </c>
       <c r="H1284" t="n">
         <v>3927642</v>
@@ -37721,7 +37721,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.31320905685425</v>
+        <v>5.31320953369141</v>
       </c>
       <c r="H1288" t="n">
         <v>14159287</v>
@@ -37779,7 +37779,7 @@
         <v>6.32399988174438</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.53919172286987</v>
+        <v>5.53919124603271</v>
       </c>
       <c r="H1290" t="n">
         <v>6095275</v>
@@ -37866,7 +37866,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1293" t="n">
         <v>5308409</v>
@@ -37924,7 +37924,7 @@
         <v>6.34800004959106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.56021356582642</v>
+        <v>5.56021308898926</v>
       </c>
       <c r="H1295" t="n">
         <v>2259411</v>
@@ -37982,7 +37982,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1297" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1297" t="n">
         <v>3771355</v>
@@ -38127,7 +38127,7 @@
         <v>6.06400012969971</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.31145811080933</v>
+        <v>5.31145763397217</v>
       </c>
       <c r="H1302" t="n">
         <v>2961447</v>
@@ -38243,7 +38243,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.39904737472534</v>
+        <v>5.3990478515625</v>
       </c>
       <c r="H1306" t="n">
         <v>2486519</v>
@@ -38446,7 +38446,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.1380295753479</v>
+        <v>5.13802909851074</v>
       </c>
       <c r="H1313" t="n">
         <v>3958401</v>
@@ -38475,7 +38475,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.9558424949646</v>
+        <v>4.95584201812744</v>
       </c>
       <c r="H1314" t="n">
         <v>6725216</v>
@@ -38591,7 +38591,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1318" t="n">
         <v>4052927</v>
@@ -38736,7 +38736,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.02766609191895</v>
+        <v>5.02766561508179</v>
       </c>
       <c r="H1323" t="n">
         <v>3480359</v>
@@ -38794,7 +38794,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.06795692443848</v>
+        <v>5.06795740127563</v>
       </c>
       <c r="H1325" t="n">
         <v>3414708</v>
@@ -38823,7 +38823,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1326" t="n">
         <v>4509639</v>
@@ -38852,7 +38852,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.12927055358887</v>
+        <v>5.12927007675171</v>
       </c>
       <c r="H1327" t="n">
         <v>2757122</v>
@@ -38997,7 +38997,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.14678812026978</v>
+        <v>5.14678859710693</v>
       </c>
       <c r="H1332" t="n">
         <v>1796199</v>
@@ -39055,7 +39055,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.18707942962646</v>
+        <v>5.18707990646362</v>
       </c>
       <c r="H1334" t="n">
         <v>2442638</v>
@@ -39374,7 +39374,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.88051462173462</v>
+        <v>4.88051509857178</v>
       </c>
       <c r="H1345" t="n">
         <v>4271493</v>
@@ -39606,7 +39606,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.85248613357544</v>
+        <v>4.85248565673828</v>
       </c>
       <c r="H1353" t="n">
         <v>4336509</v>
@@ -39693,7 +39693,7 @@
         <v>5.81400012969971</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.0924825668335</v>
+        <v>5.09248304367065</v>
       </c>
       <c r="H1356" t="n">
         <v>4898496</v>
@@ -39780,7 +39780,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.32547187805176</v>
+        <v>5.32547235488892</v>
       </c>
       <c r="H1359" t="n">
         <v>4701653</v>
@@ -39838,7 +39838,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.36926698684692</v>
+        <v>5.36926746368408</v>
       </c>
       <c r="H1361" t="n">
         <v>3909309</v>
@@ -39925,7 +39925,7 @@
         <v>6.19199991226196</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.4235725402832</v>
+        <v>5.42357301712036</v>
       </c>
       <c r="H1364" t="n">
         <v>3847158</v>
@@ -39954,7 +39954,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.47787857055664</v>
+        <v>5.4778790473938</v>
       </c>
       <c r="H1365" t="n">
         <v>3685472</v>
@@ -39983,7 +39983,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.48488616943359</v>
+        <v>5.48488569259644</v>
       </c>
       <c r="H1366" t="n">
         <v>3441108</v>
@@ -40012,7 +40012,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1367" t="n">
         <v>3381920</v>
@@ -40070,7 +40070,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1369" t="n">
         <v>3235806</v>
@@ -40128,7 +40128,7 @@
         <v>6.2979998588562</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.51641845703125</v>
+        <v>5.51641798019409</v>
       </c>
       <c r="H1371" t="n">
         <v>5322391</v>
@@ -40157,7 +40157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>5.51816987991333</v>
+        <v>5.51817035675049</v>
       </c>
       <c r="H1372" t="n">
         <v>3366363</v>
@@ -40244,7 +40244,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.59174585342407</v>
+        <v>5.59174537658691</v>
       </c>
       <c r="H1375" t="n">
         <v>3821636</v>
@@ -40302,7 +40302,7 @@
         <v>6.33400011062622</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.54795074462891</v>
+        <v>5.54795026779175</v>
       </c>
       <c r="H1377" t="n">
         <v>3315855</v>
@@ -40563,7 +40563,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.28693246841431</v>
+        <v>5.28693199157715</v>
       </c>
       <c r="H1386" t="n">
         <v>4113408</v>
@@ -40592,7 +40592,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.36226034164429</v>
+        <v>5.36225986480713</v>
       </c>
       <c r="H1387" t="n">
         <v>3290342</v>
@@ -40737,7 +40737,7 @@
         <v>5.74200010299683</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.02941799163818</v>
+        <v>5.02941751480103</v>
       </c>
       <c r="H1392" t="n">
         <v>4143531</v>
@@ -40766,7 +40766,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.09423446655273</v>
+        <v>5.09423398971558</v>
       </c>
       <c r="H1393" t="n">
         <v>2910764</v>
@@ -40882,7 +40882,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1397" t="n">
-        <v>5.1362771987915</v>
+        <v>5.13627767562866</v>
       </c>
       <c r="H1397" t="n">
         <v>2272221</v>
@@ -40998,7 +40998,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G1401" t="n">
-        <v>5.2221155166626</v>
+        <v>5.22211599349976</v>
       </c>
       <c r="H1401" t="n">
         <v>2781403</v>
@@ -41027,7 +41027,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1402" t="n">
-        <v>5.25189638137817</v>
+        <v>5.25189590454102</v>
       </c>
       <c r="H1402" t="n">
         <v>3279098</v>
@@ -41172,7 +41172,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1407" t="n">
-        <v>5.19058322906494</v>
+        <v>5.1905837059021</v>
       </c>
       <c r="H1407" t="n">
         <v>3925528</v>
@@ -41288,7 +41288,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.99613380432129</v>
+        <v>4.99613332748413</v>
       </c>
       <c r="H1411" t="n">
         <v>4270124</v>
@@ -41404,7 +41404,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G1415" t="n">
-        <v>5.0136513710022</v>
+        <v>5.01365184783936</v>
       </c>
       <c r="H1415" t="n">
         <v>1473081</v>
@@ -41520,7 +41520,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1419" t="n">
-        <v>5.03292083740234</v>
+        <v>5.0329213142395</v>
       </c>
       <c r="H1419" t="n">
         <v>2554732</v>
@@ -41549,7 +41549,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.87350797653198</v>
+        <v>4.87350749969482</v>
       </c>
       <c r="H1420" t="n">
         <v>3590506</v>
@@ -41607,7 +41607,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.81569814682007</v>
+        <v>4.81569862365723</v>
       </c>
       <c r="H1422" t="n">
         <v>4575840</v>
@@ -41694,7 +41694,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.69657611846924</v>
+        <v>4.69657564163208</v>
       </c>
       <c r="H1425" t="n">
         <v>5875598</v>
@@ -41723,7 +41723,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.79818058013916</v>
+        <v>4.798180103302</v>
       </c>
       <c r="H1426" t="n">
         <v>3488592</v>
@@ -41839,7 +41839,7 @@
         <v>5.43800020217896</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.76314449310303</v>
+        <v>4.76314401626587</v>
       </c>
       <c r="H1430" t="n">
         <v>3257140</v>
@@ -41984,7 +41984,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.98211908340454</v>
+        <v>4.9821195602417</v>
       </c>
       <c r="H1435" t="n">
         <v>7574838</v>
@@ -42071,7 +42071,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.10649728775024</v>
+        <v>5.10649681091309</v>
       </c>
       <c r="H1438" t="n">
         <v>2730777</v>
@@ -42129,7 +42129,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.07146120071411</v>
+        <v>5.07146072387695</v>
       </c>
       <c r="H1440" t="n">
         <v>1533007</v>
@@ -42245,7 +42245,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02416229248047</v>
+        <v>5.02416276931763</v>
       </c>
       <c r="H1444" t="n">
         <v>2202329</v>
@@ -42274,7 +42274,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.89628124237061</v>
+        <v>4.89628076553345</v>
       </c>
       <c r="H1445" t="n">
         <v>4675269</v>
@@ -42332,7 +42332,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.70533466339111</v>
+        <v>4.70533514022827</v>
       </c>
       <c r="H1447" t="n">
         <v>7793029</v>
@@ -42361,7 +42361,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.60373020172119</v>
+        <v>4.60373067855835</v>
       </c>
       <c r="H1448" t="n">
         <v>9976060</v>
@@ -42535,7 +42535,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.8051872253418</v>
+        <v>4.80518770217896</v>
       </c>
       <c r="H1454" t="n">
         <v>3004546</v>
@@ -42564,7 +42564,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.75088167190552</v>
+        <v>4.75088119506836</v>
       </c>
       <c r="H1455" t="n">
         <v>2808013</v>
@@ -42593,7 +42593,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.65803575515747</v>
+        <v>4.65803623199463</v>
       </c>
       <c r="H1456" t="n">
         <v>5655649</v>
@@ -42651,7 +42651,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.59672355651855</v>
+        <v>4.5967230796814</v>
       </c>
       <c r="H1458" t="n">
         <v>3824274</v>
@@ -42680,7 +42680,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.41979169845581</v>
+        <v>4.41979122161865</v>
       </c>
       <c r="H1459" t="n">
         <v>8058243</v>
@@ -42709,7 +42709,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.11760568618774</v>
+        <v>4.1176061630249</v>
       </c>
       <c r="H1460" t="n">
         <v>24123068</v>
@@ -42883,7 +42883,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.22008609771729</v>
+        <v>4.22008562088013</v>
       </c>
       <c r="H1466" t="n">
         <v>4670040</v>
@@ -42941,7 +42941,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.26826047897339</v>
+        <v>4.26826095581055</v>
       </c>
       <c r="H1468" t="n">
         <v>3902061</v>
@@ -43086,7 +43086,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.30942821502686</v>
+        <v>4.3094277381897</v>
       </c>
       <c r="H1473" t="n">
         <v>5834136</v>
@@ -43115,7 +43115,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.19030570983887</v>
+        <v>4.19030523300171</v>
       </c>
       <c r="H1474" t="n">
         <v>6818198</v>
@@ -43144,7 +43144,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.1973123550415</v>
+        <v>4.19731283187866</v>
       </c>
       <c r="H1475" t="n">
         <v>2952983</v>
@@ -43260,7 +43260,7 @@
         <v>4.41099977493286</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.86359453201294</v>
+        <v>3.86359477043152</v>
       </c>
       <c r="H1479" t="n">
         <v>8014603</v>
@@ -43289,7 +43289,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.84958052635193</v>
+        <v>3.84958028793335</v>
       </c>
       <c r="H1480" t="n">
         <v>6037789</v>
@@ -43347,7 +43347,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.11147451400757</v>
+        <v>4.11147403717041</v>
       </c>
       <c r="H1482" t="n">
         <v>8500669</v>
@@ -43405,7 +43405,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.19118165969849</v>
+        <v>4.19118118286133</v>
       </c>
       <c r="H1484" t="n">
         <v>7447202</v>
@@ -43492,7 +43492,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.03789949417114</v>
+        <v>4.03789901733398</v>
       </c>
       <c r="H1487" t="n">
         <v>5494736</v>
@@ -43521,7 +43521,7 @@
         <v>4.65299987792969</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07556247711182</v>
+        <v>4.07556295394897</v>
       </c>
       <c r="H1488" t="n">
         <v>4602969</v>
@@ -43666,7 +43666,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.43205404281616</v>
+        <v>4.432053565979</v>
       </c>
       <c r="H1493" t="n">
         <v>27309297</v>
@@ -43869,7 +43869,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.49161529541016</v>
+        <v>4.491614818573</v>
       </c>
       <c r="H1500" t="n">
         <v>8080483</v>
@@ -43898,7 +43898,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.48110437393188</v>
+        <v>4.48110485076904</v>
       </c>
       <c r="H1501" t="n">
         <v>4113515</v>
@@ -44101,7 +44101,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>4.54592132568359</v>
+        <v>4.54592084884644</v>
       </c>
       <c r="H1508" t="n">
         <v>14782313</v>
@@ -44420,7 +44420,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.59118986129761</v>
+        <v>3.59119009971619</v>
       </c>
       <c r="H1519" t="n">
         <v>17657701</v>
@@ -44449,7 +44449,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.77512907981873</v>
+        <v>3.77512884140015</v>
       </c>
       <c r="H1520" t="n">
         <v>8953295</v>
@@ -44478,7 +44478,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.70330548286438</v>
+        <v>3.7033052444458</v>
       </c>
       <c r="H1521" t="n">
         <v>7954613</v>
@@ -44507,7 +44507,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.97746181488037</v>
+        <v>3.97746205329895</v>
       </c>
       <c r="H1522" t="n">
         <v>11433613</v>
@@ -44536,7 +44536,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.95819234848022</v>
+        <v>3.95819187164307</v>
       </c>
       <c r="H1523" t="n">
         <v>5220970</v>
@@ -44565,7 +44565,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.09483242034912</v>
+        <v>4.09483289718628</v>
       </c>
       <c r="H1524" t="n">
         <v>4457429</v>
@@ -44855,7 +44855,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.50562953948975</v>
+        <v>4.5056300163269</v>
       </c>
       <c r="H1534" t="n">
         <v>4978923</v>
@@ -44913,7 +44913,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.66504383087158</v>
+        <v>4.66504335403442</v>
       </c>
       <c r="H1536" t="n">
         <v>5610045</v>
@@ -44942,7 +44942,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.70358276367188</v>
+        <v>4.70358324050903</v>
       </c>
       <c r="H1537" t="n">
         <v>3404814</v>
@@ -45029,7 +45029,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.77365493774414</v>
+        <v>4.77365446090698</v>
       </c>
       <c r="H1540" t="n">
         <v>11366742</v>
@@ -45087,7 +45087,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.74387454986572</v>
+        <v>4.74387407302856</v>
       </c>
       <c r="H1542" t="n">
         <v>46986731</v>
@@ -55910,6 +55910,35 @@
         <v>3644967</v>
       </c>
       <c r="I1915" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1916" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1916" t="n">
+        <v>4.36800003051758</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>4.43800020217896</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>4.43800020217896</v>
+      </c>
+      <c r="G1916" t="n">
+        <v>4.43800020217896</v>
+      </c>
+      <c r="H1916" t="n">
+        <v>5417639</v>
+      </c>
+      <c r="I1916" t="s">
         <v>9</v>
       </c>
     </row>
